--- a/languages/ko/output/import/韩语TOPIK2.xlsx
+++ b/languages/ko/output/import/韩语TOPIK2.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>[[ˈsʰɘ(ː)ɭɭa̠ɭ]] Seollal (农历新年) (文化)</t>
+          <t>[[ˈsʰɘ(ː)ɭɭa̠ɭ]] 农历新年；春节 (명사)</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>Seollal (农历新年) (文化)</t>
+          <t>农历新年；春节 (명사)</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>[[sʰɯcçinɕʰip̚]] Skinship（肢体接触） (文化)</t>
+          <t>[[sʰɯcçinɕʰip̚]] 肢体接触；亲昵动作 (명사)</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>Skinship（肢体接触） (文化)</t>
+          <t>肢体接触；亲昵动作 (명사)</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʌ̹nɡo̞ŋ]] Major (教育)</t>
+          <t>[[t͡ɕʌ̹nɡo̞ŋ]] 专业；主修 (명사)</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
-          <t>Major (教育)</t>
+          <t>专业；主修 (명사)</t>
         </is>
       </c>
       <c r="E33" s="1" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>[[ha̠k̚t͡ɕ͈ʌ̹m]] GPA (教育)</t>
+          <t>[[ha̠k̚t͡ɕ͈ʌ̹m]] 学分；学业成绩 (명사)</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
-          <t>GPA (教育)</t>
+          <t>学分；学业成绩 (명사)</t>
         </is>
       </c>
       <c r="E35" s="1" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>[[pa̠ɭpʰjo]] PPT (教育)</t>
+          <t>[[pa̠ɭpʰjo]] 发表；演讲；发布 (명사)</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>PPT (教育)</t>
+          <t>发表；演讲；发布 (명사)</t>
         </is>
       </c>
       <c r="E43" s="1" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>[[xɯŋbunɦa̠da̠]] 浮躁？ (情感)</t>
+          <t>[[xɯŋbunɦa̠da̠]] 兴奋；激动 (동사)</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="D88" s="1" t="inlineStr">
         <is>
-          <t>浮躁？ (情感)</t>
+          <t>兴奋；激动 (동사)</t>
         </is>
       </c>
       <c r="E88" s="1" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>[[kʰo̞ŋɡɯʎʎiɕʰi]] 韩式英语（Konglish） (文化)</t>
+          <t>[[kʰo̞ŋɡɯʎʎiɕʰi]] 韩式英语；Konglish (명사)</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="D149" s="1" t="inlineStr">
         <is>
-          <t>韩式英语（Konglish） (文化)</t>
+          <t>韩式英语；Konglish (명사)</t>
         </is>
       </c>
       <c r="E149" s="1" t="inlineStr">
@@ -7219,7 +7219,7 @@
       </c>
       <c r="B213" s="1" t="inlineStr">
         <is>
-          <t>[[ˈko̞(ː)ŋɡa̠m]] Empathy 同理心 (人际关系)</t>
+          <t>[[ˈko̞(ː)ŋɡa̠m]] 同理心；共情 (명사)</t>
         </is>
       </c>
       <c r="C213" s="1" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="D213" s="1" t="inlineStr">
         <is>
-          <t>Empathy 同理心 (人际关系)</t>
+          <t>同理心；共情 (명사)</t>
         </is>
       </c>
       <c r="E213" s="1" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="B216" s="1" t="inlineStr">
         <is>
-          <t>[pinmimang] Closeness (人际关系)</t>
+          <t>[pinmimang] 亲密；亲密感 (명사)</t>
         </is>
       </c>
       <c r="C216" s="1" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="D216" s="1" t="inlineStr">
         <is>
-          <t>Closeness (人际关系)</t>
+          <t>亲密；亲密感 (명사)</t>
         </is>
       </c>
       <c r="E216" s="1" t="inlineStr">
@@ -7347,7 +7347,7 @@
       </c>
       <c r="B217" s="1" t="inlineStr">
         <is>
-          <t>[[judɛ]] Bond（押金） (人际关系)</t>
+          <t>[[judɛ]] 纽带；羁绊；联系 (명사)</t>
         </is>
       </c>
       <c r="C217" s="1" t="inlineStr">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="D217" s="1" t="inlineStr">
         <is>
-          <t>Bond（押金） (人际关系)</t>
+          <t>纽带；羁绊；联系 (명사)</t>
         </is>
       </c>
       <c r="E217" s="1" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="B294" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʰe̞ʝʌ̹ŋ]] Body Shape (身体部位)</t>
+          <t>[[t͡ɕʰe̞ʝʌ̹ŋ]] 体型；身材 (명사)</t>
         </is>
       </c>
       <c r="C294" s="1" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="D294" s="1" t="inlineStr">
         <is>
-          <t>Body Shape (身体部位)</t>
+          <t>体型；身材 (명사)</t>
         </is>
       </c>
       <c r="E294" s="1" t="inlineStr">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="B298" s="1" t="inlineStr">
         <is>
-          <t>[chwikoim] Monolid (身体部位)</t>
+          <t>[chwikoim] 单眼皮 (명사)</t>
         </is>
       </c>
       <c r="C298" s="1" t="inlineStr">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="D298" s="1" t="inlineStr">
         <is>
-          <t>Monolid (身体部位)</t>
+          <t>单眼皮 (명사)</t>
         </is>
       </c>
       <c r="E298" s="1" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="B356" s="1" t="inlineStr">
         <is>
-          <t>[[ɕʰik̚]] 仪式（Ceremony） (校园生活)</t>
+          <t>[[ɕʰik̚]] 仪式；典礼 (명사)</t>
         </is>
       </c>
       <c r="C356" s="1" t="inlineStr">
@@ -11805,7 +11805,7 @@
       </c>
       <c r="D356" s="1" t="inlineStr">
         <is>
-          <t>仪式（Ceremony） (校园生活)</t>
+          <t>仪式；典礼 (명사)</t>
         </is>
       </c>
       <c r="E356" s="1" t="inlineStr">
@@ -12915,7 +12915,7 @@
       </c>
       <c r="B391" s="1" t="inlineStr">
         <is>
-          <t>[umrungyope] Polo衫 (服饰)</t>
+          <t>[umrungyope] Polo衫；翻领马球衫 (명사)</t>
         </is>
       </c>
       <c r="C391" s="1" t="inlineStr">
@@ -12925,7 +12925,7 @@
       </c>
       <c r="D391" s="1" t="inlineStr">
         <is>
-          <t>Polo衫 (服饰)</t>
+          <t>Polo衫；翻领马球衫 (명사)</t>
         </is>
       </c>
       <c r="E391" s="1" t="inlineStr">
@@ -17459,7 +17459,7 @@
       </c>
       <c r="B533" s="1" t="inlineStr">
         <is>
-          <t>[[ins͈a̠]] Inssa (俚语)</t>
+          <t>[[ins͈a̠]] 社交达人；圈内人 (명사)</t>
         </is>
       </c>
       <c r="C533" s="1" t="inlineStr">
@@ -17469,7 +17469,7 @@
       </c>
       <c r="D533" s="1" t="inlineStr">
         <is>
-          <t>Inssa (俚语)</t>
+          <t>社交达人；圈内人 (명사)</t>
         </is>
       </c>
       <c r="E533" s="1" t="inlineStr">
@@ -17491,7 +17491,7 @@
       </c>
       <c r="B534" s="1" t="inlineStr">
         <is>
-          <t>[[çʌ̹ntʰa̠]] Hyuntae (俚语)</t>
+          <t>[[çʌ̹ntʰa̠]] 现实清醒时间；贤者模式；幻灭感 (명사)</t>
         </is>
       </c>
       <c r="C534" s="1" t="inlineStr">
@@ -17501,7 +17501,7 @@
       </c>
       <c r="D534" s="1" t="inlineStr">
         <is>
-          <t>Hyuntae (俚语)</t>
+          <t>现实清醒时间；贤者模式；幻灭感 (명사)</t>
         </is>
       </c>
       <c r="E534" s="1" t="inlineStr">
@@ -17523,7 +17523,7 @@
       </c>
       <c r="B535" s="1" t="inlineStr">
         <is>
-          <t>[katnget] Gatsaeng (俚语)</t>
+          <t>[katnget] 模范充实人生；开挂般的生活 (명사)</t>
         </is>
       </c>
       <c r="C535" s="1" t="inlineStr">
@@ -17533,7 +17533,7 @@
       </c>
       <c r="D535" s="1" t="inlineStr">
         <is>
-          <t>Gatsaeng (俚语)</t>
+          <t>模范充实人生；开挂般的生活 (명사)</t>
         </is>
       </c>
       <c r="E535" s="1" t="inlineStr">
@@ -17555,7 +17555,7 @@
       </c>
       <c r="B536" s="1" t="inlineStr">
         <is>
-          <t>[nguwket] Sowhakhaeng (俚语)</t>
+          <t>[nguwket] 微小而确实的幸福；小确幸 (명사)</t>
         </is>
       </c>
       <c r="C536" s="1" t="inlineStr">
@@ -17565,7 +17565,7 @@
       </c>
       <c r="D536" s="1" t="inlineStr">
         <is>
-          <t>Sowhakhaeng (俚语)</t>
+          <t>微小而确实的幸福；小确幸 (명사)</t>
         </is>
       </c>
       <c r="E536" s="1" t="inlineStr">
@@ -17587,7 +17587,7 @@
       </c>
       <c r="B537" s="1" t="inlineStr">
         <is>
-          <t>[[k͈o̞ndɛ]] Kkondae (俚语)</t>
+          <t>[[k͈o̞ndɛ]] 顽固长辈；老古板 (명사)</t>
         </is>
       </c>
       <c r="C537" s="1" t="inlineStr">
@@ -17597,7 +17597,7 @@
       </c>
       <c r="D537" s="1" t="inlineStr">
         <is>
-          <t>Kkondae (俚语)</t>
+          <t>顽固长辈；老古板 (명사)</t>
         </is>
       </c>
       <c r="E537" s="1" t="inlineStr">
@@ -17619,7 +17619,7 @@
       </c>
       <c r="B538" s="1" t="inlineStr">
         <is>
-          <t>[[ka̠p̚p͈uns͈a̠]] Gabbunsssa (俚语)</t>
+          <t>[[ka̠p̚p͈uns͈a̠]] 气氛突然冷场；突然尴尬 (명사)</t>
         </is>
       </c>
       <c r="C538" s="1" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="D538" s="1" t="inlineStr">
         <is>
-          <t>Gabbunsssa (俚语)</t>
+          <t>气氛突然冷场；突然尴尬 (명사)</t>
         </is>
       </c>
       <c r="E538" s="1" t="inlineStr">
@@ -17715,7 +17715,7 @@
       </c>
       <c r="B541" s="1" t="inlineStr">
         <is>
-          <t>[mikngeechie] Mixtape (音乐)</t>
+          <t>[mikngeechie] 混音带；Mixtape (명사)</t>
         </is>
       </c>
       <c r="C541" s="1" t="inlineStr">
@@ -17725,7 +17725,7 @@
       </c>
       <c r="D541" s="1" t="inlineStr">
         <is>
-          <t>Mixtape (音乐)</t>
+          <t>混音带；Mixtape (명사)</t>
         </is>
       </c>
       <c r="E541" s="1" t="inlineStr">
@@ -17811,7 +17811,7 @@
       </c>
       <c r="B544" s="1" t="inlineStr">
         <is>
-          <t>[nguchwikang] FOMO(Fear of missing out)恐惧症。 (俚语)</t>
+          <t>[nguchwikang] 疏离感；被孤立感 (명사)</t>
         </is>
       </c>
       <c r="C544" s="1" t="inlineStr">
@@ -17821,7 +17821,7 @@
       </c>
       <c r="D544" s="1" t="inlineStr">
         <is>
-          <t>FOMO(Fear of missing out)恐惧症。 (俚语)</t>
+          <t>疏离感；被孤立感 (명사)</t>
         </is>
       </c>
       <c r="E544" s="1" t="inlineStr">
@@ -18163,7 +18163,7 @@
       </c>
       <c r="B555" s="1" t="inlineStr">
         <is>
-          <t>[[a̠d͡ʑɛ]] Ajae (俚语)</t>
+          <t>[[a̠d͡ʑɛ]] 大叔；老伯 (명사)</t>
         </is>
       </c>
       <c r="C555" s="1" t="inlineStr">
@@ -18173,7 +18173,7 @@
       </c>
       <c r="D555" s="1" t="inlineStr">
         <is>
-          <t>Ajae (俚语)</t>
+          <t>大叔；老伯 (명사)</t>
         </is>
       </c>
       <c r="E555" s="1" t="inlineStr">
@@ -21011,7 +21011,7 @@
       </c>
       <c r="B644" s="1" t="inlineStr">
         <is>
-          <t>[inehe] Fintech (科技)</t>
+          <t>[inehe] 金融科技；Fintech (명사)</t>
         </is>
       </c>
       <c r="C644" s="1" t="inlineStr">
@@ -21021,7 +21021,7 @@
       </c>
       <c r="D644" s="1" t="inlineStr">
         <is>
-          <t>Fintech (科技)</t>
+          <t>金融科技；Fintech (명사)</t>
         </is>
       </c>
       <c r="E644" s="1" t="inlineStr">
@@ -21235,7 +21235,7 @@
       </c>
       <c r="B651" s="1" t="inlineStr">
         <is>
-          <t>[[kʰucçi]] Cookie (科技)</t>
+          <t>[[kʰucçi]] 曲奇；Cookie (명사)</t>
         </is>
       </c>
       <c r="C651" s="1" t="inlineStr">
@@ -21245,7 +21245,7 @@
       </c>
       <c r="D651" s="1" t="inlineStr">
         <is>
-          <t>Cookie (科技)</t>
+          <t>曲奇；Cookie (명사)</t>
         </is>
       </c>
       <c r="E651" s="1" t="inlineStr">
@@ -26835,7 +26835,7 @@
       </c>
       <c r="B826" s="1" t="inlineStr">
         <is>
-          <t>[ngemritpek] Slingback (时尚与风格)</t>
+          <t>[ngemritpek] 后跟系带凉鞋；Slingback (명사)</t>
         </is>
       </c>
       <c r="C826" s="1" t="inlineStr">
@@ -26845,7 +26845,7 @@
       </c>
       <c r="D826" s="1" t="inlineStr">
         <is>
-          <t>Slingback (时尚与风格)</t>
+          <t>后跟系带凉鞋；Slingback (명사)</t>
         </is>
       </c>
       <c r="E826" s="1" t="inlineStr">
@@ -27091,7 +27091,7 @@
       </c>
       <c r="B834" s="1" t="inlineStr">
         <is>
-          <t>[[kwa̠ŋɦa̠ps͈ʌ̹ŋ]] 光合作用(Photosynthesis) (环境)</t>
+          <t>[[kwa̠ŋɦa̠ps͈ʌ̹ŋ]] 光合作用 (명사)</t>
         </is>
       </c>
       <c r="C834" s="1" t="inlineStr">
@@ -27101,7 +27101,7 @@
       </c>
       <c r="D834" s="1" t="inlineStr">
         <is>
-          <t>光合作用(Photosynthesis) (环境)</t>
+          <t>光合作用 (명사)</t>
         </is>
       </c>
       <c r="E834" s="1" t="inlineStr">
@@ -34131,7 +34131,7 @@
       </c>
       <c r="B1054" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕwe̞(ː)]] 罪 (joe) (宗教)</t>
+          <t>[[t͡ɕwe̞(ː)]] 罪过；罪 (명사)</t>
         </is>
       </c>
       <c r="C1054" s="1" t="inlineStr">
@@ -34141,7 +34141,7 @@
       </c>
       <c r="D1054" s="1" t="inlineStr">
         <is>
-          <t>罪 (joe) (宗教)</t>
+          <t>罪过；罪 (명사)</t>
         </is>
       </c>
       <c r="E1054" s="1" t="inlineStr">
@@ -34163,7 +34163,7 @@
       </c>
       <c r="B1055" s="1" t="inlineStr">
         <is>
-          <t>[[ˈku(ː)wʌ̹n]] 救赎 (guseok) (宗教)</t>
+          <t>[[ˈku(ː)wʌ̹n]] 救赎；拯救 (명사)</t>
         </is>
       </c>
       <c r="C1055" s="1" t="inlineStr">
@@ -34173,7 +34173,7 @@
       </c>
       <c r="D1055" s="1" t="inlineStr">
         <is>
-          <t>救赎 (guseok) (宗教)</t>
+          <t>救赎；拯救 (명사)</t>
         </is>
       </c>
       <c r="E1055" s="1" t="inlineStr">
@@ -34195,7 +34195,7 @@
       </c>
       <c r="B1056" s="1" t="inlineStr">
         <is>
-          <t>[[ɯnʝe̞]] 恩典 (eunhye) (宗教)</t>
+          <t>[[ɯnʝe̞]] 恩典；恩惠 (명사)</t>
         </is>
       </c>
       <c r="C1056" s="1" t="inlineStr">
@@ -34205,7 +34205,7 @@
       </c>
       <c r="D1056" s="1" t="inlineStr">
         <is>
-          <t>恩典 (eunhye) (宗教)</t>
+          <t>恩典；恩惠 (명사)</t>
         </is>
       </c>
       <c r="E1056" s="1" t="inlineStr">
@@ -34227,7 +34227,7 @@
       </c>
       <c r="B1057" s="1" t="inlineStr">
         <is>
-          <t>[[ˈɸwe̞(ː)ɡɛ]] 悔改 (hoekai) (宗教)</t>
+          <t>[[ˈɸwe̞(ː)ɡɛ]] 悔改；忏悔 (명사)</t>
         </is>
       </c>
       <c r="C1057" s="1" t="inlineStr">
@@ -34237,7 +34237,7 @@
       </c>
       <c r="D1057" s="1" t="inlineStr">
         <is>
-          <t>悔改 (hoekai) (宗教)</t>
+          <t>悔改；忏悔 (명사)</t>
         </is>
       </c>
       <c r="E1057" s="1" t="inlineStr">
@@ -34259,7 +34259,7 @@
       </c>
       <c r="B1058" s="1" t="inlineStr">
         <is>
-          <t>[[ˈpu(ː)βwa̠ɭ]] 复活 (hubok) (宗教)</t>
+          <t>[[ˈpu(ː)βwa̠ɭ]] 复活；再生 (명사)</t>
         </is>
       </c>
       <c r="C1058" s="1" t="inlineStr">
@@ -34269,7 +34269,7 @@
       </c>
       <c r="D1058" s="1" t="inlineStr">
         <is>
-          <t>复活 (hubok) (宗教)</t>
+          <t>复活；再生 (명사)</t>
         </is>
       </c>
       <c r="E1058" s="1" t="inlineStr">
@@ -34451,7 +34451,7 @@
       </c>
       <c r="B1064" s="1" t="inlineStr">
         <is>
-          <t>[[to̞(ː)ɭ]] 周岁宴 (Dol) (亲子与家庭生活)</t>
+          <t>[[to̞(ː)ɭ]] 周岁；周岁宴 (명사)</t>
         </is>
       </c>
       <c r="C1064" s="1" t="inlineStr">
@@ -34461,7 +34461,7 @@
       </c>
       <c r="D1064" s="1" t="inlineStr">
         <is>
-          <t>周岁宴 (Dol) (亲子与家庭生活)</t>
+          <t>周岁；周岁宴 (명사)</t>
         </is>
       </c>
       <c r="E1064" s="1" t="inlineStr">
@@ -34803,7 +34803,7 @@
       </c>
       <c r="B1075" s="1" t="inlineStr">
         <is>
-          <t>[[tɯŋdɛ]] 【11】蓝方基地 (建筑)</t>
+          <t>[[tɯŋdɛ]] 灯塔 (명사)</t>
         </is>
       </c>
       <c r="C1075" s="1" t="inlineStr">
@@ -34813,7 +34813,7 @@
       </c>
       <c r="D1075" s="1" t="inlineStr">
         <is>
-          <t>【11】蓝方基地 (建筑)</t>
+          <t>灯塔 (명사)</t>
         </is>
       </c>
       <c r="E1075" s="1" t="inlineStr">
@@ -35955,7 +35955,7 @@
       </c>
       <c r="B1111" s="1" t="inlineStr">
         <is>
-          <t>[[o̞pʰisʰɯtʰe̞ɭ]] Officetel (建筑)</t>
+          <t>[[o̞pʰisʰɯtʰe̞ɭ]] 商住两用楼；单身公寓 (명사)</t>
         </is>
       </c>
       <c r="C1111" s="1" t="inlineStr">
@@ -35965,7 +35965,7 @@
       </c>
       <c r="D1111" s="1" t="inlineStr">
         <is>
-          <t>Officetel (建筑)</t>
+          <t>商住两用楼；单身公寓 (명사)</t>
         </is>
       </c>
       <c r="E1111" s="1" t="inlineStr">
@@ -36947,7 +36947,7 @@
       </c>
       <c r="B1142" s="1" t="inlineStr">
         <is>
-          <t>[[sʰa̠mɡje̞tʰa̠ŋ]] 参鸡汤(Samgyetang) (韩式饮食)</t>
+          <t>[[sʰa̠mɡje̞tʰa̠ŋ]] 参鸡汤 (명사)</t>
         </is>
       </c>
       <c r="C1142" s="1" t="inlineStr">
@@ -36957,7 +36957,7 @@
       </c>
       <c r="D1142" s="1" t="inlineStr">
         <is>
-          <t>参鸡汤(Samgyetang) (韩式饮食)</t>
+          <t>参鸡汤 (명사)</t>
         </is>
       </c>
       <c r="E1142" s="1" t="inlineStr">
@@ -36979,7 +36979,7 @@
       </c>
       <c r="B1143" s="1" t="inlineStr">
         <is>
-          <t>[[put͡ɕʰimɡɛ]] 韩式煎饼(Buchimgae) (韩式饮食)</t>
+          <t>[[put͡ɕʰimɡɛ]] 韩式煎饼 (명사)</t>
         </is>
       </c>
       <c r="C1143" s="1" t="inlineStr">
@@ -36989,7 +36989,7 @@
       </c>
       <c r="D1143" s="1" t="inlineStr">
         <is>
-          <t>韩式煎饼(Buchimgae) (韩式饮食)</t>
+          <t>韩式煎饼 (명사)</t>
         </is>
       </c>
       <c r="E1143" s="1" t="inlineStr">
@@ -37299,7 +37299,7 @@
       </c>
       <c r="B1153" s="1" t="inlineStr">
         <is>
-          <t>[tumngupipingpang] 石锅拌饭 (Dolsot Bibimbap) (韩国饮食)</t>
+          <t>[tumngupipingpang] 石锅拌饭 (명사)</t>
         </is>
       </c>
       <c r="C1153" s="1" t="inlineStr">
@@ -37309,7 +37309,7 @@
       </c>
       <c r="D1153" s="1" t="inlineStr">
         <is>
-          <t>石锅拌饭 (Dolsot Bibimbap) (韩国饮食)</t>
+          <t>石锅拌饭 (명사)</t>
         </is>
       </c>
       <c r="E1153" s="1" t="inlineStr">
@@ -37331,7 +37331,7 @@
       </c>
       <c r="B1154" s="1" t="inlineStr">
         <is>
-          <t>[[ta̠k̚p͈o̞k͈ɯmtʰa̠ŋ]] 辣炖鸡 (Dak Bokkeum Tang) (韩国饮食)</t>
+          <t>[[ta̠k̚p͈o̞k͈ɯmtʰa̠ŋ]] 辣炖鸡 (명사)</t>
         </is>
       </c>
       <c r="C1154" s="1" t="inlineStr">
@@ -37341,7 +37341,7 @@
       </c>
       <c r="D1154" s="1" t="inlineStr">
         <is>
-          <t>辣炖鸡 (Dak Bokkeum Tang) (韩国饮食)</t>
+          <t>辣炖鸡 (명사)</t>
         </is>
       </c>
       <c r="E1154" s="1" t="inlineStr">
@@ -37363,7 +37363,7 @@
       </c>
       <c r="B1155" s="1" t="inlineStr">
         <is>
-          <t>[kampikuring] 炖带鱼 (Galchi Jorim) (韩国饮食)</t>
+          <t>[kampikuring] 炖带鱼 (명사)</t>
         </is>
       </c>
       <c r="C1155" s="1" t="inlineStr">
@@ -37373,7 +37373,7 @@
       </c>
       <c r="D1155" s="1" t="inlineStr">
         <is>
-          <t>炖带鱼 (Galchi Jorim) (韩国饮食)</t>
+          <t>炖带鱼 (명사)</t>
         </is>
       </c>
       <c r="E1155" s="1" t="inlineStr">
@@ -37395,7 +37395,7 @@
       </c>
       <c r="B1156" s="1" t="inlineStr">
         <is>
-          <t>[makkikngi] 荞麦面 (Makguksu) (韩国饮食)</t>
+          <t>[makkikngi] 荞麦面 (명사)</t>
         </is>
       </c>
       <c r="C1156" s="1" t="inlineStr">
@@ -37405,7 +37405,7 @@
       </c>
       <c r="D1156" s="1" t="inlineStr">
         <is>
-          <t>荞麦面 (Makguksu) (韩国饮食)</t>
+          <t>荞麦面 (명사)</t>
         </is>
       </c>
       <c r="E1156" s="1" t="inlineStr">
@@ -37427,7 +37427,7 @@
       </c>
       <c r="B1157" s="1" t="inlineStr">
         <is>
-          <t>[myompipukcheng] 炒小鱼干 (Myeolchi Bokkeum) (韩国饮食)</t>
+          <t>[myompipukcheng] 炒小鱼干 (명사)</t>
         </is>
       </c>
       <c r="C1157" s="1" t="inlineStr">
@@ -37437,7 +37437,7 @@
       </c>
       <c r="D1157" s="1" t="inlineStr">
         <is>
-          <t>炒小鱼干 (Myeolchi Bokkeum) (韩国饮食)</t>
+          <t>炒小鱼干 (명사)</t>
         </is>
       </c>
       <c r="E1157" s="1" t="inlineStr">
@@ -37459,7 +37459,7 @@
       </c>
       <c r="B1158" s="1" t="inlineStr">
         <is>
-          <t>[ngintekik] 米肠汤 (Sundaeguk) (韩国饮食)</t>
+          <t>[ngintekik] 米肠汤 (명사)</t>
         </is>
       </c>
       <c r="C1158" s="1" t="inlineStr">
@@ -37469,7 +37469,7 @@
       </c>
       <c r="D1158" s="1" t="inlineStr">
         <is>
-          <t>米肠汤 (Sundaeguk) (韩国饮食)</t>
+          <t>米肠汤 (명사)</t>
         </is>
       </c>
       <c r="E1158" s="1" t="inlineStr">
@@ -37491,7 +37491,7 @@
       </c>
       <c r="B1159" s="1" t="inlineStr">
         <is>
-          <t>[[kʌ̹t̚t͡ɕ͈ʌ̹ɾi]] 鲜拌泡菜 (Geotjeori) (韩国饮食)</t>
+          <t>[[kʌ̹t̚t͡ɕ͈ʌ̹ɾi]] 鲜拌泡菜 (명사)</t>
         </is>
       </c>
       <c r="C1159" s="1" t="inlineStr">
@@ -37501,7 +37501,7 @@
       </c>
       <c r="D1159" s="1" t="inlineStr">
         <is>
-          <t>鲜拌泡菜 (Geotjeori) (韩国饮食)</t>
+          <t>鲜拌泡菜 (명사)</t>
         </is>
       </c>
       <c r="E1159" s="1" t="inlineStr">
@@ -37523,7 +37523,7 @@
       </c>
       <c r="B1160" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕo̞ɾim]] 炖煮 (Jorim) (韩国饮食)</t>
+          <t>[[t͡ɕo̞ɾim]] 酱油炖煮菜；炖菜 (명사)</t>
         </is>
       </c>
       <c r="C1160" s="1" t="inlineStr">
@@ -37533,7 +37533,7 @@
       </c>
       <c r="D1160" s="1" t="inlineStr">
         <is>
-          <t>炖煮 (Jorim) (韩国饮食)</t>
+          <t>酱油炖煮菜；炖菜 (명사)</t>
         </is>
       </c>
       <c r="E1160" s="1" t="inlineStr">
@@ -37555,7 +37555,7 @@
       </c>
       <c r="B1161" s="1" t="inlineStr">
         <is>
-          <t>[[mut͡ɕʰim]] 拌菜 (Muchim) (韩国饮食)</t>
+          <t>[[mut͡ɕʰim]] 凉拌菜 (명사)</t>
         </is>
       </c>
       <c r="C1161" s="1" t="inlineStr">
@@ -37565,7 +37565,7 @@
       </c>
       <c r="D1161" s="1" t="inlineStr">
         <is>
-          <t>拌菜 (Muchim) (韩国饮食)</t>
+          <t>凉拌菜 (명사)</t>
         </is>
       </c>
       <c r="E1161" s="1" t="inlineStr">
@@ -37587,7 +37587,7 @@
       </c>
       <c r="B1162" s="1" t="inlineStr">
         <is>
-          <t>[[k͈a̠k̚t͈uɡi]] 块状萝卜泡菜 (Kkakdugi) (韩国饮食)</t>
+          <t>[[k͈a̠k̚t͈uɡi]] 辣萝卜块；萝卜泡菜 (명사)</t>
         </is>
       </c>
       <c r="C1162" s="1" t="inlineStr">
@@ -37597,7 +37597,7 @@
       </c>
       <c r="D1162" s="1" t="inlineStr">
         <is>
-          <t>块状萝卜泡菜 (Kkakdugi) (韩国饮食)</t>
+          <t>辣萝卜块；萝卜泡菜 (명사)</t>
         </is>
       </c>
       <c r="E1162" s="1" t="inlineStr">
@@ -37619,7 +37619,7 @@
       </c>
       <c r="B1163" s="1" t="inlineStr">
         <is>
-          <t>[talkik] 鸡肉粥 (Dakjuk) (韩国饮食)</t>
+          <t>[talkik] 鸡肉粥 (명사)</t>
         </is>
       </c>
       <c r="C1163" s="1" t="inlineStr">
@@ -37629,7 +37629,7 @@
       </c>
       <c r="D1163" s="1" t="inlineStr">
         <is>
-          <t>鸡肉粥 (Dakjuk) (韩国饮食)</t>
+          <t>鸡肉粥 (명사)</t>
         </is>
       </c>
       <c r="E1163" s="1" t="inlineStr">
@@ -37651,7 +37651,7 @@
       </c>
       <c r="B1164" s="1" t="inlineStr">
         <is>
-          <t>[kankatkichi] Ganjang Gui (韩国饮食文化)</t>
+          <t>[kankatkichi] 酱油烤肉/烤鱼；酱油烧烤 (명사)</t>
         </is>
       </c>
       <c r="C1164" s="1" t="inlineStr">
@@ -37661,7 +37661,7 @@
       </c>
       <c r="D1164" s="1" t="inlineStr">
         <is>
-          <t>Ganjang Gui (韩国饮食文化)</t>
+          <t>酱油烤肉/烤鱼；酱油烧烤 (명사)</t>
         </is>
       </c>
       <c r="E1164" s="1" t="inlineStr">
@@ -37683,7 +37683,7 @@
       </c>
       <c r="B1165" s="1" t="inlineStr">
         <is>
-          <t>[upakkon] Hobak Jeon (韩国饮食文化)</t>
+          <t>[upakkon] 煎西葫芦饼；南瓜饼 (명사)</t>
         </is>
       </c>
       <c r="C1165" s="1" t="inlineStr">
@@ -37693,7 +37693,7 @@
       </c>
       <c r="D1165" s="1" t="inlineStr">
         <is>
-          <t>Hobak Jeon (韩国饮食文化)</t>
+          <t>煎西葫芦饼；南瓜饼 (명사)</t>
         </is>
       </c>
       <c r="E1165" s="1" t="inlineStr">
@@ -37715,7 +37715,7 @@
       </c>
       <c r="B1166" s="1" t="inlineStr">
         <is>
-          <t>[twekikikpang] Dwaeji Gukbap (韩国饮食文化)</t>
+          <t>[twekikikpang] 猪肉汤饭 (명사)</t>
         </is>
       </c>
       <c r="C1166" s="1" t="inlineStr">
@@ -37725,7 +37725,7 @@
       </c>
       <c r="D1166" s="1" t="inlineStr">
         <is>
-          <t>Dwaeji Gukbap (韩国饮食文化)</t>
+          <t>猪肉汤饭 (명사)</t>
         </is>
       </c>
       <c r="E1166" s="1" t="inlineStr">
@@ -37747,7 +37747,7 @@
       </c>
       <c r="B1167" s="1" t="inlineStr">
         <is>
-          <t>[[kʰa̠ɭɡuks͈u]] Kalguksu (韩国饮食文化)</t>
+          <t>[[kʰa̠ɭɡuks͈u]] 刀切面；刀削面 (명사)</t>
         </is>
       </c>
       <c r="C1167" s="1" t="inlineStr">
@@ -37757,7 +37757,7 @@
       </c>
       <c r="D1167" s="1" t="inlineStr">
         <is>
-          <t>Kalguksu (韩国饮食文化)</t>
+          <t>刀切面；刀削面 (명사)</t>
         </is>
       </c>
       <c r="E1167" s="1" t="inlineStr">
@@ -37779,7 +37779,7 @@
       </c>
       <c r="B1168" s="1" t="inlineStr">
         <is>
-          <t>[pipikon] Buchu Jeon (韩国饮食文化)</t>
+          <t>[pipikon] 韭菜煎饼 (명사)</t>
         </is>
       </c>
       <c r="C1168" s="1" t="inlineStr">
@@ -37789,7 +37789,7 @@
       </c>
       <c r="D1168" s="1" t="inlineStr">
         <is>
-          <t>Buchu Jeon (韩国饮食文化)</t>
+          <t>韭菜煎饼 (명사)</t>
         </is>
       </c>
       <c r="E1168" s="1" t="inlineStr">
@@ -37843,7 +37843,7 @@
       </c>
       <c r="B1170" s="1" t="inlineStr">
         <is>
-          <t>[ngintepukcheng] Sundae Bokkeum (韩国饮食文化)</t>
+          <t>[ngintepukcheng] 炒米肠 (명사)</t>
         </is>
       </c>
       <c r="C1170" s="1" t="inlineStr">
@@ -37853,7 +37853,7 @@
       </c>
       <c r="D1170" s="1" t="inlineStr">
         <is>
-          <t>Sundae Bokkeum (韩国饮食文化)</t>
+          <t>炒米肠 (명사)</t>
         </is>
       </c>
       <c r="E1170" s="1" t="inlineStr">
@@ -37907,7 +37907,7 @@
       </c>
       <c r="B1172" s="1" t="inlineStr">
         <is>
-          <t>[[ta̠k̚t͈o̞ɾitʰa̠ŋ]] Dakdoritang (韩国饮食文化)</t>
+          <t>[[ta̠k̚t͈o̞ɾitʰa̠ŋ]] 辣子鸡汤；辣炒鸡块 (명사)</t>
         </is>
       </c>
       <c r="C1172" s="1" t="inlineStr">
@@ -37917,7 +37917,7 @@
       </c>
       <c r="D1172" s="1" t="inlineStr">
         <is>
-          <t>Dakdoritang (韩国饮食文化)</t>
+          <t>辣子鸡汤；辣炒鸡块 (명사)</t>
         </is>
       </c>
       <c r="E1172" s="1" t="inlineStr">
@@ -37939,7 +37939,7 @@
       </c>
       <c r="B1173" s="1" t="inlineStr">
         <is>
-          <t>[chwku] Yukpo (韩国饮食文化)</t>
+          <t>[chwku] 肉干；牛肉干 (명사)</t>
         </is>
       </c>
       <c r="C1173" s="1" t="inlineStr">
@@ -37949,7 +37949,7 @@
       </c>
       <c r="D1173" s="1" t="inlineStr">
         <is>
-          <t>Yukpo (韩国饮食文化)</t>
+          <t>肉干；牛肉干 (명사)</t>
         </is>
       </c>
       <c r="E1173" s="1" t="inlineStr">
@@ -37971,7 +37971,7 @@
       </c>
       <c r="B1174" s="1" t="inlineStr">
         <is>
-          <t>[[to̞tʰo̞ɾimuk̚]] Dotorimuk (韩国饮食文化)</t>
+          <t>[[to̞tʰo̞ɾimuk̚]] 橡子冻；橡子凉粉 (명사)</t>
         </is>
       </c>
       <c r="C1174" s="1" t="inlineStr">
@@ -37981,7 +37981,7 @@
       </c>
       <c r="D1174" s="1" t="inlineStr">
         <is>
-          <t>Dotorimuk (韩国饮食文化)</t>
+          <t>橡子冻；橡子凉粉 (명사)</t>
         </is>
       </c>
       <c r="E1174" s="1" t="inlineStr">
@@ -38003,7 +38003,7 @@
       </c>
       <c r="B1175" s="1" t="inlineStr">
         <is>
-          <t>[[ko̞mtʰa̠ŋ]] Gomtang (韩国饮食文化)</t>
+          <t>[[ko̞mtʰa̠ŋ]] 牛骨汤；牛肉浓汤 (명사)</t>
         </is>
       </c>
       <c r="C1175" s="1" t="inlineStr">
@@ -38013,7 +38013,7 @@
       </c>
       <c r="D1175" s="1" t="inlineStr">
         <is>
-          <t>Gomtang (韩国饮食文化)</t>
+          <t>牛骨汤；牛肉浓汤 (명사)</t>
         </is>
       </c>
       <c r="E1175" s="1" t="inlineStr">
@@ -38035,7 +38035,7 @@
       </c>
       <c r="B1176" s="1" t="inlineStr">
         <is>
-          <t>[ngichwk] Suyuk (韩国饮食文化)</t>
+          <t>[ngichwk] 白切肉；熟肉 (명사)</t>
         </is>
       </c>
       <c r="C1176" s="1" t="inlineStr">
@@ -38045,7 +38045,7 @@
       </c>
       <c r="D1176" s="1" t="inlineStr">
         <is>
-          <t>Suyuk (韩国饮食文化)</t>
+          <t>白切肉；熟肉 (명사)</t>
         </is>
       </c>
       <c r="E1176" s="1" t="inlineStr">

--- a/languages/ko/output/import/韩语TOPIK2.xlsx
+++ b/languages/ko/output/import/韩语TOPIK2.xlsx
@@ -16339,7 +16339,7 @@
       </c>
       <c r="B498" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕa̠ŋɕʰikʰa̠da̠]] 传唤 ,传讯,扣发债务人的工资,扣押债务人的财产 ;v.下达扣押令 (烹饪)</t>
+          <t>[[t͡ɕa̠ŋɕʰikʰa̠da̠]] 装饰；装点；点缀 (동사)</t>
         </is>
       </c>
       <c r="C498" s="1" t="inlineStr">
@@ -16349,7 +16349,7 @@
       </c>
       <c r="D498" s="1" t="inlineStr">
         <is>
-          <t>传唤 ,传讯,扣发债务人的工资,扣押债务人的财产 ;v.下达扣押令 (烹饪)</t>
+          <t>装饰；装点；点缀 (동사)</t>
         </is>
       </c>
       <c r="E498" s="1" t="inlineStr">

--- a/languages/ko/output/import/韩语TOPIK2.xlsx
+++ b/languages/ko/output/import/韩语TOPIK2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="词汇表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="词汇表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -659,12 +659,12 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>[ngapamchengngik] 寺庙饮食 (文化)</t>
+          <t>[[sa̠t͡ɕʰa̠ɾɯmɕʰik̚]] 寺庙饮食 (文化)</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>ngapamchengngik</t>
+          <t>[sa̠t͡ɕʰa̠ɾɯmɕʰik̚]</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
@@ -851,12 +851,12 @@
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>[ngonmimaki] 赠礼 (文化)</t>
+          <t>[[sʰʌ̹nmulha̠ɡi]] 赠礼 (文化)</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>ngonmimaki</t>
+          <t>[sʰʌ̹nmulha̠ɡi]</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>[pimwiken] 通勤 (日常生活)</t>
+          <t>[[t͡ɕʰuɭtʰwe̞ɡɯn]] 通勤 (日常生活)</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>pimwiken</t>
+          <t>[t͡ɕʰuɭtʰwe̞ɡɯn]</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>[konkatkongkin] 健康检查 (日常生活)</t>
+          <t>[[kʌ̹nha̠ŋɡʌ̹mt͡ɕin]] 健康检查 (日常生活)</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>konkatkongkin</t>
+          <t>[kʌ̹nha̠ŋɡʌ̹mt͡ɕin]</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>[kewmchyt] 回收 (日常生活)</t>
+          <t>[[t͡ɕɛːɦwa̠ʎʎoŋ]] 回收 (日常生活)</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>kewmchyt</t>
+          <t>[t͡ɕɛːɦwa̠ʎʎoŋ]</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
@@ -1139,17 +1139,17 @@
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>[kanyonkyomke] 移动支付 (日常生活)</t>
+          <t>[[ka̠npʲʌ̹nkjʌ̹lkʲe̞]] 便捷支付 (日常生活)</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>kanyonkyomke</t>
+          <t>[ka̠npʲʌ̹nkjʌ̹lkʲe̞]</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>移动支付 (日常生活)</t>
+          <t>便捷支付 (日常生活)</t>
         </is>
       </c>
       <c r="E23" s="1" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>[[ha̠p̚k͈jʌ̹k̚]] 及格 (教育)</t>
+          <t>[[ha̠p̚k͈jʌ̹k̚]] 合格；通过 (教育)</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
-          <t>及格 (教育)</t>
+          <t>合格；通过 (教育)</t>
         </is>
       </c>
       <c r="E25" s="1" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>[[po̞ks͈ɯp̚]] 复诊记录 (教育)</t>
+          <t>[[po̞ks͈ɯp̚]] 复习 (教育)</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
-          <t>复诊记录 (教育)</t>
+          <t>复习 (教育)</t>
         </is>
       </c>
       <c r="E27" s="1" t="inlineStr">
@@ -1491,17 +1491,17 @@
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>[pikonkut] 不重要 (教育)</t>
+          <t>[[puːt͡ɕʌ̹nɡo̞ŋ]] 辅修专业 (教育)</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>pikonkut</t>
+          <t>[puːt͡ɕʌ̹nɡo̞ŋ]</t>
         </is>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>不重要 (教育)</t>
+          <t>辅修专业 (教育)</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>[[e̞s͈e̞i]] 作文 (教育)</t>
+          <t>[[e̞s͈e̞i]] 随笔；散文 (教育)</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>作文 (教育)</t>
+          <t>随笔；散文 (教育)</t>
         </is>
       </c>
       <c r="E44" s="1" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>[[ˈi(ː)ɾjʌ̹ks͈ʌ̹]] 履历 (教育)</t>
+          <t>[[ˈi(ː)ɾjʌ̹ks͈ʌ̹]] 简历 (教育)</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>履历 (教育)</t>
+          <t>简历 (教育)</t>
         </is>
       </c>
       <c r="E52" s="1" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>[choakchen] 语学院 (教育)</t>
+          <t>[[ʌːhaɡwʌn]] 语学院 (教育)</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>choakchen</t>
+          <t>[ʌːhaɡwʌn]</t>
         </is>
       </c>
       <c r="D55" s="1" t="inlineStr">
@@ -2227,12 +2227,12 @@
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>[chironit] 电子学习 (教育)</t>
+          <t>[[irʌniŋ]] 电子学习 (教育)</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>chironit</t>
+          <t>[irʌniŋ]</t>
         </is>
       </c>
       <c r="D57" s="1" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>[makangchim] 截止日期 (教育)</t>
+          <t>[[maɡamiɭ]] 截止日期 (教育)</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>makangchim</t>
+          <t>[maɡamiɭ]</t>
         </is>
       </c>
       <c r="D58" s="1" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>[aknyontu] 学年： (教育)</t>
+          <t>[[hʌŋɲʌndo]] 学年： (教育)</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>aknyontu</t>
+          <t>[hʌŋɲʌndo]</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr">
@@ -2547,12 +2547,12 @@
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>[chantuata] 放心的 (情感)</t>
+          <t>[[a̠ndoɦa̠da̠]] 放心的 (情感)</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>chantuata</t>
+          <t>[a̠ndoɦa̠da̠]</t>
         </is>
       </c>
       <c r="D67" s="1" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>[[ma̠ɲd͡ʑo̞ks͈ɯɾʌ̹p̚t͈a̠]] 操作内容 (情感)</t>
+          <t>[[ma̠ɲd͡ʑo̞ks͈ɯɾʌ̹p̚t͈a̠]] 满足 (情感)</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="D68" s="1" t="inlineStr">
         <is>
-          <t>操作内容 (情感)</t>
+          <t>满足 (情感)</t>
         </is>
       </c>
       <c r="E68" s="1" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>[pitkyokpakta] 震惊 (情感)</t>
+          <t>[[t͡ɕʰuŋɡjʌ̹k̚pa̠t̚ta̠]] 震惊 (情感)</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>pitkyokpakta</t>
+          <t>[t͡ɕʰuŋɡjʌ̹k̚pa̠t̚ta̠]</t>
         </is>
       </c>
       <c r="D69" s="1" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>[changtutwita] 不知所措 (情绪)</t>
+          <t>[[a̠p̚to̞twe̞da̠]] 不知所措 (情绪)</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>changtutwita</t>
+          <t>[a̠p̚to̞twe̞da̠]</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr">
@@ -2835,12 +2835,12 @@
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>[pimchankotata] 不安全感 (情绪)</t>
+          <t>[[puɾa̠ndʑʌ̹ŋɦa̠da̠]] 不安全感 (情绪)</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>pimchankotata</t>
+          <t>[puɾa̠ndʑʌ̹ŋɦa̠da̠]</t>
         </is>
       </c>
       <c r="D76" s="1" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>[kommatata] 绝望 (情绪)</t>
+          <t>[[t͡ɕʌ̹ɾma̠ŋɦa̠da̠]] 绝望 (情绪)</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>kommatata</t>
+          <t>[t͡ɕʌ̹ɾma̠ŋɦa̠da̠]</t>
         </is>
       </c>
       <c r="D77" s="1" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>[chyomkotkokchita] 热情 (情绪)</t>
+          <t>[[jʌ̹ɾt͡ɕʌ̹ŋd͡ʑʌ̹ɡida̠]] 热情 (情绪)</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>chyomkotkokchita</t>
+          <t>[jʌ̹ɾt͡ɕʌ̹ŋd͡ʑʌ̹ɡida̠]</t>
         </is>
       </c>
       <c r="D79" s="1" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>[naktangata] 垂头丧气 (情感)</t>
+          <t>[[na̠k̚ta̠ma̠da̠]] 垂头丧气 (情感)</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>naktangata</t>
+          <t>[na̠k̚ta̠ma̠da̠]</t>
         </is>
       </c>
       <c r="D84" s="1" t="inlineStr">
@@ -3123,12 +3123,12 @@
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>[kompakata] 绝望 (情感)</t>
+          <t>[[t͡ɕʌ̹ɾba̠kʰa̠da̠]] 绝望 (情感)</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
         <is>
-          <t>kompakata</t>
+          <t>[t͡ɕʌ̹ɾba̠kʰa̠da̠]</t>
         </is>
       </c>
       <c r="D85" s="1" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>[[kɯɾiwʌ̹ɦa̠da̠]] 渴望 (情感)</t>
+          <t>[[kɯɾiwʌ̹ɦa̠da̠]] 思念 (情感)</t>
         </is>
       </c>
       <c r="C86" s="1" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="D86" s="1" t="inlineStr">
         <is>
-          <t>渴望 (情感)</t>
+          <t>思念 (情感)</t>
         </is>
       </c>
       <c r="E86" s="1" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>[chimmokchita] 哭 (情感)</t>
+          <t>[[uɾmʌ̹ɡida̠]] 哭 (情感)</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>chimmokchita</t>
+          <t>[uɾmʌ̹ɡida̠]</t>
         </is>
       </c>
       <c r="D87" s="1" t="inlineStr">
@@ -3283,17 +3283,17 @@
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>[cikngerongta] 迎头痛击 (情感)</t>
+          <t>[[s͈uks͈ʌ̹ɾʌ̹p̚t͈a̠]] 害羞 (情感)</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>cikngerongta</t>
+          <t>[s͈uks͈ʌ̹ɾʌ̹p̚t͈a̠]</t>
         </is>
       </c>
       <c r="D90" s="1" t="inlineStr">
         <is>
-          <t>迎头痛击 (情感)</t>
+          <t>害羞 (情感)</t>
         </is>
       </c>
       <c r="E90" s="1" t="inlineStr">
@@ -3315,17 +3315,17 @@
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>[tetangata] 加粗 (情感)</t>
+          <t>[[tɛ̝da̠ma̠da̠]] 大胆 (情感)</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>tetangata</t>
+          <t>[tɛ̝da̠ma̠da̠]</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr">
         <is>
-          <t>加粗 (情感)</t>
+          <t>大胆 (情感)</t>
         </is>
       </c>
       <c r="E91" s="1" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>[[ɸʷunβunɦa̠da̠]] 治愈向 (情感)</t>
+          <t>[[ɸʷunβunɦa̠da̠]] 温馨；暖人心 (情感)</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
-          <t>治愈向 (情感)</t>
+          <t>温馨；暖人心 (情感)</t>
         </is>
       </c>
       <c r="E92" s="1" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>[sitetata] 已履约 (情感)</t>
+          <t>[[p͈ɯdɯtʰa̠da̠]] 欣慰 (情感)</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>sitetata</t>
+          <t>[p͈ɯdɯtʰa̠da̠]</t>
         </is>
       </c>
       <c r="D93" s="1" t="inlineStr">
         <is>
-          <t>已履约 (情感)</t>
+          <t>欣慰 (情感)</t>
         </is>
       </c>
       <c r="E93" s="1" t="inlineStr">
@@ -3571,12 +3571,12 @@
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>[emimakon] 海鲜葱饼 (食物)</t>
+          <t>[[hɛmulpʰadʑʌn]] 海鲜葱饼 (食物)</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>emimakon</t>
+          <t>[hɛmulpʰadʑʌn]</t>
         </is>
       </c>
       <c r="D99" s="1" t="inlineStr">
@@ -3635,12 +3635,12 @@
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>[hutkikngi] 豆浆冷面 (食物)</t>
+          <t>[[koŋɡuks͈u]] 豆浆冷面 (食物)</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>hutkikngi</t>
+          <t>[koŋɡuks͈u]</t>
         </is>
       </c>
       <c r="D101" s="1" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>[emimat] 海鲜汤 (食物)</t>
+          <t>[[hɛmultʰaŋ]] 海鲜汤 (食物)</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t>emimat</t>
+          <t>[hɛmultʰaŋ]</t>
         </is>
       </c>
       <c r="D105" s="1" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>[[sʰundɛ]] 圣代 (食物)</t>
+          <t>[[sʰundɛ]] 米肠 (食物)</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
-          <t>圣代 (食物)</t>
+          <t>米肠 (食物)</t>
         </is>
       </c>
       <c r="E108" s="1" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>[[ja̠ŋɲʌ̹m]] 韩式辣椒酱 (食物)</t>
+          <t>[[ja̠ŋɲʌ̹m]] 调味料 (食物)</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="D109" s="1" t="inlineStr">
         <is>
-          <t>韩式辣椒酱 (食物)</t>
+          <t>调味料 (食物)</t>
         </is>
       </c>
       <c r="E109" s="1" t="inlineStr">
@@ -3923,12 +3923,12 @@
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>[chetchenamkechy] 我支持你 (问候)</t>
+          <t>[[ɯŋwʌnhalɡ͈ejo]] 我支持你 (问候)</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
         <is>
-          <t>chetchenamkechy</t>
+          <t>[ɯŋwʌnhalɡ͈ejo]</t>
         </is>
       </c>
       <c r="D110" s="1" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>[karatngerochechy] 我为你感到骄傲 (问候语)</t>
+          <t>[[t͡ɕaɾaŋsɯɾʌwʌjo]] 我为你感到骄傲 (问候语)</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
         <is>
-          <t>karatngerochechy</t>
+          <t>[t͡ɕaɾaŋsɯɾʌwʌjo]</t>
         </is>
       </c>
       <c r="D111" s="1" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>[pyommamcengchemchy] 不客气 (问候语)</t>
+          <t>[[bjʌlmals͈ɯmɯljo]] 不客气 (问候语)</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t>pyommamcengchemchy</t>
+          <t>[bjʌlmals͈ɯmɯljo]</t>
         </is>
       </c>
       <c r="D112" s="1" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>[eruuke] 求婚 (关系)</t>
+          <t>[[pʰɯɾopʰoʒɯ]] 求婚 (关系)</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
         <is>
-          <t>eruuke</t>
+          <t>[pʰɯɾopʰoʒɯ]</t>
         </is>
       </c>
       <c r="D119" s="1" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="B129" s="1" t="inlineStr">
         <is>
-          <t>[[ˈɰi(ː)ɾi]] 忠诚 (人际关系)</t>
+          <t>[[ˈɰi(ː)ɾi]] 义气；情义 (人际关系)</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="D129" s="1" t="inlineStr">
         <is>
-          <t>忠诚 (人际关系)</t>
+          <t>义气；情义 (人际关系)</t>
         </is>
       </c>
       <c r="E129" s="1" t="inlineStr">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>[[tɯk̚tʰe̞m]] 讨价还价/优惠 (购物)</t>
+          <t>[[tɯk̚tʰe̞m]] 淘到好货 (购物)</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="D130" s="1" t="inlineStr">
         <is>
-          <t>讨价还价/优惠 (购物)</t>
+          <t>淘到好货 (购物)</t>
         </is>
       </c>
       <c r="E130" s="1" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>[ankotan] 限量版 (购物)</t>
+          <t>[[ha̠ɲd͡ʑʌ̹ŋpʰa̠n]] 限量版 (购物)</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
         <is>
-          <t>ankotan</t>
+          <t>[ha̠ɲd͡ʑʌ̹ŋpʰa̠n]</t>
         </is>
       </c>
       <c r="D131" s="1" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>[momiemrechicho] 멀티플레이어 (文化)</t>
+          <t>[[mʌlɭtʰipʰɯlle̞ie̞o]] 멀티플레이어 (文化)</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
         <is>
-          <t>momiemrechicho</t>
+          <t>[mʌlɭtʰipʰɯlle̞ie̞o]</t>
         </is>
       </c>
       <c r="D136" s="1" t="inlineStr">
@@ -4787,17 +4787,17 @@
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t>[chyonngengnget] 韩国流行音乐学员 (文化)</t>
+          <t>[[jʌnsɯbsɛŋ]] 练习生 (文化)</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr">
         <is>
-          <t>chyonngengnget</t>
+          <t>[jʌnsɯbsɛŋ]</t>
         </is>
       </c>
       <c r="D137" s="1" t="inlineStr">
         <is>
-          <t>韩国流行音乐学员 (文化)</t>
+          <t>练习生 (文化)</t>
         </is>
       </c>
       <c r="E137" s="1" t="inlineStr">
@@ -4819,12 +4819,12 @@
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>[kiwiknga] 娱乐公司 (文化)</t>
+          <t>[[kihwɛksa]] 娱乐公司 (文化)</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
         <is>
-          <t>kiwiknga</t>
+          <t>[kihwɛksa]</t>
         </is>
       </c>
       <c r="D138" s="1" t="inlineStr">
@@ -4851,12 +4851,12 @@
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>[chanien] 黑粉 (文化)</t>
+          <t>[[antipʰɛn]] 黑粉 (文化)</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
         <is>
-          <t>chanien</t>
+          <t>[antipʰɛn]</t>
         </is>
       </c>
       <c r="D139" s="1" t="inlineStr">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>[[kundɛ]] 兵役 (文化)</t>
+          <t>[[kundɛ]] 军队 (文化)</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="D140" s="1" t="inlineStr">
         <is>
-          <t>兵役 (文化)</t>
+          <t>军队 (文化)</t>
         </is>
       </c>
       <c r="E140" s="1" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>[[ˈɯ(ː)ŋwʌ̹nbʌ̹p̚]] 粉丝呐喊 (文化)</t>
+          <t>[[ˈɯ(ː)ŋwʌ̹nbʌ̹p̚]] 应援方法 (文化)</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="D144" s="1" t="inlineStr">
         <is>
-          <t>粉丝呐喊 (文化)</t>
+          <t>应援方法 (文化)</t>
         </is>
       </c>
       <c r="E144" s="1" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>[ngingatngik] 颁奖典礼 (文化)</t>
+          <t>[[ɕisɐŋɕik]] 颁奖典礼 (文化)</t>
         </is>
       </c>
       <c r="C146" s="1" t="inlineStr">
         <is>
-          <t>ngingatngik</t>
+          <t>[ɕisɐŋɕik]</t>
         </is>
       </c>
       <c r="D146" s="1" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>[tatwtngerochin] 慌乱 (情绪)</t>
+          <t>[[tʰa̠ŋɦwa̠ŋsɯɾʌ̹wn]] 慌乱 (情绪)</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr">
         <is>
-          <t>tatwtngerochin</t>
+          <t>[tʰa̠ŋɦwa̠ŋsɯɾʌ̹wn]</t>
         </is>
       </c>
       <c r="D151" s="1" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>[kangtutpakchen] 深受感动 (情绪)</t>
+          <t>[[ka̠mdo̞ŋpa̠dɯn]] 深受感动 (情绪)</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr">
         <is>
-          <t>kangtutpakchen</t>
+          <t>[ka̠mdo̞ŋpa̠dɯn]</t>
         </is>
       </c>
       <c r="D152" s="1" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t>[chumikapa] 五味子茶 (食物)</t>
+          <t>[[o̞mid͡ʑa̠t͡ɕʰa̠]] 五味子茶 (食物)</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr">
         <is>
-          <t>chumikapa</t>
+          <t>[o̞mid͡ʑa̠t͡ɕʰa̠]</t>
         </is>
       </c>
       <c r="D154" s="1" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="B174" s="1" t="inlineStr">
         <is>
-          <t>[[ha̠k̚]] 起重机 (自然)</t>
+          <t>[[ha̠k̚]] 鹤 (自然)</t>
         </is>
       </c>
       <c r="C174" s="1" t="inlineStr">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="D174" s="1" t="inlineStr">
         <is>
-          <t>起重机 (自然)</t>
+          <t>鹤 (自然)</t>
         </is>
       </c>
       <c r="E174" s="1" t="inlineStr">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="B176" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʰʌ̹ɭs͈ɛ]] 鸟类迁徙 (自然)</t>
+          <t>[[t͡ɕʰʌ̹ɭs͈ɛ]] 候鸟 (自然)</t>
         </is>
       </c>
       <c r="C176" s="1" t="inlineStr">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="D176" s="1" t="inlineStr">
         <is>
-          <t>鸟类迁徙 (自然)</t>
+          <t>候鸟 (自然)</t>
         </is>
       </c>
       <c r="E176" s="1" t="inlineStr">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="B177" s="1" t="inlineStr">
         <is>
-          <t>[[to̞tʰo̞ɾi]] 栓皮栎 (自然)</t>
+          <t>[[to̞tʰo̞ɾi]] 橡子 (自然)</t>
         </is>
       </c>
       <c r="C177" s="1" t="inlineStr">
@@ -6077,7 +6077,7 @@
       </c>
       <c r="D177" s="1" t="inlineStr">
         <is>
-          <t>栓皮栎 (自然)</t>
+          <t>橡子 (自然)</t>
         </is>
       </c>
       <c r="E177" s="1" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="B180" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕa̠ɡa̠ɭ]] 鹅卵石 (自然)</t>
+          <t>[[t͡ɕa̠ɡa̠ɭ]] 碎石 (自然)</t>
         </is>
       </c>
       <c r="C180" s="1" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="D180" s="1" t="inlineStr">
         <is>
-          <t>鹅卵石 (自然)</t>
+          <t>碎石 (自然)</t>
         </is>
       </c>
       <c r="E180" s="1" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="B183" s="1" t="inlineStr">
         <is>
-          <t>[achingngechim] 限时特卖 (购物)</t>
+          <t>[[tʰa̠imsʰe̞il̚]] 限时特卖 (购物)</t>
         </is>
       </c>
       <c r="C183" s="1" t="inlineStr">
         <is>
-          <t>achingngechim</t>
+          <t>[tʰa̠imsʰe̞il̚]</t>
         </is>
       </c>
       <c r="D183" s="1" t="inlineStr">
@@ -6291,12 +6291,12 @@
       </c>
       <c r="B184" s="1" t="inlineStr">
         <is>
-          <t>[puketngo] 保证书 (购物)</t>
+          <t>[[po̞dʑʌ̹ŋs͈ʌ̹]] 保证书 (购物)</t>
         </is>
       </c>
       <c r="C184" s="1" t="inlineStr">
         <is>
-          <t>puketngo</t>
+          <t>[po̞dʑʌ̹ŋs͈ʌ̹]</t>
         </is>
       </c>
       <c r="D184" s="1" t="inlineStr">
@@ -6483,12 +6483,12 @@
       </c>
       <c r="B190" s="1" t="inlineStr">
         <is>
-          <t>[eit] 海风 (自然)</t>
+          <t>[[hɛpʰuŋ]] 海风 (自然)</t>
         </is>
       </c>
       <c r="C190" s="1" t="inlineStr">
         <is>
-          <t>eit</t>
+          <t>[hɛpʰuŋ]</t>
         </is>
       </c>
       <c r="D190" s="1" t="inlineStr">
@@ -6515,12 +6515,12 @@
       </c>
       <c r="B191" s="1" t="inlineStr">
         <is>
-          <t>[chuenmahet] 开放式市场 (购物)</t>
+          <t>[[o̞pʰɛnma̞kʰɛt̚]] 开放式市场 (购物)</t>
         </is>
       </c>
       <c r="C191" s="1" t="inlineStr">
         <is>
-          <t>chuenmahet</t>
+          <t>[o̞pʰɛnma̞kʰɛt̚]</t>
         </is>
       </c>
       <c r="D191" s="1" t="inlineStr">
@@ -6547,12 +6547,12 @@
       </c>
       <c r="B192" s="1" t="inlineStr">
         <is>
-          <t>[hengipek] 现金回馈 (购物)</t>
+          <t>[[kʰɛɕʰibɛk̚]] 现金回馈 (购物)</t>
         </is>
       </c>
       <c r="C192" s="1" t="inlineStr">
         <is>
-          <t>hengipek</t>
+          <t>[kʰɛɕʰibɛk̚]</t>
         </is>
       </c>
       <c r="D192" s="1" t="inlineStr">
@@ -6579,12 +6579,12 @@
       </c>
       <c r="B193" s="1" t="inlineStr">
         <is>
-          <t>[pittutkime] 冲动购物 (购物)</t>
+          <t>[[t͡ɕʰuŋdoŋɡumɛ]] 冲动购物 (购物)</t>
         </is>
       </c>
       <c r="C193" s="1" t="inlineStr">
         <is>
-          <t>pittutkime</t>
+          <t>[t͡ɕʰuŋdoŋɡumɛ]</t>
         </is>
       </c>
       <c r="D193" s="1" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="B201" s="1" t="inlineStr">
         <is>
-          <t>[kekyomang] 复合 (人际关系)</t>
+          <t>[[t͡ɕɛɡjʌɦap̚]] 复合 (人际关系)</t>
         </is>
       </c>
       <c r="C201" s="1" t="inlineStr">
         <is>
-          <t>kekyomang</t>
+          <t>[t͡ɕɛɡjʌɦap̚]</t>
         </is>
       </c>
       <c r="D201" s="1" t="inlineStr">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="B206" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕo̞nɡjʌ̹ŋɦa̠da̠]] 钦佩 (人际关系)</t>
+          <t>[[t͡ɕo̞nɡjʌ̹ŋɦa̠da̠]] 尊敬 (人际关系)</t>
         </is>
       </c>
       <c r="C206" s="1" t="inlineStr">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="D206" s="1" t="inlineStr">
         <is>
-          <t>钦佩 (人际关系)</t>
+          <t>尊敬 (人际关系)</t>
         </is>
       </c>
       <c r="E206" s="1" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="B207" s="1" t="inlineStr">
         <is>
-          <t>[[no̞ʎʎida̠]] 开玩笑 (人际关系)</t>
+          <t>[[no̞ʎʎida̠]] 捉弄；戏弄 (人际关系)</t>
         </is>
       </c>
       <c r="C207" s="1" t="inlineStr">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="D207" s="1" t="inlineStr">
         <is>
-          <t>开玩笑 (人际关系)</t>
+          <t>捉弄；戏弄 (人际关系)</t>
         </is>
       </c>
       <c r="E207" s="1" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="B209" s="1" t="inlineStr">
         <is>
-          <t>[[ˈhɘ(ː)nɕʰin]] 承诺 (人际关系)</t>
+          <t>[[ˈhɘ(ː)nɕʰin]] 奉献 (人际关系)</t>
         </is>
       </c>
       <c r="C209" s="1" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="D209" s="1" t="inlineStr">
         <is>
-          <t>承诺 (人际关系)</t>
+          <t>奉献 (人际关系)</t>
         </is>
       </c>
       <c r="E209" s="1" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="B210" s="1" t="inlineStr">
         <is>
-          <t>[onkot] 献辞 (人际关系)</t>
+          <t>[[hʌnd͡ʑʌŋ]] 献辞 (人际关系)</t>
         </is>
       </c>
       <c r="C210" s="1" t="inlineStr">
         <is>
-          <t>onkot</t>
+          <t>[hʌnd͡ʑʌŋ]</t>
         </is>
       </c>
       <c r="D210" s="1" t="inlineStr">
@@ -7283,12 +7283,12 @@
       </c>
       <c r="B215" s="1" t="inlineStr">
         <is>
-          <t>[tatetang] 温暖 (人际关系)</t>
+          <t>[[t͈a̠t͈ɯtʰa̠m]] 温暖 (人际关系)</t>
         </is>
       </c>
       <c r="C215" s="1" t="inlineStr">
         <is>
-          <t>tatetang</t>
+          <t>[t͈a̠t͈ɯtʰa̠m]</t>
         </is>
       </c>
       <c r="D215" s="1" t="inlineStr">
@@ -7315,12 +7315,12 @@
       </c>
       <c r="B216" s="1" t="inlineStr">
         <is>
-          <t>[pinmimang] 亲密；亲密感 (명사)</t>
+          <t>[[pʰinmiɾam]] 亲密；亲密感 (명사)</t>
         </is>
       </c>
       <c r="C216" s="1" t="inlineStr">
         <is>
-          <t>pinmimang</t>
+          <t>[pʰinmiɾam]</t>
         </is>
       </c>
       <c r="D216" s="1" t="inlineStr">
@@ -7635,17 +7635,17 @@
       </c>
       <c r="B226" s="1" t="inlineStr">
         <is>
-          <t>[piniki] 葡萄酒 (购物)</t>
+          <t>[[pint͡ɕid͡ʑi]] 复古 (购物)</t>
         </is>
       </c>
       <c r="C226" s="1" t="inlineStr">
         <is>
-          <t>piniki</t>
+          <t>[pint͡ɕid͡ʑi]</t>
         </is>
       </c>
       <c r="D226" s="1" t="inlineStr">
         <is>
-          <t>葡萄酒 (购物)</t>
+          <t>复古 (购物)</t>
         </is>
       </c>
       <c r="E226" s="1" t="inlineStr">
@@ -7667,7 +7667,7 @@
       </c>
       <c r="B227" s="1" t="inlineStr">
         <is>
-          <t>[[ˈkjɘ(ː)ŋmɛ]] 投拍 (购物)</t>
+          <t>[[ˈkjɘ(ː)ŋmɛ]] 拍卖 (购物)</t>
         </is>
       </c>
       <c r="C227" s="1" t="inlineStr">
@@ -7677,7 +7677,7 @@
       </c>
       <c r="D227" s="1" t="inlineStr">
         <is>
-          <t>投拍 (购物)</t>
+          <t>拍卖 (购物)</t>
         </is>
       </c>
       <c r="E227" s="1" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="B229" s="1" t="inlineStr">
         <is>
-          <t>[kechingku] 补货 (购物)</t>
+          <t>[[t͡ɕeːip̚pʰo̞]] 补货 (购物)</t>
         </is>
       </c>
       <c r="C229" s="1" t="inlineStr">
         <is>
-          <t>kechingku</t>
+          <t>[t͡ɕeːip̚pʰo̞]</t>
         </is>
       </c>
       <c r="D229" s="1" t="inlineStr">
@@ -7955,12 +7955,12 @@
       </c>
       <c r="B236" s="1" t="inlineStr">
         <is>
-          <t>[rangngeo] 龙虾 (动物)</t>
+          <t>[[ɾap̚sʰɯtʰʌ̹]] 龙虾 (动物)</t>
         </is>
       </c>
       <c r="C236" s="1" t="inlineStr">
         <is>
-          <t>rangngeo</t>
+          <t>[ɾap̚sʰɯtʰʌ̹]</t>
         </is>
       </c>
       <c r="D236" s="1" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="B240" s="1" t="inlineStr">
         <is>
-          <t>[emramitku] 红鹤 (动物)</t>
+          <t>[[pʰɯɭɭamiŋɡo̞]] 红鹤 (动物)</t>
         </is>
       </c>
       <c r="C240" s="1" t="inlineStr">
         <is>
-          <t>emramitku</t>
+          <t>[pʰɯɭɭamiŋɡo̞]</t>
         </is>
       </c>
       <c r="D240" s="1" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="B243" s="1" t="inlineStr">
         <is>
-          <t>[takkotpomre] 甲虫 (动物)</t>
+          <t>[[t͈a̠k̚t͡ɕʌ̹ŋbʌ̹ɭɭe̞]] 甲虫 (动物)</t>
         </is>
       </c>
       <c r="C243" s="1" t="inlineStr">
         <is>
-          <t>takkotpomre</t>
+          <t>[t͈a̠k̚t͡ɕʌ̹ŋbʌ̹ɭɭe̞]</t>
         </is>
       </c>
       <c r="D243" s="1" t="inlineStr">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="B245" s="1" t="inlineStr">
         <is>
-          <t>[[nʌ̹ɡuɾi]] 浣熊 (动物)</t>
+          <t>[[nʌ̹ɡuɾi]] 貉；狸 (动物)</t>
         </is>
       </c>
       <c r="C245" s="1" t="inlineStr">
@@ -8253,7 +8253,7 @@
       </c>
       <c r="D245" s="1" t="inlineStr">
         <is>
-          <t>浣熊 (动物)</t>
+          <t>貉；狸 (动物)</t>
         </is>
       </c>
       <c r="E245" s="1" t="inlineStr">
@@ -8627,12 +8627,12 @@
       </c>
       <c r="B257" s="1" t="inlineStr">
         <is>
-          <t>[kintuke] 珍岛犬 (动物)</t>
+          <t>[[t͡ɕindo̞ɡe̞]] 珍岛犬 (动物)</t>
         </is>
       </c>
       <c r="C257" s="1" t="inlineStr">
         <is>
-          <t>kintuke</t>
+          <t>[t͡ɕindo̞ɡe̞]</t>
         </is>
       </c>
       <c r="D257" s="1" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="B262" s="1" t="inlineStr">
         <is>
-          <t>[[tʰʌ̹k̚p͈jʌ̹]] 下颚 (身体部位)</t>
+          <t>[[tʰʌ̹k̚p͈jʌ̹]] 颌骨 (身体部位)</t>
         </is>
       </c>
       <c r="C262" s="1" t="inlineStr">
@@ -8797,7 +8797,7 @@
       </c>
       <c r="D262" s="1" t="inlineStr">
         <is>
-          <t>下颚 (身体部位)</t>
+          <t>颌骨 (身体部位)</t>
         </is>
       </c>
       <c r="E262" s="1" t="inlineStr">
@@ -8883,12 +8883,12 @@
       </c>
       <c r="B265" s="1" t="inlineStr">
         <is>
-          <t>[kongkingunkarak] 食指 (身体部位)</t>
+          <t>[[kʌ̹md͡ʑisʰo̞nɡa̠ɾa̠k̚]] 食指 (身体部位)</t>
         </is>
       </c>
       <c r="C265" s="1" t="inlineStr">
         <is>
-          <t>kongkingunkarak</t>
+          <t>[kʌ̹md͡ʑisʰo̞nɡa̠ɾa̠k̚]</t>
         </is>
       </c>
       <c r="D265" s="1" t="inlineStr">
@@ -8915,12 +8915,12 @@
       </c>
       <c r="B266" s="1" t="inlineStr">
         <is>
-          <t>[kitkingunkarak] 中指 (身体部位)</t>
+          <t>[[t͡ɕuŋd͡ʑisʰo̞nɡa̠ɾa̠k̚]] 中指 (身体部位)</t>
         </is>
       </c>
       <c r="C266" s="1" t="inlineStr">
         <is>
-          <t>kitkingunkarak</t>
+          <t>[t͡ɕuŋd͡ʑisʰo̞nɡa̠ɾa̠k̚]</t>
         </is>
       </c>
       <c r="D266" s="1" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="B267" s="1" t="inlineStr">
         <is>
-          <t>[chyakkingunkarak] 无名指 (身体部位)</t>
+          <t>[[ja̠kd͡ʑisʰo̞nɡa̠ɾa̠k̚]] 无名指 (身体部位)</t>
         </is>
       </c>
       <c r="C267" s="1" t="inlineStr">
         <is>
-          <t>chyakkingunkarak</t>
+          <t>[ja̠kd͡ʑisʰo̞nɡa̠ɾa̠k̚]</t>
         </is>
       </c>
       <c r="D267" s="1" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="B274" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʌ̹ŋɡa̠ŋi]] 胫골 (身体部位)</t>
+          <t>[[t͡ɕʌ̹ŋɡa̠ŋi]] 小腿前部 (身体部位)</t>
         </is>
       </c>
       <c r="C274" s="1" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="D274" s="1" t="inlineStr">
         <is>
-          <t>胫골 (身体部位)</t>
+          <t>小腿前部 (身体部位)</t>
         </is>
       </c>
       <c r="E274" s="1" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="B288" s="1" t="inlineStr">
         <is>
-          <t>[kingun] 惯用手 (身体部位)</t>
+          <t>[[t͡ɕuson]] 惯用手 (身体部位)</t>
         </is>
       </c>
       <c r="C288" s="1" t="inlineStr">
         <is>
-          <t>kingun</t>
+          <t>[t͡ɕuson]</t>
         </is>
       </c>
       <c r="D288" s="1" t="inlineStr">
@@ -9843,17 +9843,17 @@
       </c>
       <c r="B295" s="1" t="inlineStr">
         <is>
-          <t>[kenchwkkimchy] 肌肉 (身体部位)</t>
+          <t>[[kɯɲjukt͡ɕiɾɯi]] 肌肉发达的 (身体部位)</t>
         </is>
       </c>
       <c r="C295" s="1" t="inlineStr">
         <is>
-          <t>kenchwkkimchy</t>
+          <t>[kɯɲjukt͡ɕiɾɯi]</t>
         </is>
       </c>
       <c r="D295" s="1" t="inlineStr">
         <is>
-          <t>肌肉 (身体部位)</t>
+          <t>肌肉发达的 (身体部位)</t>
         </is>
       </c>
       <c r="E295" s="1" t="inlineStr">
@@ -9875,17 +9875,17 @@
       </c>
       <c r="B296" s="1" t="inlineStr">
         <is>
-          <t>[chwchyonngot] 形态切换 (身体部位)</t>
+          <t>[[jujʌnsʌŋ]] 柔韧性 (身体部位)</t>
         </is>
       </c>
       <c r="C296" s="1" t="inlineStr">
         <is>
-          <t>chwchyonngot</t>
+          <t>[jujʌnsʌŋ]</t>
         </is>
       </c>
       <c r="D296" s="1" t="inlineStr">
         <is>
-          <t>形态切换 (身体部位)</t>
+          <t>柔韧性 (身体部位)</t>
         </is>
       </c>
       <c r="E296" s="1" t="inlineStr">
@@ -9939,12 +9939,12 @@
       </c>
       <c r="B298" s="1" t="inlineStr">
         <is>
-          <t>[chwikoim] 单眼皮 (명사)</t>
+          <t>[[weɡ͈ʌpʰul]] 单眼皮 (명사)</t>
         </is>
       </c>
       <c r="C298" s="1" t="inlineStr">
         <is>
-          <t>chwikoim</t>
+          <t>[weɡ͈ʌpʰul]</t>
         </is>
       </c>
       <c r="D298" s="1" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="B302" s="1" t="inlineStr">
         <is>
-          <t>[kinsamkat] 深红色 (颜色和形状)</t>
+          <t>[[t͡ɕinp͈aŋaŋ]] 深红色 (颜色和形状)</t>
         </is>
       </c>
       <c r="C302" s="1" t="inlineStr">
         <is>
-          <t>kinsamkat</t>
+          <t>[t͡ɕinp͈aŋaŋ]</t>
         </is>
       </c>
       <c r="D302" s="1" t="inlineStr">
@@ -10099,12 +10099,12 @@
       </c>
       <c r="B303" s="1" t="inlineStr">
         <is>
-          <t>[chyonarat] 浅蓝色 (颜色与形状)</t>
+          <t>[[jʌnpʰaɾaŋ]] 浅蓝色 (颜色与形状)</t>
         </is>
       </c>
       <c r="C303" s="1" t="inlineStr">
         <is>
-          <t>chyonarat</t>
+          <t>[jʌnpʰaɾaŋ]</t>
         </is>
       </c>
       <c r="D303" s="1" t="inlineStr">
@@ -10131,12 +10131,12 @@
       </c>
       <c r="B304" s="1" t="inlineStr">
         <is>
-          <t>[kinpuruk] 深绿色 (颜色与形状)</t>
+          <t>[[t͡ɕint͡ɕʰoɾok̚]] 深绿色 (颜色与形状)</t>
         </is>
       </c>
       <c r="C304" s="1" t="inlineStr">
         <is>
-          <t>kinpuruk</t>
+          <t>[t͡ɕint͡ɕʰoɾok̚]</t>
         </is>
       </c>
       <c r="D304" s="1" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="B305" s="1" t="inlineStr">
         <is>
-          <t>[chachipuri] 象牙白 (颜色与形状)</t>
+          <t>[[aiboɾi]] 象牙白 (颜色与形状)</t>
         </is>
       </c>
       <c r="C305" s="1" t="inlineStr">
         <is>
-          <t>chachipuri</t>
+          <t>[aiboɾi]</t>
         </is>
       </c>
       <c r="D305" s="1" t="inlineStr">
@@ -10195,12 +10195,12 @@
       </c>
       <c r="B306" s="1" t="inlineStr">
         <is>
-          <t>[heringngek] 奶油色 (颜色与形状)</t>
+          <t>[[kʰɯɾimsʰɛk̚]] 奶油色 (颜色与形状)</t>
         </is>
       </c>
       <c r="C306" s="1" t="inlineStr">
         <is>
-          <t>heringngek</t>
+          <t>[kʰɯɾimsʰɛk̚]</t>
         </is>
       </c>
       <c r="D306" s="1" t="inlineStr">
@@ -10227,12 +10227,12 @@
       </c>
       <c r="B307" s="1" t="inlineStr">
         <is>
-          <t>[ohingokngek] 绿松石色 (颜色与形状)</t>
+          <t>[[tʰʌkisʌks͈ɛk̚]] 绿松石色 (颜色与形状)</t>
         </is>
       </c>
       <c r="C307" s="1" t="inlineStr">
         <is>
-          <t>ohingokngek</t>
+          <t>[tʰʌkisʌks͈ɛk̚]</t>
         </is>
       </c>
       <c r="D307" s="1" t="inlineStr">
@@ -10259,12 +10259,12 @@
       </c>
       <c r="B308" s="1" t="inlineStr">
         <is>
-          <t>[kautngek] 品红色 (颜色与形状)</t>
+          <t>[[t͡ɕahoŋsʰɛk̚]] 品红色 (颜色与形状)</t>
         </is>
       </c>
       <c r="C308" s="1" t="inlineStr">
         <is>
-          <t>kautngek</t>
+          <t>[t͡ɕahoŋsʰɛk̚]</t>
         </is>
       </c>
       <c r="D308" s="1" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="B309" s="1" t="inlineStr">
         <is>
-          <t>[kepikutngek] 紫罗兰色 (颜色与形状)</t>
+          <t>[[t͡ɕebik͈ots͈ɛk̚]] 紫罗兰色 (颜色与形状)</t>
         </is>
       </c>
       <c r="C309" s="1" t="inlineStr">
         <is>
-          <t>kepikutngek</t>
+          <t>[t͡ɕebik͈ots͈ɛk̚]</t>
         </is>
       </c>
       <c r="D309" s="1" t="inlineStr">
@@ -10387,12 +10387,12 @@
       </c>
       <c r="B312" s="1" t="inlineStr">
         <is>
-          <t>[chumripengek] 橄榄绿 (颜色与形状)</t>
+          <t>[[olliks͈ɛk̚]] 橄榄绿 (颜色与形状)</t>
         </is>
       </c>
       <c r="C312" s="1" t="inlineStr">
         <is>
-          <t>chumripengek</t>
+          <t>[olliks͈ɛk̚]</t>
         </is>
       </c>
       <c r="D312" s="1" t="inlineStr">
@@ -10419,12 +10419,12 @@
       </c>
       <c r="B313" s="1" t="inlineStr">
         <is>
-          <t>[potrukngek] 蓝绿色 (颜色与形状)</t>
+          <t>[[t͡ɕʰʌŋɾoks͈ɛk̚]] 蓝绿色 (颜色与形状)</t>
         </is>
       </c>
       <c r="C313" s="1" t="inlineStr">
         <is>
-          <t>potrukngek</t>
+          <t>[t͡ɕʰʌŋɾoks͈ɛk̚]</t>
         </is>
       </c>
       <c r="D313" s="1" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="B314" s="1" t="inlineStr">
         <is>
-          <t>[katmingek] 玫瑰色 (颜色与形状)</t>
+          <t>[[t͡ɕaŋmisʰɛk̚]] 玫瑰色 (颜色与形状)</t>
         </is>
       </c>
       <c r="C314" s="1" t="inlineStr">
         <is>
-          <t>katmingek</t>
+          <t>[t͡ɕaŋmisʰɛk̚]</t>
         </is>
       </c>
       <c r="D314" s="1" t="inlineStr">
@@ -10483,12 +10483,12 @@
       </c>
       <c r="B315" s="1" t="inlineStr">
         <is>
-          <t>[rapentongek] 薰衣草色 (颜色与形状)</t>
+          <t>[[ɾabendʌsʰɛk̚]] 薰衣草色 (颜色与形状)</t>
         </is>
       </c>
       <c r="C315" s="1" t="inlineStr">
         <is>
-          <t>rapentongek</t>
+          <t>[ɾabendʌsʰɛk̚]</t>
         </is>
       </c>
       <c r="D315" s="1" t="inlineStr">
@@ -10515,12 +10515,12 @@
       </c>
       <c r="B316" s="1" t="inlineStr">
         <is>
-          <t>[pukngitchangek] 桃子色 (颜色与形状)</t>
+          <t>[[poks͈uŋasʰɛk̚]] 桃子色 (颜色与形状)</t>
         </is>
       </c>
       <c r="C316" s="1" t="inlineStr">
         <is>
-          <t>pukngitchangek</t>
+          <t>[poks͈uŋasʰɛk̚]</t>
         </is>
       </c>
       <c r="D316" s="1" t="inlineStr">
@@ -10547,12 +10547,12 @@
       </c>
       <c r="B317" s="1" t="inlineStr">
         <is>
-          <t>[rachimrakngek] 淡紫色 (颜色与形状)</t>
+          <t>[[ɾa.il.lak̚.sʰɛk̚]] 淡紫色 (颜色与形状)</t>
         </is>
       </c>
       <c r="C317" s="1" t="inlineStr">
         <is>
-          <t>rachimrakngek</t>
+          <t>[ɾa.il.lak̚.sʰɛk̚]</t>
         </is>
       </c>
       <c r="D317" s="1" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="B329" s="1" t="inlineStr">
         <is>
-          <t>[ngikik] 垂直 (颜色与形状)</t>
+          <t>[[su.dʑʌk̚]] 垂直 (颜色与形状)</t>
         </is>
       </c>
       <c r="C329" s="1" t="inlineStr">
         <is>
-          <t>ngikik</t>
+          <t>[su.dʑʌk̚]</t>
         </is>
       </c>
       <c r="D329" s="1" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="B330" s="1" t="inlineStr">
         <is>
-          <t>[tekakngon] 对角线 (颜色与形状)</t>
+          <t>[[tɛ.ɡak̚.s͈ʌn]] 对角线 (颜色与形状)</t>
         </is>
       </c>
       <c r="C330" s="1" t="inlineStr">
         <is>
-          <t>tekakngon</t>
+          <t>[tɛ.ɡak̚.s͈ʌn]</t>
         </is>
       </c>
       <c r="D330" s="1" t="inlineStr">
@@ -11027,12 +11027,12 @@
       </c>
       <c r="B332" s="1" t="inlineStr">
         <is>
-          <t>[sykukan] 尖锐 (颜色与形状)</t>
+          <t>[[p͈jo.dʑu.kʰan]] 尖锐 (颜色与形状)</t>
         </is>
       </c>
       <c r="C332" s="1" t="inlineStr">
         <is>
-          <t>sykukan</t>
+          <t>[p͈jo.dʑu.kʰan]</t>
         </is>
       </c>
       <c r="D332" s="1" t="inlineStr">
@@ -11059,17 +11059,17 @@
       </c>
       <c r="B333" s="1" t="inlineStr">
         <is>
-          <t>[tantanan] 实心 (颜色与形状)</t>
+          <t>[[ta.nːan]] 坚硬的 (颜色与形状)</t>
         </is>
       </c>
       <c r="C333" s="1" t="inlineStr">
         <is>
-          <t>tantanan</t>
+          <t>[ta.nːan]</t>
         </is>
       </c>
       <c r="D333" s="1" t="inlineStr">
         <is>
-          <t>实心 (颜色与形状)</t>
+          <t>坚硬的 (颜色与形状)</t>
         </is>
       </c>
       <c r="E333" s="1" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="B336" s="1" t="inlineStr">
         <is>
-          <t>[[mo̞sʰʌ̹ɾi]] 边缘 (颜色与形状)</t>
+          <t>[[mo̞sʰʌ̹ɾi]] 棱角 (颜色与形状)</t>
         </is>
       </c>
       <c r="C336" s="1" t="inlineStr">
@@ -11165,7 +11165,7 @@
       </c>
       <c r="D336" s="1" t="inlineStr">
         <is>
-          <t>边缘 (颜色与形状)</t>
+          <t>棱角 (颜色与形状)</t>
         </is>
       </c>
       <c r="E336" s="1" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="B340" s="1" t="inlineStr">
         <is>
-          <t>[kotean] 巨大的 (颜色与形状)</t>
+          <t>[[kʌ.dɛ.ɦan]] 巨大的 (颜色与形状)</t>
         </is>
       </c>
       <c r="C340" s="1" t="inlineStr">
         <is>
-          <t>kotean</t>
+          <t>[kʌ.dɛ.ɦan]</t>
         </is>
       </c>
       <c r="D340" s="1" t="inlineStr">
@@ -11315,12 +11315,12 @@
       </c>
       <c r="B341" s="1" t="inlineStr">
         <is>
-          <t>[peheminy] 格子 (颜色与形状)</t>
+          <t>[[tɕʰe.kʰɯ.mu.nɰi]] 格子 (颜色与形状)</t>
         </is>
       </c>
       <c r="C341" s="1" t="inlineStr">
         <is>
-          <t>peheminy</t>
+          <t>[tɕʰe.kʰɯ.mu.nɰi]</t>
         </is>
       </c>
       <c r="D341" s="1" t="inlineStr">
@@ -11347,12 +11347,12 @@
       </c>
       <c r="B342" s="1" t="inlineStr">
         <is>
-          <t>[kikekeke] 锯齿形 (颜色与形状)</t>
+          <t>[[tɕi.ɡɯ.tɕɛ.ɡɯ]] 锯齿形 (颜色与形状)</t>
         </is>
       </c>
       <c r="C342" s="1" t="inlineStr">
         <is>
-          <t>kikekeke</t>
+          <t>[tɕi.ɡɯ.tɕɛ.ɡɯ]</t>
         </is>
       </c>
       <c r="D342" s="1" t="inlineStr">
@@ -11411,12 +11411,12 @@
       </c>
       <c r="B344" s="1" t="inlineStr">
         <is>
-          <t>[ngingnyon] 十年 (数字与时间)</t>
+          <t>[[ɕim.ɲʌn]] 十年 (数字与时间)</t>
         </is>
       </c>
       <c r="C344" s="1" t="inlineStr">
         <is>
-          <t>ngingnyon</t>
+          <t>[ɕim.ɲʌn]</t>
         </is>
       </c>
       <c r="D344" s="1" t="inlineStr">
@@ -11443,12 +11443,12 @@
       </c>
       <c r="B345" s="1" t="inlineStr">
         <is>
-          <t>[ngattangngonngetning] 校内辅导员 (校园生活)</t>
+          <t>[[saŋ.dam.sʰʌn.sʰɛŋ.nim]] 校内辅导员 (校园生活)</t>
         </is>
       </c>
       <c r="C345" s="1" t="inlineStr">
         <is>
-          <t>ngattangngonngetning</t>
+          <t>[saŋ.dam.sʰʌn.sʰɛŋ.nim]</t>
         </is>
       </c>
       <c r="D345" s="1" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="B349" s="1" t="inlineStr">
         <is>
-          <t>[tetngi] 排名 (学校生活)</t>
+          <t>[[tɯŋ.sʰu]] 排名 (学校生活)</t>
         </is>
       </c>
       <c r="C349" s="1" t="inlineStr">
         <is>
-          <t>tetngi</t>
+          <t>[tɯŋ.sʰu]</t>
         </is>
       </c>
       <c r="D349" s="1" t="inlineStr">
@@ -11667,12 +11667,12 @@
       </c>
       <c r="B352" s="1" t="inlineStr">
         <is>
-          <t>[mingimngim] 美术教室 (学校生活)</t>
+          <t>[[mi.sul.ɕil]] 美术教室 (学校生活)</t>
         </is>
       </c>
       <c r="C352" s="1" t="inlineStr">
         <is>
-          <t>mingimngim</t>
+          <t>[mi.sul.ɕil]</t>
         </is>
       </c>
       <c r="D352" s="1" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="B355" s="1" t="inlineStr">
         <is>
-          <t>[[ˈu(ː)ndo̞ŋβwe̞]] 实地考察日 (校园生活)</t>
+          <t>[[ˈu(ː)ndo̞ŋβwe̞]] 运动会 (校园生活)</t>
         </is>
       </c>
       <c r="C355" s="1" t="inlineStr">
@@ -11773,7 +11773,7 @@
       </c>
       <c r="D355" s="1" t="inlineStr">
         <is>
-          <t>实地考察日 (校园生活)</t>
+          <t>运动会 (校园生活)</t>
         </is>
       </c>
       <c r="E355" s="1" t="inlineStr">
@@ -11827,17 +11827,17 @@
       </c>
       <c r="B357" s="1" t="inlineStr">
         <is>
-          <t>[minwke] 文化祭 (校园生活)</t>
+          <t>[[mun.ɦwa.dʑe]] 文化节 (校园生活)</t>
         </is>
       </c>
       <c r="C357" s="1" t="inlineStr">
         <is>
-          <t>minwke</t>
+          <t>[mun.ɦwa.dʑe]</t>
         </is>
       </c>
       <c r="D357" s="1" t="inlineStr">
         <is>
-          <t>文化祭 (校园生活)</t>
+          <t>文化节 (校园生活)</t>
         </is>
       </c>
       <c r="E357" s="1" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="B359" s="1" t="inlineStr">
         <is>
-          <t>[orakkat] 权限单 (校园生活)</t>
+          <t>[[hʌ.ɾaŋ.tɕaŋ]] 权限单 (校园生活)</t>
         </is>
       </c>
       <c r="C359" s="1" t="inlineStr">
         <is>
-          <t>orakkat</t>
+          <t>[hʌ.ɾaŋ.tɕaŋ]</t>
         </is>
       </c>
       <c r="D359" s="1" t="inlineStr">
@@ -12051,17 +12051,17 @@
       </c>
       <c r="B364" s="1" t="inlineStr">
         <is>
-          <t>[kangengngim] · 自主学习 (校园生活)</t>
+          <t>[[tɕa.sɯp.s͈il]] 自习室 (校园生活)</t>
         </is>
       </c>
       <c r="C364" s="1" t="inlineStr">
         <is>
-          <t>kangengngim</t>
+          <t>[tɕa.sɯp.s͈il]</t>
         </is>
       </c>
       <c r="D364" s="1" t="inlineStr">
         <is>
-          <t>· 自主学习 (校园生活)</t>
+          <t>自习室 (校园生活)</t>
         </is>
       </c>
       <c r="E364" s="1" t="inlineStr">
@@ -12083,17 +12083,17 @@
       </c>
       <c r="B365" s="1" t="inlineStr">
         <is>
-          <t>[chomchopinen] 冰点的 (天气)</t>
+          <t>[[ʌ.ɾʌ.pun.nɯn]] 结冰的 (天气)</t>
         </is>
       </c>
       <c r="C365" s="1" t="inlineStr">
         <is>
-          <t>chomchopinen</t>
+          <t>[ʌ.ɾʌ.pun.nɯn]</t>
         </is>
       </c>
       <c r="D365" s="1" t="inlineStr">
         <is>
-          <t>冰点的 (天气)</t>
+          <t>结冰的 (天气)</t>
         </is>
       </c>
       <c r="E365" s="1" t="inlineStr">
@@ -12115,12 +12115,12 @@
       </c>
       <c r="B366" s="1" t="inlineStr">
         <is>
-          <t>[chunwan] 温和 (天气)</t>
+          <t>[[onβwaɦan]] 温和 (天气)</t>
         </is>
       </c>
       <c r="C366" s="1" t="inlineStr">
         <is>
-          <t>chunwan</t>
+          <t>[onβwaɦan]</t>
         </is>
       </c>
       <c r="D366" s="1" t="inlineStr">
@@ -12307,12 +12307,12 @@
       </c>
       <c r="B372" s="1" t="inlineStr">
         <is>
-          <t>[monkiukit] 沙尘暴 (天气)</t>
+          <t>[[mʌn.dʑi.pʰok̚.puŋ]] 沙尘暴 (天气)</t>
         </is>
       </c>
       <c r="C372" s="1" t="inlineStr">
         <is>
-          <t>monkiukit</t>
+          <t>[mʌn.dʑi.pʰok̚.puŋ]</t>
         </is>
       </c>
       <c r="D372" s="1" t="inlineStr">
@@ -12371,12 +12371,12 @@
       </c>
       <c r="B374" s="1" t="inlineStr">
         <is>
-          <t>[konki] 干季 (天气)</t>
+          <t>[[kʌŋ.k͈i]] 干季 (天气)</t>
         </is>
       </c>
       <c r="C374" s="1" t="inlineStr">
         <is>
-          <t>konki</t>
+          <t>[kʌŋ.k͈i]</t>
         </is>
       </c>
       <c r="D374" s="1" t="inlineStr">
@@ -12403,12 +12403,12 @@
       </c>
       <c r="B375" s="1" t="inlineStr">
         <is>
-          <t>[kutkikim] 空气品质 (天气)</t>
+          <t>[[koŋɡidʑil]] 空气品质 (天气)</t>
         </is>
       </c>
       <c r="C375" s="1" t="inlineStr">
         <is>
-          <t>kutkikim</t>
+          <t>[koŋɡidʑil]</t>
         </is>
       </c>
       <c r="D375" s="1" t="inlineStr">
@@ -12499,12 +12499,12 @@
       </c>
       <c r="B378" s="1" t="inlineStr">
         <is>
-          <t>[ityat] 风向 (天气)</t>
+          <t>[[pʰuŋçaŋ]] 风向 (天气)</t>
         </is>
       </c>
       <c r="C378" s="1" t="inlineStr">
         <is>
-          <t>ityat</t>
+          <t>[pʰuŋçaŋ]</t>
         </is>
       </c>
       <c r="D378" s="1" t="inlineStr">
@@ -12563,7 +12563,7 @@
       </c>
       <c r="B380" s="1" t="inlineStr">
         <is>
-          <t>[[ˈtɛ(ː)pʰisʰo̞]] 房屋 (天气)</t>
+          <t>[[ˈtɛ(ː)pʰisʰo̞]] 避难所 (天气)</t>
         </is>
       </c>
       <c r="C380" s="1" t="inlineStr">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="D380" s="1" t="inlineStr">
         <is>
-          <t>房屋 (天气)</t>
+          <t>避难所 (天气)</t>
         </is>
       </c>
       <c r="E380" s="1" t="inlineStr">
@@ -12627,17 +12627,17 @@
       </c>
       <c r="B382" s="1" t="inlineStr">
         <is>
-          <t>[chimkwtwngat] 晒斑 (天气)</t>
+          <t>[[ilkwɛŋɦʷasäŋ]] 晒伤 (天气)</t>
         </is>
       </c>
       <c r="C382" s="1" t="inlineStr">
         <is>
-          <t>chimkwtwngat</t>
+          <t>[ilkwɛŋɦʷasäŋ]</t>
         </is>
       </c>
       <c r="D382" s="1" t="inlineStr">
         <is>
-          <t>晒斑 (天气)</t>
+          <t>晒伤 (天气)</t>
         </is>
       </c>
       <c r="E382" s="1" t="inlineStr">
@@ -12691,12 +12691,12 @@
       </c>
       <c r="B384" s="1" t="inlineStr">
         <is>
-          <t>[amngi] 脱水 (天气)</t>
+          <t>[[tʰals͈u]] 脱水 (天气)</t>
         </is>
       </c>
       <c r="C384" s="1" t="inlineStr">
         <is>
-          <t>amngi</t>
+          <t>[tʰals͈u]</t>
         </is>
       </c>
       <c r="D384" s="1" t="inlineStr">
@@ -12723,12 +12723,12 @@
       </c>
       <c r="B385" s="1" t="inlineStr">
         <is>
-          <t>[sichyon] 朦胧的 (天气)</t>
+          <t>[[p͈ujʌn]] 朦胧的 (天气)</t>
         </is>
       </c>
       <c r="C385" s="1" t="inlineStr">
         <is>
-          <t>sichyon</t>
+          <t>[p͈ujʌn]</t>
         </is>
       </c>
       <c r="D385" s="1" t="inlineStr">
@@ -12787,17 +12787,17 @@
       </c>
       <c r="B387" s="1" t="inlineStr">
         <is>
-          <t>[pemrechiko] 伐刀者 (服饰)</t>
+          <t>[[p͈ɯlleːdʑʌ]] 西装外套 (服饰)</t>
         </is>
       </c>
       <c r="C387" s="1" t="inlineStr">
         <is>
-          <t>pemrechiko</t>
+          <t>[p͈ɯlleːdʑʌ]</t>
         </is>
       </c>
       <c r="D387" s="1" t="inlineStr">
         <is>
-          <t>伐刀者 (服饰)</t>
+          <t>西装外套 (服饰)</t>
         </is>
       </c>
       <c r="E387" s="1" t="inlineStr">
@@ -12819,12 +12819,12 @@
       </c>
       <c r="B388" s="1" t="inlineStr">
         <is>
-          <t>[etit] 羽绒夹克 (服饰)</t>
+          <t>[[pʰɛːdiŋ]] 羽绒夹克 (服饰)</t>
         </is>
       </c>
       <c r="C388" s="1" t="inlineStr">
         <is>
-          <t>etit</t>
+          <t>[pʰɛːdiŋ]</t>
         </is>
       </c>
       <c r="D388" s="1" t="inlineStr">
@@ -12883,12 +12883,12 @@
       </c>
       <c r="B390" s="1" t="inlineStr">
         <is>
-          <t>[oemnek] 高领衫 (服饰)</t>
+          <t>[[tʰʌt͈ɯlnek̚]] 高领衫 (服饰)</t>
         </is>
       </c>
       <c r="C390" s="1" t="inlineStr">
         <is>
-          <t>oemnek</t>
+          <t>[tʰʌt͈ɯlnek̚]</t>
         </is>
       </c>
       <c r="D390" s="1" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="B391" s="1" t="inlineStr">
         <is>
-          <t>[umrungyope] Polo衫；翻领马球衫 (명사)</t>
+          <t>[[pʰolloɕʰʌt͈ɕʰɯ]] Polo衫；翻领马球衫 (명사)</t>
         </is>
       </c>
       <c r="C391" s="1" t="inlineStr">
         <is>
-          <t>umrungyope</t>
+          <t>[pʰolloɕʰʌt͈ɕʰɯ]</t>
         </is>
       </c>
       <c r="D391" s="1" t="inlineStr">
@@ -12947,12 +12947,12 @@
       </c>
       <c r="B392" s="1" t="inlineStr">
         <is>
-          <t>[terengengyope] 正装衬衫 (服饰)</t>
+          <t>[[dɯleːsɯɕʰʌt͈ɕʰɯ]] 正装衬衫 (服饰)</t>
         </is>
       </c>
       <c r="C392" s="1" t="inlineStr">
         <is>
-          <t>terengengyope</t>
+          <t>[dɯleːsɯɕʰʌt͈ɕʰɯ]</t>
         </is>
       </c>
       <c r="D392" s="1" t="inlineStr">
@@ -13043,12 +13043,12 @@
       </c>
       <c r="B395" s="1" t="inlineStr">
         <is>
-          <t>[achipe] 裤袜 (服饰)</t>
+          <t>[[tʰait͈ɕʰɯ]] 裤袜 (服饰)</t>
         </is>
       </c>
       <c r="C395" s="1" t="inlineStr">
         <is>
-          <t>achipe</t>
+          <t>[tʰait͈ɕʰɯ]</t>
         </is>
       </c>
       <c r="D395" s="1" t="inlineStr">
@@ -13107,12 +13107,12 @@
       </c>
       <c r="B397" s="1" t="inlineStr">
         <is>
-          <t>[ruo] 乐福鞋 (服饰)</t>
+          <t>[[lo̞pʰʌ̹]] 乐福鞋 (服饰)</t>
         </is>
       </c>
       <c r="C397" s="1" t="inlineStr">
         <is>
-          <t>ruo</t>
+          <t>[lo̞pʰʌ̹]</t>
         </is>
       </c>
       <c r="D397" s="1" t="inlineStr">
@@ -13139,12 +13139,12 @@
       </c>
       <c r="B398" s="1" t="inlineStr">
         <is>
-          <t>[chukngeute] 牛津鞋 (服饰)</t>
+          <t>[[o̞ksʰɯpʰo̞tʰɯ]] 牛津鞋 (服饰)</t>
         </is>
       </c>
       <c r="C398" s="1" t="inlineStr">
         <is>
-          <t>chukngeute</t>
+          <t>[o̞ksʰɯpʰo̞tʰɯ]</t>
         </is>
       </c>
       <c r="D398" s="1" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="B399" s="1" t="inlineStr">
         <is>
-          <t>[potchorikatkang] 连指手套 (服饰)</t>
+          <t>[[bʌ̹ŋʌ̹ɾidʑa̠ŋɡa̠p̚]] 连指手套 (服饰)</t>
         </is>
       </c>
       <c r="C399" s="1" t="inlineStr">
         <is>
-          <t>potchorikatkang</t>
+          <t>[bʌ̹ŋʌ̹ɾidʑa̠ŋɡa̠p̚]</t>
         </is>
       </c>
       <c r="D399" s="1" t="inlineStr">
@@ -13363,12 +13363,12 @@
       </c>
       <c r="B405" s="1" t="inlineStr">
         <is>
-          <t>[napinekachi] 领结 (服饰)</t>
+          <t>[[na̠binɛɡtʰa̠i]] 领结 (服饰)</t>
         </is>
       </c>
       <c r="C405" s="1" t="inlineStr">
         <is>
-          <t>napinekachi</t>
+          <t>[na̠binɛɡtʰa̠i]</t>
         </is>
       </c>
       <c r="D405" s="1" t="inlineStr">
@@ -13459,12 +13459,12 @@
       </c>
       <c r="B408" s="1" t="inlineStr">
         <is>
-          <t>[echochekngengori] 发饰 (服饰)</t>
+          <t>[[he̞ʌ̹ɛksʰe̞sʰʌ̹ɾi]] 发饰 (服饰)</t>
         </is>
       </c>
       <c r="C408" s="1" t="inlineStr">
         <is>
-          <t>echochekngengori</t>
+          <t>[he̞ʌ̹ɛksʰe̞sʰʌ̹ɾi]</t>
         </is>
       </c>
       <c r="D408" s="1" t="inlineStr">
@@ -13523,12 +13523,12 @@
       </c>
       <c r="B410" s="1" t="inlineStr">
         <is>
-          <t>[etepente] 头带 (服饰)</t>
+          <t>[[he̞dɯbɛntʰɯ]] 头带 (服饰)</t>
         </is>
       </c>
       <c r="C410" s="1" t="inlineStr">
         <is>
-          <t>etepente</t>
+          <t>[he̞dɯbɛntʰɯ]</t>
         </is>
       </c>
       <c r="D410" s="1" t="inlineStr">
@@ -13651,12 +13651,12 @@
       </c>
       <c r="B414" s="1" t="inlineStr">
         <is>
-          <t>[kingchecho] 健身服 (服饰)</t>
+          <t>[[dʑimwʌ̹]] 健身服 (服饰)</t>
         </is>
       </c>
       <c r="C414" s="1" t="inlineStr">
         <is>
-          <t>kingchecho</t>
+          <t>[dʑimwʌ̹]</t>
         </is>
       </c>
       <c r="D414" s="1" t="inlineStr">
@@ -13683,12 +13683,12 @@
       </c>
       <c r="B415" s="1" t="inlineStr">
         <is>
-          <t>[chykaenpe] 瑜珈裤 (服饰)</t>
+          <t>[[jo̞ɡapʰɛnt͡ɕʰɯ]] 瑜珈裤 (服饰)</t>
         </is>
       </c>
       <c r="C415" s="1" t="inlineStr">
         <is>
-          <t>chykaenpe</t>
+          <t>[jo̞ɡapʰɛnt͡ɕʰɯ]</t>
         </is>
       </c>
       <c r="D415" s="1" t="inlineStr">
@@ -13715,17 +13715,17 @@
       </c>
       <c r="B416" s="1" t="inlineStr">
         <is>
-          <t>[konutchyngat] 韩服 (服饰)</t>
+          <t>[[dʑʌ̹ntʰo̞ŋɯːsa̠ŋ]] 传统服饰 (服饰)</t>
         </is>
       </c>
       <c r="C416" s="1" t="inlineStr">
         <is>
-          <t>konutchyngat</t>
+          <t>[dʑʌ̹ntʰo̞ŋɯːsa̠ŋ]</t>
         </is>
       </c>
       <c r="D416" s="1" t="inlineStr">
         <is>
-          <t>韩服 (服饰)</t>
+          <t>传统服饰 (服饰)</t>
         </is>
       </c>
       <c r="E416" s="1" t="inlineStr">
@@ -13779,12 +13779,12 @@
       </c>
       <c r="B418" s="1" t="inlineStr">
         <is>
-          <t>[rinnen] 亚麻 (服装)</t>
+          <t>[[linne̞n]] 亚麻 (服装)</t>
         </is>
       </c>
       <c r="C418" s="1" t="inlineStr">
         <is>
-          <t>rinnen</t>
+          <t>[linne̞n]</t>
         </is>
       </c>
       <c r="D418" s="1" t="inlineStr">
@@ -13811,12 +13811,12 @@
       </c>
       <c r="B419" s="1" t="inlineStr">
         <is>
-          <t>[ngimhe] 丝绸 (服装)</t>
+          <t>[[ɕilkʰɯ]] 丝绸 (服装)</t>
         </is>
       </c>
       <c r="C419" s="1" t="inlineStr">
         <is>
-          <t>ngimhe</t>
+          <t>[ɕilkʰɯ]</t>
         </is>
       </c>
       <c r="D419" s="1" t="inlineStr">
@@ -13907,12 +13907,12 @@
       </c>
       <c r="B422" s="1" t="inlineStr">
         <is>
-          <t>[iit] 拟合 (服装)</t>
+          <t>[[pʰitʰiŋ]] 拟合 (服装)</t>
         </is>
       </c>
       <c r="C422" s="1" t="inlineStr">
         <is>
-          <t>iit</t>
+          <t>[pʰitʰiŋ]</t>
         </is>
       </c>
       <c r="D422" s="1" t="inlineStr">
@@ -13971,12 +13971,12 @@
       </c>
       <c r="B424" s="1" t="inlineStr">
         <is>
-          <t>[terachihemrinit] 干洗 (服装)</t>
+          <t>[[tɯɾa̠ikʰɯliniŋ]] 干洗 (服装)</t>
         </is>
       </c>
       <c r="C424" s="1" t="inlineStr">
         <is>
-          <t>terachihemrinit</t>
+          <t>[tɯɾa̠ikʰɯliniŋ]</t>
         </is>
       </c>
       <c r="D424" s="1" t="inlineStr">
@@ -14003,12 +14003,12 @@
       </c>
       <c r="B425" s="1" t="inlineStr">
         <is>
-          <t>[ngunngeak] 手洗 (服装)</t>
+          <t>[[so̞nsʰe̞tʰa̠k̚]] 手洗 (服装)</t>
         </is>
       </c>
       <c r="C425" s="1" t="inlineStr">
         <is>
-          <t>ngunngeak</t>
+          <t>[so̞nsʰe̞tʰa̠k̚]</t>
         </is>
       </c>
       <c r="D425" s="1" t="inlineStr">
@@ -14163,12 +14163,12 @@
       </c>
       <c r="B430" s="1" t="inlineStr">
         <is>
-          <t>[kewi] 重逢 (韩剧用语)</t>
+          <t>[[t͡ɕɛɦwe]] 重逢 (韩剧用语)</t>
         </is>
       </c>
       <c r="C430" s="1" t="inlineStr">
         <is>
-          <t>kewi</t>
+          <t>[t͡ɕɛɦwe]</t>
         </is>
       </c>
       <c r="D430" s="1" t="inlineStr">
@@ -14323,12 +14323,12 @@
       </c>
       <c r="B435" s="1" t="inlineStr">
         <is>
-          <t>[hemrieetko] 悬念结尾 (韩剧用语)</t>
+          <t>[[kʰɯɭɭipʰɯɦɛŋɡʌ̹]] 悬念结尾 (韩剧用语)</t>
         </is>
       </c>
       <c r="C435" s="1" t="inlineStr">
         <is>
-          <t>hemrieetko</t>
+          <t>[kʰɯɭɭipʰɯɦɛŋɡʌ̹]</t>
         </is>
       </c>
       <c r="D435" s="1" t="inlineStr">
@@ -14387,12 +14387,12 @@
       </c>
       <c r="B437" s="1" t="inlineStr">
         <is>
-          <t>[mumchapuki] 追剧 (韩剧用语)</t>
+          <t>[[mo̞ɾa̠bo̞ɡi]] 追剧 (韩剧用语)</t>
         </is>
       </c>
       <c r="C437" s="1" t="inlineStr">
         <is>
-          <t>mumchapuki</t>
+          <t>[mo̞ɾa̠bo̞ɡi]</t>
         </is>
       </c>
       <c r="D437" s="1" t="inlineStr">
@@ -14451,12 +14451,12 @@
       </c>
       <c r="B439" s="1" t="inlineStr">
         <is>
-          <t>[enkom] 女粉丝 (韩剧用语)</t>
+          <t>[[pʰɛɡʌ̹ɭ]] 女粉丝 (韩剧用语)</t>
         </is>
       </c>
       <c r="C439" s="1" t="inlineStr">
         <is>
-          <t>enkom</t>
+          <t>[pʰɛɡʌ̹ɭ]</t>
         </is>
       </c>
       <c r="D439" s="1" t="inlineStr">
@@ -14483,12 +14483,12 @@
       </c>
       <c r="B440" s="1" t="inlineStr">
         <is>
-          <t>[enpuchi] 男粉丝 (韩剧用语)</t>
+          <t>[[pʰɛbo̞i]] 男粉丝 (韩剧用语)</t>
         </is>
       </c>
       <c r="C440" s="1" t="inlineStr">
         <is>
-          <t>enpuchi</t>
+          <t>[pʰɛbo̞i]</t>
         </is>
       </c>
       <c r="D440" s="1" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="B441" s="1" t="inlineStr">
         <is>
-          <t>[piachinte] 幕后花絮 (韩剧用语)</t>
+          <t>[[piɦaindɯ]] 幕后花絮 (韩剧用语)</t>
         </is>
       </c>
       <c r="C441" s="1" t="inlineStr">
         <is>
-          <t>piachinte</t>
+          <t>[piɦaindɯ]</t>
         </is>
       </c>
       <c r="D441" s="1" t="inlineStr">
@@ -14579,12 +14579,12 @@
       </c>
       <c r="B443" s="1" t="inlineStr">
         <is>
-          <t>[yontekek] 现代剧 (韩剧用语)</t>
+          <t>[[çʌ̹ndɛɡɯk̚]] 现代剧 (韩剧用语)</t>
         </is>
       </c>
       <c r="C443" s="1" t="inlineStr">
         <is>
-          <t>yontekek</t>
+          <t>[çʌ̹ndɛɡɯk̚]</t>
         </is>
       </c>
       <c r="D443" s="1" t="inlineStr">
@@ -14707,7 +14707,7 @@
       </c>
       <c r="B447" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʰo̞nɯŋɲʌ̹k̚]] 超自然力量 (韩剧表达)</t>
+          <t>[[t͡ɕʰo̞nɯŋɲʌ̹k̚]] 超能力 (韩剧表达)</t>
         </is>
       </c>
       <c r="C447" s="1" t="inlineStr">
@@ -14717,7 +14717,7 @@
       </c>
       <c r="D447" s="1" t="inlineStr">
         <is>
-          <t>超自然力量 (韩剧表达)</t>
+          <t>超能力 (韩剧表达)</t>
         </is>
       </c>
       <c r="E447" s="1" t="inlineStr">
@@ -14739,12 +14739,12 @@
       </c>
       <c r="B448" s="1" t="inlineStr">
         <is>
-          <t>[ngwekum] 锁骨 (身体部位)</t>
+          <t>[[sʰwɛɡo̞ɭ]] 锁骨 (身体部位)</t>
         </is>
       </c>
       <c r="C448" s="1" t="inlineStr">
         <is>
-          <t>ngwekum</t>
+          <t>[sʰwɛɡo̞ɭ]</t>
         </is>
       </c>
       <c r="D448" s="1" t="inlineStr">
@@ -14803,17 +14803,17 @@
       </c>
       <c r="B450" s="1" t="inlineStr">
         <is>
-          <t>[pitankim] 滑路 (天气)</t>
+          <t>[[piŋpʰa̠ŋiɭ]] 结冰的路面 (天气)</t>
         </is>
       </c>
       <c r="C450" s="1" t="inlineStr">
         <is>
-          <t>pitankim</t>
+          <t>[piŋpʰa̠ŋiɭ]</t>
         </is>
       </c>
       <c r="D450" s="1" t="inlineStr">
         <is>
-          <t>滑路 (天气)</t>
+          <t>结冰的路面 (天气)</t>
         </is>
       </c>
       <c r="E450" s="1" t="inlineStr">
@@ -14867,12 +14867,12 @@
       </c>
       <c r="B452" s="1" t="inlineStr">
         <is>
-          <t>[chyomtechya] 热带之夜 (天气)</t>
+          <t>[[jʌ̹ldɛja̠]] 热带之夜 (天气)</t>
         </is>
       </c>
       <c r="C452" s="1" t="inlineStr">
         <is>
-          <t>chyomtechya</t>
+          <t>[jʌ̹ldɛja̠]</t>
         </is>
       </c>
       <c r="D452" s="1" t="inlineStr">
@@ -14931,12 +14931,12 @@
       </c>
       <c r="B454" s="1" t="inlineStr">
         <is>
-          <t>[tumit] 阵风 (天气)</t>
+          <t>[[to̞ɭpʰuŋ]] 阵风 (天气)</t>
         </is>
       </c>
       <c r="C454" s="1" t="inlineStr">
         <is>
-          <t>tumit</t>
+          <t>[to̞ɭpʰuŋ]</t>
         </is>
       </c>
       <c r="D454" s="1" t="inlineStr">
@@ -14963,12 +14963,12 @@
       </c>
       <c r="B455" s="1" t="inlineStr">
         <is>
-          <t>[pyotka] 病假 (校园生活)</t>
+          <t>[[pjʌ̹ŋɡa̠]] 病假 (校园生活)</t>
         </is>
       </c>
       <c r="C455" s="1" t="inlineStr">
         <is>
-          <t>pyotka</t>
+          <t>[pjʌ̹ŋɡa̠]</t>
         </is>
       </c>
       <c r="D455" s="1" t="inlineStr">
@@ -14995,17 +14995,17 @@
       </c>
       <c r="B456" s="1" t="inlineStr">
         <is>
-          <t>[konaknget] 转学学生 (校园生活)</t>
+          <t>[[tɕʌnɦɛks͈ɛŋ]] 转学生 (校园生活)</t>
         </is>
       </c>
       <c r="C456" s="1" t="inlineStr">
         <is>
-          <t>konaknget</t>
+          <t>[tɕʌnɦɛks͈ɛŋ]</t>
         </is>
       </c>
       <c r="D456" s="1" t="inlineStr">
         <is>
-          <t>转学学生 (校园生活)</t>
+          <t>转学生 (校园生活)</t>
         </is>
       </c>
       <c r="E456" s="1" t="inlineStr">
@@ -15027,7 +15027,7 @@
       </c>
       <c r="B457" s="1" t="inlineStr">
         <is>
-          <t>[[kʰʌ̹npʰʌ̹ɾʌ̹nsʰɯ]] 多人会议 (商业)</t>
+          <t>[[kʰʌ̹npʰʌ̹ɾʌ̹nsʰɯ]] 会议；研讨会 (商业)</t>
         </is>
       </c>
       <c r="C457" s="1" t="inlineStr">
@@ -15037,7 +15037,7 @@
       </c>
       <c r="D457" s="1" t="inlineStr">
         <is>
-          <t>多人会议 (商业)</t>
+          <t>会议；研讨会 (商业)</t>
         </is>
       </c>
       <c r="E457" s="1" t="inlineStr">
@@ -15187,12 +15187,12 @@
       </c>
       <c r="B462" s="1" t="inlineStr">
         <is>
-          <t>[piponchin] 推荐人 (商业)</t>
+          <t>[[tɕʰutɕʰʌnin]] 推荐人 (商业)</t>
         </is>
       </c>
       <c r="C462" s="1" t="inlineStr">
         <is>
-          <t>piponchin</t>
+          <t>[tɕʰutɕʰʌnin]</t>
         </is>
       </c>
       <c r="D462" s="1" t="inlineStr">
@@ -15219,12 +15219,12 @@
       </c>
       <c r="B463" s="1" t="inlineStr">
         <is>
-          <t>[ngingengkikan] 试用期 (商业)</t>
+          <t>[[sɯs͈ip̚kigaŋ]] 试用期 (商业)</t>
         </is>
       </c>
       <c r="C463" s="1" t="inlineStr">
         <is>
-          <t>ngingengkikan</t>
+          <t>[sɯs͈ip̚kigaŋ]</t>
         </is>
       </c>
       <c r="D463" s="1" t="inlineStr">
@@ -15315,12 +15315,12 @@
       </c>
       <c r="B466" s="1" t="inlineStr">
         <is>
-          <t>[pimnganwka] 产假 (商业)</t>
+          <t>[[tɕʰuls͈ançjuga]] 产假 (商业)</t>
         </is>
       </c>
       <c r="C466" s="1" t="inlineStr">
         <is>
-          <t>pimnganwka</t>
+          <t>[tɕʰuls͈ançjuga]</t>
         </is>
       </c>
       <c r="D466" s="1" t="inlineStr">
@@ -15347,17 +15347,17 @@
       </c>
       <c r="B467" s="1" t="inlineStr">
         <is>
-          <t>[chwkchawkik] 陪产假 (商业)</t>
+          <t>[[jugatɕʰudʑik̚]] 育儿假 (商业)</t>
         </is>
       </c>
       <c r="C467" s="1" t="inlineStr">
         <is>
-          <t>chwkchawkik</t>
+          <t>[jugatɕʰudʑik̚]</t>
         </is>
       </c>
       <c r="D467" s="1" t="inlineStr">
         <is>
-          <t>陪产假 (商业)</t>
+          <t>育儿假 (商业)</t>
         </is>
       </c>
       <c r="E467" s="1" t="inlineStr">
@@ -15603,12 +15603,12 @@
       </c>
       <c r="B475" s="1" t="inlineStr">
         <is>
-          <t>[erenpachike] 加盟 (商业)</t>
+          <t>[[p͈ɯlentɕʰait͈ɕʰɯ]] 加盟 (商业)</t>
         </is>
       </c>
       <c r="C475" s="1" t="inlineStr">
         <is>
-          <t>erenpachike</t>
+          <t>[p͈ɯlentɕʰait͈ɕʰɯ]</t>
         </is>
       </c>
       <c r="D475" s="1" t="inlineStr">
@@ -15667,12 +15667,12 @@
       </c>
       <c r="B477" s="1" t="inlineStr">
         <is>
-          <t>[kutkengchongpe] 供应商 (商业)</t>
+          <t>[[koŋɡɯbʌpt͈ɕʰɛ]] 供应商 (商业)</t>
         </is>
       </c>
       <c r="C477" s="1" t="inlineStr">
         <is>
-          <t>kutkengchongpe</t>
+          <t>[koŋɡɯbʌpt͈ɕʰɛ]</t>
         </is>
       </c>
       <c r="D477" s="1" t="inlineStr">
@@ -15699,7 +15699,7 @@
       </c>
       <c r="B478" s="1" t="inlineStr">
         <is>
-          <t>[[pʰa̠nmɛd͡ʑa̠]] 供应商 (商业)</t>
+          <t>[[pʰa̠nmɛd͡ʑa̠]] 卖家 (商业)</t>
         </is>
       </c>
       <c r="C478" s="1" t="inlineStr">
@@ -15709,7 +15709,7 @@
       </c>
       <c r="D478" s="1" t="inlineStr">
         <is>
-          <t>供应商 (商业)</t>
+          <t>卖家 (商业)</t>
         </is>
       </c>
       <c r="E478" s="1" t="inlineStr">
@@ -15731,12 +15731,12 @@
       </c>
       <c r="B479" s="1" t="inlineStr">
         <is>
-          <t>[aenonging] 合作伙伴关系 (商业)</t>
+          <t>[[pʰat͈ɯnʌɕʰip̚]] 合作伙伴关系 (商业)</t>
         </is>
       </c>
       <c r="C479" s="1" t="inlineStr">
         <is>
-          <t>aenonging</t>
+          <t>[pʰat͈ɯnʌɕʰip̚]</t>
         </is>
       </c>
       <c r="D479" s="1" t="inlineStr">
@@ -15795,12 +15795,12 @@
       </c>
       <c r="B481" s="1" t="inlineStr">
         <is>
-          <t>[kyotketnga] 竞争者 (商业)</t>
+          <t>[[kjaŋdʑɛŋsa]] 竞争者 (商业)</t>
         </is>
       </c>
       <c r="C481" s="1" t="inlineStr">
         <is>
-          <t>kyotketnga</t>
+          <t>[kjaŋdʑɛŋsa]</t>
         </is>
       </c>
       <c r="D481" s="1" t="inlineStr">
@@ -15827,12 +15827,12 @@
       </c>
       <c r="B482" s="1" t="inlineStr">
         <is>
-          <t>[piakikchen] 下属 (商业)</t>
+          <t>[[puɦatɕigwʌn]] 下属 (商业)</t>
         </is>
       </c>
       <c r="C482" s="1" t="inlineStr">
         <is>
-          <t>piakikchen</t>
+          <t>[puɦatɕigwʌn]</t>
         </is>
       </c>
       <c r="D482" s="1" t="inlineStr">
@@ -15859,12 +15859,12 @@
       </c>
       <c r="B483" s="1" t="inlineStr">
         <is>
-          <t>[ponchachit] 职业倦怠 (商业)</t>
+          <t>[[pʌɾa.ut̚]] 职业倦怠 (商业)</t>
         </is>
       </c>
       <c r="C483" s="1" t="inlineStr">
         <is>
-          <t>ponchachit</t>
+          <t>[pʌɾa.ut̚]</t>
         </is>
       </c>
       <c r="D483" s="1" t="inlineStr">
@@ -15891,12 +15891,12 @@
       </c>
       <c r="B484" s="1" t="inlineStr">
         <is>
-          <t>[menurit] 导师指导 (商业)</t>
+          <t>[[mentoɾiŋ]] 导师指导 (商业)</t>
         </is>
       </c>
       <c r="C484" s="1" t="inlineStr">
         <is>
-          <t>menurit</t>
+          <t>[mentoɾiŋ]</t>
         </is>
       </c>
       <c r="D484" s="1" t="inlineStr">
@@ -15987,12 +15987,12 @@
       </c>
       <c r="B487" s="1" t="inlineStr">
         <is>
-          <t>[rungeeata] 烘烤 (烹饪)</t>
+          <t>[[ɾo̞sʰɨtʰa̠da̠]] 烘烤 (烹饪)</t>
         </is>
       </c>
       <c r="C487" s="1" t="inlineStr">
         <is>
-          <t>rungeeata</t>
+          <t>[ɾo̞sʰɨtʰa̠da̠]</t>
         </is>
       </c>
       <c r="D487" s="1" t="inlineStr">
@@ -16083,7 +16083,7 @@
       </c>
       <c r="B490" s="1" t="inlineStr">
         <is>
-          <t>[[tudɯɾida̠]] 元 (烹饪)</t>
+          <t>[[tudɯɾida̠]] 拍打 (烹饪)</t>
         </is>
       </c>
       <c r="C490" s="1" t="inlineStr">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="D490" s="1" t="inlineStr">
         <is>
-          <t>元 (烹饪)</t>
+          <t>拍打 (烹饪)</t>
         </is>
       </c>
       <c r="E490" s="1" t="inlineStr">
@@ -16115,12 +16115,12 @@
       </c>
       <c r="B491" s="1" t="inlineStr">
         <is>
-          <t>[piteta] 揉~ (烹饪)</t>
+          <t>[[t͡ɕʰidɛda̠]] 揉~ (烹饪)</t>
         </is>
       </c>
       <c r="C491" s="1" t="inlineStr">
         <is>
-          <t>piteta</t>
+          <t>[t͡ɕʰidɛda̠]</t>
         </is>
       </c>
       <c r="D491" s="1" t="inlineStr">
@@ -16147,7 +16147,7 @@
       </c>
       <c r="B492" s="1" t="inlineStr">
         <is>
-          <t>[[ˈma̠(ː)ɭda̠]] 投掷 (烹饪)</t>
+          <t>[[ˈma̠(ː)ɭda̠]] 卷 (烹饪)</t>
         </is>
       </c>
       <c r="C492" s="1" t="inlineStr">
@@ -16157,7 +16157,7 @@
       </c>
       <c r="D492" s="1" t="inlineStr">
         <is>
-          <t>投掷 (烹饪)</t>
+          <t>卷 (烹饪)</t>
         </is>
       </c>
       <c r="E492" s="1" t="inlineStr">
@@ -16179,7 +16179,7 @@
       </c>
       <c r="B493" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʌ̹p̚t͈a̠]] 收回 (烹饪)</t>
+          <t>[[t͡ɕʌ̹p̚t͈a̠]] 折叠 (烹饪)</t>
         </is>
       </c>
       <c r="C493" s="1" t="inlineStr">
@@ -16189,7 +16189,7 @@
       </c>
       <c r="D493" s="1" t="inlineStr">
         <is>
-          <t>收回 (烹饪)</t>
+          <t>折叠 (烹饪)</t>
         </is>
       </c>
       <c r="E493" s="1" t="inlineStr">
@@ -16211,7 +16211,7 @@
       </c>
       <c r="B494" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʰɛuda̠]] 物品 (烹饪)</t>
+          <t>[[t͡ɕʰɛuda̠]] 填满 (烹饪)</t>
         </is>
       </c>
       <c r="C494" s="1" t="inlineStr">
@@ -16221,7 +16221,7 @@
       </c>
       <c r="D494" s="1" t="inlineStr">
         <is>
-          <t>物品 (烹饪)</t>
+          <t>填满 (烹饪)</t>
         </is>
       </c>
       <c r="E494" s="1" t="inlineStr">
@@ -16243,7 +16243,7 @@
       </c>
       <c r="B495" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʌ̹ɾida̠]] 泡菜 (烹饪)</t>
+          <t>[[t͡ɕʌ̹ɾida̠]] 腌制 (烹饪)</t>
         </is>
       </c>
       <c r="C495" s="1" t="inlineStr">
@@ -16253,7 +16253,7 @@
       </c>
       <c r="D495" s="1" t="inlineStr">
         <is>
-          <t>泡菜 (烹饪)</t>
+          <t>腌制 (烹饪)</t>
         </is>
       </c>
       <c r="E495" s="1" t="inlineStr">
@@ -16307,17 +16307,17 @@
       </c>
       <c r="B497" s="1" t="inlineStr">
         <is>
-          <t>[kukomata] 升温降温 (烹饪)</t>
+          <t>[[t͡ɕo̞d͡ʑʌ̹ɾa̠da̠]] 调节 (烹饪)</t>
         </is>
       </c>
       <c r="C497" s="1" t="inlineStr">
         <is>
-          <t>kukomata</t>
+          <t>[t͡ɕo̞d͡ʑʌ̹ɾa̠da̠]</t>
         </is>
       </c>
       <c r="D497" s="1" t="inlineStr">
         <is>
-          <t>升温降温 (烹饪)</t>
+          <t>调节 (烹饪)</t>
         </is>
       </c>
       <c r="E497" s="1" t="inlineStr">
@@ -16371,12 +16371,12 @@
       </c>
       <c r="B499" s="1" t="inlineStr">
         <is>
-          <t>[changryokpangngu] 压力锅 (烹饪)</t>
+          <t>[[a̠mɲʌ̹k̚p͈a̠p̚s͈o̞t̚]] 压力锅 (烹饪)</t>
         </is>
       </c>
       <c r="C499" s="1" t="inlineStr">
         <is>
-          <t>changryokpangngu</t>
+          <t>[a̠mɲʌ̹k̚p͈a̠p̚s͈o̞t̚]</t>
         </is>
       </c>
       <c r="D499" s="1" t="inlineStr">
@@ -16499,7 +16499,7 @@
       </c>
       <c r="B503" s="1" t="inlineStr">
         <is>
-          <t>[[ɯmpʰjo]] 备注 (音乐)</t>
+          <t>[[ɯmpʰjo]] 音符 (音乐)</t>
         </is>
       </c>
       <c r="C503" s="1" t="inlineStr">
@@ -16509,7 +16509,7 @@
       </c>
       <c r="D503" s="1" t="inlineStr">
         <is>
-          <t>备注 (音乐)</t>
+          <t>音符 (音乐)</t>
         </is>
       </c>
       <c r="E503" s="1" t="inlineStr">
@@ -16531,7 +16531,7 @@
       </c>
       <c r="B504" s="1" t="inlineStr">
         <is>
-          <t>[[ɸwa̠ɯm]] 弦形 (音乐)</t>
+          <t>[[ɸwa̠ɯm]] 和声 (音乐)</t>
         </is>
       </c>
       <c r="C504" s="1" t="inlineStr">
@@ -16541,7 +16541,7 @@
       </c>
       <c r="D504" s="1" t="inlineStr">
         <is>
-          <t>弦形 (音乐)</t>
+          <t>和声 (音乐)</t>
         </is>
       </c>
       <c r="E504" s="1" t="inlineStr">
@@ -16563,7 +16563,7 @@
       </c>
       <c r="B505" s="1" t="inlineStr">
         <is>
-          <t>[[ɯmɡje̞]] 设备规模 (音乐)</t>
+          <t>[[ɯmɡje̞]] 音阶 (音乐)</t>
         </is>
       </c>
       <c r="C505" s="1" t="inlineStr">
@@ -16573,7 +16573,7 @@
       </c>
       <c r="D505" s="1" t="inlineStr">
         <is>
-          <t>设备规模 (音乐)</t>
+          <t>音阶 (音乐)</t>
         </is>
       </c>
       <c r="E505" s="1" t="inlineStr">
@@ -16627,17 +16627,17 @@
       </c>
       <c r="B507" s="1" t="inlineStr">
         <is>
-          <t>[peritki] 舰桥 (音乐)</t>
+          <t>[[pɯɾit͡ɕi]] 桥段 (音乐)</t>
         </is>
       </c>
       <c r="C507" s="1" t="inlineStr">
         <is>
-          <t>peritki</t>
+          <t>[pɯɾit͡ɕi]</t>
         </is>
       </c>
       <c r="D507" s="1" t="inlineStr">
         <is>
-          <t>舰桥 (音乐)</t>
+          <t>桥段 (音乐)</t>
         </is>
       </c>
       <c r="E507" s="1" t="inlineStr">
@@ -16691,7 +16691,7 @@
       </c>
       <c r="B509" s="1" t="inlineStr">
         <is>
-          <t>[[ˈpa̠(ː)nbo̞k̚]] 副歌 (音乐)</t>
+          <t>[[ˈpa̠(ː)nbo̞k̚]] 重复 (音乐)</t>
         </is>
       </c>
       <c r="C509" s="1" t="inlineStr">
@@ -16701,7 +16701,7 @@
       </c>
       <c r="D509" s="1" t="inlineStr">
         <is>
-          <t>副歌 (音乐)</t>
+          <t>重复 (音乐)</t>
         </is>
       </c>
       <c r="E509" s="1" t="inlineStr">
@@ -16723,12 +16723,12 @@
       </c>
       <c r="B510" s="1" t="inlineStr">
         <is>
-          <t>[chathure] 安可 (音乐)</t>
+          <t>[[a̠ŋkʰo̞ɾɯ]] 安可 (音乐)</t>
         </is>
       </c>
       <c r="C510" s="1" t="inlineStr">
         <is>
-          <t>chathure</t>
+          <t>[a̠ŋkʰo̞ɾɯ]</t>
         </is>
       </c>
       <c r="D510" s="1" t="inlineStr">
@@ -16755,7 +16755,7 @@
       </c>
       <c r="B511" s="1" t="inlineStr">
         <is>
-          <t>[[ɛmpʰɯ]] 扩大机 (音乐)</t>
+          <t>[[ɛmpʰɯ]] 放大器；扩音机 (音乐)</t>
         </is>
       </c>
       <c r="C511" s="1" t="inlineStr">
@@ -16765,7 +16765,7 @@
       </c>
       <c r="D511" s="1" t="inlineStr">
         <is>
-          <t>扩大机 (音乐)</t>
+          <t>放大器；扩音机 (音乐)</t>
         </is>
       </c>
       <c r="E511" s="1" t="inlineStr">
@@ -16851,7 +16851,7 @@
       </c>
       <c r="B514" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕa̠ks͈a̠ɡa̠]] 词曲作家 (音乐)</t>
+          <t>[[t͡ɕa̠ks͈a̠ɡa̠]] 作词人 (音乐)</t>
         </is>
       </c>
       <c r="C514" s="1" t="inlineStr">
@@ -16861,7 +16861,7 @@
       </c>
       <c r="D514" s="1" t="inlineStr">
         <is>
-          <t>词曲作家 (音乐)</t>
+          <t>作词人 (音乐)</t>
         </is>
       </c>
       <c r="E514" s="1" t="inlineStr">
@@ -16915,12 +16915,12 @@
       </c>
       <c r="B516" s="1" t="inlineStr">
         <is>
-          <t>[ngachinchempong] 签名专辑 (音乐)</t>
+          <t>[[sa.inɛlpʌm]] 签名专辑 (音乐)</t>
         </is>
       </c>
       <c r="C516" s="1" t="inlineStr">
         <is>
-          <t>ngachinchempong</t>
+          <t>[sa.inɛlpʌm]</t>
         </is>
       </c>
       <c r="D516" s="1" t="inlineStr">
@@ -16947,12 +16947,12 @@
       </c>
       <c r="B517" s="1" t="inlineStr">
         <is>
-          <t>[hopotennge] 翻跳 (音乐)</t>
+          <t>[[kʰʌbɔtɛnsɨ]] 翻跳 (音乐)</t>
         </is>
       </c>
       <c r="C517" s="1" t="inlineStr">
         <is>
-          <t>hopotennge</t>
+          <t>[kʰʌbɔtɛnsɨ]</t>
         </is>
       </c>
       <c r="D517" s="1" t="inlineStr">
@@ -16979,12 +16979,12 @@
       </c>
       <c r="B518" s="1" t="inlineStr">
         <is>
-          <t>[chechikonngi] 经纪公司 (音乐)</t>
+          <t>[[eːitɕənsʰi]] 经纪公司 (音乐)</t>
         </is>
       </c>
       <c r="C518" s="1" t="inlineStr">
         <is>
-          <t>chechikonngi</t>
+          <t>[eːitɕənsʰi]</t>
         </is>
       </c>
       <c r="D518" s="1" t="inlineStr">
@@ -17011,12 +17011,12 @@
       </c>
       <c r="B519" s="1" t="inlineStr">
         <is>
-          <t>[ruchyomi] 版税 (音乐)</t>
+          <t>[[ɾojʌltʰi]] 版税 (音乐)</t>
         </is>
       </c>
       <c r="C519" s="1" t="inlineStr">
         <is>
-          <t>ruchyomi</t>
+          <t>[ɾojʌltʰi]</t>
         </is>
       </c>
       <c r="D519" s="1" t="inlineStr">
@@ -17043,17 +17043,17 @@
       </c>
       <c r="B520" s="1" t="inlineStr">
         <is>
-          <t>[pimpute] 告示牌 (音乐)</t>
+          <t>[[pilbɔtɨ]] 公告牌榜单 (音乐)</t>
         </is>
       </c>
       <c r="C520" s="1" t="inlineStr">
         <is>
-          <t>pimpute</t>
+          <t>[pilbɔtɨ]</t>
         </is>
       </c>
       <c r="D520" s="1" t="inlineStr">
         <is>
-          <t>告示牌 (音乐)</t>
+          <t>公告牌榜单 (音乐)</t>
         </is>
       </c>
       <c r="E520" s="1" t="inlineStr">
@@ -17075,12 +17075,12 @@
       </c>
       <c r="B521" s="1" t="inlineStr">
         <is>
-          <t>[keremi] 葛莱美奖 (音乐)</t>
+          <t>[[kɨɾɛmi]] 葛莱美奖 (音乐)</t>
         </is>
       </c>
       <c r="C521" s="1" t="inlineStr">
         <is>
-          <t>keremi</t>
+          <t>[kɨɾɛmi]</t>
         </is>
       </c>
       <c r="D521" s="1" t="inlineStr">
@@ -17107,12 +17107,12 @@
       </c>
       <c r="B522" s="1" t="inlineStr">
         <is>
-          <t>[chinkikachy] 人气歌谣 (音乐)</t>
+          <t>[[iŋɡiɡajo]] 人气歌谣 (音乐)</t>
         </is>
       </c>
       <c r="C522" s="1" t="inlineStr">
         <is>
-          <t>chinkikachy</t>
+          <t>[iŋɡiɡajo]</t>
         </is>
       </c>
       <c r="D522" s="1" t="inlineStr">
@@ -17139,12 +17139,12 @@
       </c>
       <c r="B523" s="1" t="inlineStr">
         <is>
-          <t>[mwkikpethe] 音乐银行 (音乐)</t>
+          <t>[[mjutɕikpɛŋkʰɨ]] 音乐银行 (音乐)</t>
         </is>
       </c>
       <c r="C523" s="1" t="inlineStr">
         <is>
-          <t>mwkikpethe</t>
+          <t>[mjutɕikpɛŋkʰɨ]</t>
         </is>
       </c>
       <c r="D523" s="1" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="B524" s="1" t="inlineStr">
         <is>
-          <t>[[ka̠ja̠ɡɯm]] 伽唢啰 (音乐)</t>
+          <t>[[ka̠ja̠ɡɯm]] 伽倻琴 (音乐)</t>
         </is>
       </c>
       <c r="C524" s="1" t="inlineStr">
@@ -17181,7 +17181,7 @@
       </c>
       <c r="D524" s="1" t="inlineStr">
         <is>
-          <t>伽唢啰 (音乐)</t>
+          <t>伽倻琴 (音乐)</t>
         </is>
       </c>
       <c r="E524" s="1" t="inlineStr">
@@ -17235,12 +17235,12 @@
       </c>
       <c r="B526" s="1" t="inlineStr">
         <is>
-          <t>[nginnge] 合成器 (音乐)</t>
+          <t>[[ɕinsɨ]] 合成器 (音乐)</t>
         </is>
       </c>
       <c r="C526" s="1" t="inlineStr">
         <is>
-          <t>nginnge</t>
+          <t>[ɕinsɨ]</t>
         </is>
       </c>
       <c r="D526" s="1" t="inlineStr">
@@ -17299,12 +17299,12 @@
       </c>
       <c r="B528" s="1" t="inlineStr">
         <is>
-          <t>[mikngit] 混合 (音乐)</t>
+          <t>[[mikɕiŋ]] 混合 (音乐)</t>
         </is>
       </c>
       <c r="C528" s="1" t="inlineStr">
         <is>
-          <t>mikngit</t>
+          <t>[mikɕiŋ]</t>
         </is>
       </c>
       <c r="D528" s="1" t="inlineStr">
@@ -17331,17 +17331,17 @@
       </c>
       <c r="B529" s="1" t="inlineStr">
         <is>
-          <t>[mangeorit] 控制 (音乐)</t>
+          <t>[[masɨtʰɔɾiŋ]] 母带处理 (音乐)</t>
         </is>
       </c>
       <c r="C529" s="1" t="inlineStr">
         <is>
-          <t>mangeorit</t>
+          <t>[masɨtʰɔɾiŋ]</t>
         </is>
       </c>
       <c r="D529" s="1" t="inlineStr">
         <is>
-          <t>控制 (音乐)</t>
+          <t>母带处理 (音乐)</t>
         </is>
       </c>
       <c r="E529" s="1" t="inlineStr">
@@ -17395,17 +17395,17 @@
       </c>
       <c r="B531" s="1" t="inlineStr">
         <is>
-          <t>[neechehit] 网络 (商业)</t>
+          <t>[[netʰɨwɔkʰiŋ]] 人脉拓展 (商业)</t>
         </is>
       </c>
       <c r="C531" s="1" t="inlineStr">
         <is>
-          <t>neechehit</t>
+          <t>[netʰɨwɔkʰiŋ]</t>
         </is>
       </c>
       <c r="D531" s="1" t="inlineStr">
         <is>
-          <t>网络 (商业)</t>
+          <t>人脉拓展 (商业)</t>
         </is>
       </c>
       <c r="E531" s="1" t="inlineStr">
@@ -17427,7 +17427,7 @@
       </c>
       <c r="B532" s="1" t="inlineStr">
         <is>
-          <t>[[kʰa̠ʎd͡ʑiɭ]] 刀技 (烹饪)</t>
+          <t>[[kʰa̠ʎd͡ʑiɭ]] 刀工；切菜 (烹饪)</t>
         </is>
       </c>
       <c r="C532" s="1" t="inlineStr">
@@ -17437,7 +17437,7 @@
       </c>
       <c r="D532" s="1" t="inlineStr">
         <is>
-          <t>刀技 (烹饪)</t>
+          <t>刀工；切菜 (烹饪)</t>
         </is>
       </c>
       <c r="E532" s="1" t="inlineStr">
@@ -17523,12 +17523,12 @@
       </c>
       <c r="B535" s="1" t="inlineStr">
         <is>
-          <t>[katnget] 模范充实人生；开挂般的生活 (명사)</t>
+          <t>[[kat̚sɛŋ]] 模范充实人生；开挂般的生活 (명사)</t>
         </is>
       </c>
       <c r="C535" s="1" t="inlineStr">
         <is>
-          <t>katnget</t>
+          <t>[kat̚sɛŋ]</t>
         </is>
       </c>
       <c r="D535" s="1" t="inlineStr">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="B536" s="1" t="inlineStr">
         <is>
-          <t>[nguwket] 微小而确实的幸福；小确幸 (명사)</t>
+          <t>[[sʰoɦwakʰɛŋ]] 微小而确实的幸福；小确幸 (명사)</t>
         </is>
       </c>
       <c r="C536" s="1" t="inlineStr">
         <is>
-          <t>nguwket</t>
+          <t>[sʰoɦwakʰɛŋ]</t>
         </is>
       </c>
       <c r="D536" s="1" t="inlineStr">
@@ -17683,7 +17683,7 @@
       </c>
       <c r="B540" s="1" t="inlineStr">
         <is>
-          <t>[[a̠ɭɡo̞ɾid͡ʑɯm]] 流程图（见附件） (科技)</t>
+          <t>[[a̠ɭɡo̞ɾid͡ʑɯm]] 算法 (科技)</t>
         </is>
       </c>
       <c r="C540" s="1" t="inlineStr">
@@ -17693,7 +17693,7 @@
       </c>
       <c r="D540" s="1" t="inlineStr">
         <is>
-          <t>流程图（见附件） (科技)</t>
+          <t>算法 (科技)</t>
         </is>
       </c>
       <c r="E540" s="1" t="inlineStr">
@@ -17715,12 +17715,12 @@
       </c>
       <c r="B541" s="1" t="inlineStr">
         <is>
-          <t>[mikngeechie] 混音带；Mixtape (명사)</t>
+          <t>[[miksɨtʰɛipʰɨ]] 混音带；Mixtape (명사)</t>
         </is>
       </c>
       <c r="C541" s="1" t="inlineStr">
         <is>
-          <t>mikngeechie</t>
+          <t>[miksɨtʰɛipʰɨ]</t>
         </is>
       </c>
       <c r="D541" s="1" t="inlineStr">
@@ -17747,12 +17747,12 @@
       </c>
       <c r="B542" s="1" t="inlineStr">
         <is>
-          <t>[ngachintepehe] 声音检查 (音乐)</t>
+          <t>[[sa.unt̚tɕʰekʰ]] 声音检查 (音乐)</t>
         </is>
       </c>
       <c r="C542" s="1" t="inlineStr">
         <is>
-          <t>ngachintepehe</t>
+          <t>[sa.unt̚tɕʰekʰ]</t>
         </is>
       </c>
       <c r="D542" s="1" t="inlineStr">
@@ -17811,12 +17811,12 @@
       </c>
       <c r="B544" s="1" t="inlineStr">
         <is>
-          <t>[nguchwikang] 疏离感；被孤立感 (명사)</t>
+          <t>[[sʰowɛɡam]] 疏离感；被孤立感 (명사)</t>
         </is>
       </c>
       <c r="C544" s="1" t="inlineStr">
         <is>
-          <t>nguchwikang</t>
+          <t>[sʰowɛɡam]</t>
         </is>
       </c>
       <c r="D544" s="1" t="inlineStr">
@@ -17843,12 +17843,12 @@
       </c>
       <c r="B545" s="1" t="inlineStr">
         <is>
-          <t>[tonta] 超酷 (俚语)</t>
+          <t>[[t͈ɕʌn̚t͈a̠]] 超酷 (俚语)</t>
         </is>
       </c>
       <c r="C545" s="1" t="inlineStr">
         <is>
-          <t>tonta</t>
+          <t>[t͈ɕʌn̚t͈a̠]</t>
         </is>
       </c>
       <c r="D545" s="1" t="inlineStr">
@@ -17875,7 +17875,7 @@
       </c>
       <c r="B546" s="1" t="inlineStr">
         <is>
-          <t>[[hɛk̚]] 特级 (俚语)</t>
+          <t>[[hɛk̚]] 超级（加强语气） (俚语)</t>
         </is>
       </c>
       <c r="C546" s="1" t="inlineStr">
@@ -17885,7 +17885,7 @@
       </c>
       <c r="D546" s="1" t="inlineStr">
         <is>
-          <t>特级 (俚语)</t>
+          <t>超级（加强语气） (俚语)</t>
         </is>
       </c>
       <c r="E546" s="1" t="inlineStr">
@@ -17907,12 +17907,12 @@
       </c>
       <c r="B547" s="1" t="inlineStr">
         <is>
-          <t>[mipyolta] 疯狂 (俚语)</t>
+          <t>[[miˈt͈ɕʰjʌ̹t̚t͈a̠]] 疯狂 (俚语)</t>
         </is>
       </c>
       <c r="C547" s="1" t="inlineStr">
         <is>
-          <t>mipyolta</t>
+          <t>[miˈt͈ɕʰjʌ̹t̚t͈a̠]</t>
         </is>
       </c>
       <c r="D547" s="1" t="inlineStr">
@@ -17939,7 +17939,7 @@
       </c>
       <c r="B548" s="1" t="inlineStr">
         <is>
-          <t>[[k͈uɭ]] 甜品 (俚语)</t>
+          <t>[[k͈uɭ]] 绝佳（超棒） (俚语)</t>
         </is>
       </c>
       <c r="C548" s="1" t="inlineStr">
@@ -17949,7 +17949,7 @@
       </c>
       <c r="D548" s="1" t="inlineStr">
         <is>
-          <t>甜品 (俚语)</t>
+          <t>绝佳（超棒） (俚语)</t>
         </is>
       </c>
       <c r="E548" s="1" t="inlineStr">
@@ -18003,7 +18003,7 @@
       </c>
       <c r="B550" s="1" t="inlineStr">
         <is>
-          <t>[[ka̠t̚]] 神 (俚语)</t>
+          <t>[[ka̠t̚]] 帽子；刚刚 (俚语)</t>
         </is>
       </c>
       <c r="C550" s="1" t="inlineStr">
@@ -18013,7 +18013,7 @@
       </c>
       <c r="D550" s="1" t="inlineStr">
         <is>
-          <t>神 (俚语)</t>
+          <t>帽子；刚刚 (俚语)</t>
         </is>
       </c>
       <c r="E550" s="1" t="inlineStr">
@@ -18067,12 +18067,12 @@
       </c>
       <c r="B552" s="1" t="inlineStr">
         <is>
-          <t>[pekun] 尊重品味 (俚语)</t>
+          <t>[[t͡ɕʰɥi.t͡ɕo̞n]] 尊重品味 (俚语)</t>
         </is>
       </c>
       <c r="C552" s="1" t="inlineStr">
         <is>
-          <t>pekun</t>
+          <t>[t͡ɕʰɥi.t͡ɕo̞n]</t>
         </is>
       </c>
       <c r="D552" s="1" t="inlineStr">
@@ -18227,12 +18227,12 @@
       </c>
       <c r="B557" s="1" t="inlineStr">
         <is>
-          <t>[ninpichotta] 没有眼力 (俚语)</t>
+          <t>[[nun.t͡ɕʰi.ʌ̹p̚t͈a̠]] 没有眼力 (俚语)</t>
         </is>
       </c>
       <c r="C557" s="1" t="inlineStr">
         <is>
-          <t>ninpichotta</t>
+          <t>[nun.t͡ɕʰi.ʌ̹p̚t͈a̠]</t>
         </is>
       </c>
       <c r="D557" s="1" t="inlineStr">
@@ -18259,12 +18259,12 @@
       </c>
       <c r="B558" s="1" t="inlineStr">
         <is>
-          <t>[ngenngechotta] 没有品味 (俚语)</t>
+          <t>[[sʰe̞n.sɯ.ʌ̹p̚t͈a̠]] 没有品味 (俚语)</t>
         </is>
       </c>
       <c r="C558" s="1" t="inlineStr">
         <is>
-          <t>ngenngechotta</t>
+          <t>[sʰe̞n.sɯ.ʌ̹p̚t͈a̠]</t>
         </is>
       </c>
       <c r="D558" s="1" t="inlineStr">
@@ -18323,12 +18323,12 @@
       </c>
       <c r="B560" s="1" t="inlineStr">
         <is>
-          <t>[ekchinca] 超级受欢迎 (俚语)</t>
+          <t>[[hɛ̝.ɡin͈.s͈a̠]] 超级受欢迎 (俚语)</t>
         </is>
       </c>
       <c r="C560" s="1" t="inlineStr">
         <is>
-          <t>ekchinca</t>
+          <t>[hɛ̝.ɡin͈.s͈a̠]</t>
         </is>
       </c>
       <c r="D560" s="1" t="inlineStr">
@@ -18387,12 +18387,12 @@
       </c>
       <c r="B562" s="1" t="inlineStr">
         <is>
-          <t>[kekkutkang] 极度同感 (俚语)</t>
+          <t>[[kɯ.ɡk͈o̞ŋ.ɡa̠m]] 极度同感 (俚语)</t>
         </is>
       </c>
       <c r="C562" s="1" t="inlineStr">
         <is>
-          <t>kekkutkang</t>
+          <t>[kɯ.ɡk͈o̞ŋ.ɡa̠m]</t>
         </is>
       </c>
       <c r="D562" s="1" t="inlineStr">
@@ -18451,12 +18451,12 @@
       </c>
       <c r="B564" s="1" t="inlineStr">
         <is>
-          <t>[kangingpi] 心情消费 (俚语)</t>
+          <t>[[ka̠.ɕim.bi]] 心情消费 (俚语)</t>
         </is>
       </c>
       <c r="C564" s="1" t="inlineStr">
         <is>
-          <t>kangingpi</t>
+          <t>[ka̠.ɕim.bi]</t>
         </is>
       </c>
       <c r="D564" s="1" t="inlineStr">
@@ -18611,12 +18611,12 @@
       </c>
       <c r="B569" s="1" t="inlineStr">
         <is>
-          <t>[ngepimke] 不好笑 (俚语)</t>
+          <t>[[sɯ.buɭ.d͡ʑɛ̝]] 不好笑 (俚语)</t>
         </is>
       </c>
       <c r="C569" s="1" t="inlineStr">
         <is>
-          <t>ngepimke</t>
+          <t>[sɯ.buɭ.d͡ʑɛ̝]</t>
         </is>
       </c>
       <c r="D569" s="1" t="inlineStr">
@@ -18707,12 +18707,12 @@
       </c>
       <c r="B572" s="1" t="inlineStr">
         <is>
-          <t>[kwmumching] 痴迷 (俚语)</t>
+          <t>[[kwa̠.mo̞.ɾip̚]] 痴迷 (俚语)</t>
         </is>
       </c>
       <c r="C572" s="1" t="inlineStr">
         <is>
-          <t>kwmumching</t>
+          <t>[kwa̠.mo̞.ɾip̚]</t>
         </is>
       </c>
       <c r="D572" s="1" t="inlineStr">
@@ -18835,12 +18835,12 @@
       </c>
       <c r="B576" s="1" t="inlineStr">
         <is>
-          <t>[ingata] 时髦 (俚语)</t>
+          <t>[[çi.pʰa̠.da̠]] 时髦 (俚语)</t>
         </is>
       </c>
       <c r="C576" s="1" t="inlineStr">
         <is>
-          <t>ingata</t>
+          <t>[çi.pʰa̠.da̠]</t>
         </is>
       </c>
       <c r="D576" s="1" t="inlineStr">
@@ -18899,12 +18899,12 @@
       </c>
       <c r="B578" s="1" t="inlineStr">
         <is>
-          <t>[chinngetngyat] 人生照 (俚语)</t>
+          <t>[[in.sɛ̝ŋ.s͈a̠t̚]] 人生照 (俚语)</t>
         </is>
       </c>
       <c r="C578" s="1" t="inlineStr">
         <is>
-          <t>chinngetngyat</t>
+          <t>[in.sɛ̝ŋ.s͈a̠t̚]</t>
         </is>
       </c>
       <c r="D578" s="1" t="inlineStr">
@@ -18931,12 +18931,12 @@
       </c>
       <c r="B579" s="1" t="inlineStr">
         <is>
-          <t>[atem] 热门地点 (俚语)</t>
+          <t>[[ha̠p̚.p͈ɯɾ]] 热门地点 (俚语)</t>
         </is>
       </c>
       <c r="C579" s="1" t="inlineStr">
         <is>
-          <t>atem</t>
+          <t>[ha̠p̚.p͈ɯɾ]</t>
         </is>
       </c>
       <c r="D579" s="1" t="inlineStr">
@@ -18963,17 +18963,17 @@
       </c>
       <c r="B580" s="1" t="inlineStr">
         <is>
-          <t>[kemri] 蜕变 (俚语)</t>
+          <t>[[kɯɭ.ɭu]] 胶水 (俚语)</t>
         </is>
       </c>
       <c r="C580" s="1" t="inlineStr">
         <is>
-          <t>kemri</t>
+          <t>[kɯɭ.ɭu]</t>
         </is>
       </c>
       <c r="D580" s="1" t="inlineStr">
         <is>
-          <t>蜕变 (俚语)</t>
+          <t>胶水 (俚语)</t>
         </is>
       </c>
       <c r="E580" s="1" t="inlineStr">
@@ -18995,12 +18995,12 @@
       </c>
       <c r="B581" s="1" t="inlineStr">
         <is>
-          <t>[tokngat] 股价飙升 (俚语)</t>
+          <t>[[tʌ̹k͈.sa̠ŋ]] 股价飙升 (俚语)</t>
         </is>
       </c>
       <c r="C581" s="1" t="inlineStr">
         <is>
-          <t>tokngat</t>
+          <t>[tʌ̹k͈.sa̠ŋ]</t>
         </is>
       </c>
       <c r="D581" s="1" t="inlineStr">
@@ -19027,12 +19027,12 @@
       </c>
       <c r="B582" s="1" t="inlineStr">
         <is>
-          <t>[tokrak] 股价暴跌 (俚语)</t>
+          <t>[[tʌ̹ŋ.ŋa̠k̚]] 股价暴跌 (俚语)</t>
         </is>
       </c>
       <c r="C582" s="1" t="inlineStr">
         <is>
-          <t>tokrak</t>
+          <t>[tʌ̹ŋ.ŋa̠k̚]</t>
         </is>
       </c>
       <c r="D582" s="1" t="inlineStr">
@@ -19091,17 +19091,17 @@
       </c>
       <c r="B584" s="1" t="inlineStr">
         <is>
-          <t>[chyotkem] 全部投放 (俚语)</t>
+          <t>[[jʌ̹ŋ.ɡ͈ɯɭ]] 倾尽所有超前投资 (俚语) (俚语)</t>
         </is>
       </c>
       <c r="C584" s="1" t="inlineStr">
         <is>
-          <t>chyotkem</t>
+          <t>[jʌ̹ŋ.ɡ͈ɯɭ]</t>
         </is>
       </c>
       <c r="D584" s="1" t="inlineStr">
         <is>
-          <t>全部投放 (俚语)</t>
+          <t>倾尽所有超前投资 (俚语) (俚语)</t>
         </is>
       </c>
       <c r="E584" s="1" t="inlineStr">
@@ -19123,12 +19123,12 @@
       </c>
       <c r="B585" s="1" t="inlineStr">
         <is>
-          <t>[pipi] 借贷投资 (俚语)</t>
+          <t>[[pin͈.tʰu]] 借贷投资 (俚语)</t>
         </is>
       </c>
       <c r="C585" s="1" t="inlineStr">
         <is>
-          <t>pipi</t>
+          <t>[pin͈.tʰu]</t>
         </is>
       </c>
       <c r="D585" s="1" t="inlineStr">
@@ -19155,17 +19155,17 @@
       </c>
       <c r="B586" s="1" t="inlineStr">
         <is>
-          <t>[maut] 妈妈的钱 (俚语)</t>
+          <t>[[ma̠.t͈o̞ŋ]] 妈妈卡 (俚语)</t>
         </is>
       </c>
       <c r="C586" s="1" t="inlineStr">
         <is>
-          <t>maut</t>
+          <t>[ma̠.t͈o̞ŋ]</t>
         </is>
       </c>
       <c r="D586" s="1" t="inlineStr">
         <is>
-          <t>妈妈的钱 (俚语)</t>
+          <t>妈妈卡 (俚语)</t>
         </is>
       </c>
       <c r="E586" s="1" t="inlineStr">
@@ -19219,12 +19219,12 @@
       </c>
       <c r="B588" s="1" t="inlineStr">
         <is>
-          <t>[niekuk] 尼特族 (俚语)</t>
+          <t>[[ni.tʰɯ.d͡ʑo̞k̚]] 尼特族 (俚语)</t>
         </is>
       </c>
       <c r="C588" s="1" t="inlineStr">
         <is>
-          <t>niekuk</t>
+          <t>[ni.tʰɯ.d͡ʑo̞k̚]</t>
         </is>
       </c>
       <c r="D588" s="1" t="inlineStr">
@@ -19283,12 +19283,12 @@
       </c>
       <c r="B590" s="1" t="inlineStr">
         <is>
-          <t>[ikyongehechiit] 花式溜冰 (运动)</t>
+          <t>[[pʰi.ɡjʌ.sɯ.kʰe.i.tʰiŋ]] 花式溜冰 (运动)</t>
         </is>
       </c>
       <c r="C590" s="1" t="inlineStr">
         <is>
-          <t>ikyongehechiit</t>
+          <t>[pʰi.ɡjʌ.sɯ.kʰe.i.tʰiŋ]</t>
         </is>
       </c>
       <c r="D590" s="1" t="inlineStr">
@@ -19763,12 +19763,12 @@
       </c>
       <c r="B605" s="1" t="inlineStr">
         <is>
-          <t>[chenantonkiki] 铁饼 (运动)</t>
+          <t>[[wʌn.pʰan.tʌn.tɕi.ɡi]] 铁饼 (运动)</t>
         </is>
       </c>
       <c r="C605" s="1" t="inlineStr">
         <is>
-          <t>chenantonkiki</t>
+          <t>[wʌn.pʰan.tʌn.tɕi.ɡi]</t>
         </is>
       </c>
       <c r="D605" s="1" t="inlineStr">
@@ -19891,12 +19891,12 @@
       </c>
       <c r="B609" s="1" t="inlineStr">
         <is>
-          <t>[changpyoktetpan] 攀岩 (运动)</t>
+          <t>[[am.bjʌk̚.tɯŋ.pan]] 攀岩 (运动)</t>
         </is>
       </c>
       <c r="C609" s="1" t="inlineStr">
         <is>
-          <t>changpyoktetpan</t>
+          <t>[am.bjʌk̚.tɯŋ.pan]</t>
         </is>
       </c>
       <c r="D609" s="1" t="inlineStr">
@@ -19923,12 +19923,12 @@
       </c>
       <c r="B610" s="1" t="inlineStr">
         <is>
-          <t>[kikiryok] 耐力 (运动)</t>
+          <t>[[tɕi.ɡu.ŋjʌk̚]] 耐力 (运动)</t>
         </is>
       </c>
       <c r="C610" s="1" t="inlineStr">
         <is>
-          <t>kikiryok</t>
+          <t>[tɕi.ɡu.ŋjʌk̚]</t>
         </is>
       </c>
       <c r="D610" s="1" t="inlineStr">
@@ -20179,12 +20179,12 @@
       </c>
       <c r="B618" s="1" t="inlineStr">
         <is>
-          <t>[changichankeching] 亚洲运动会 (运动)</t>
+          <t>[[a.ɕi.an.ɡe.im]] 亚洲运动会 (运动)</t>
         </is>
       </c>
       <c r="C618" s="1" t="inlineStr">
         <is>
-          <t>changichankeching</t>
+          <t>[a.ɕi.an.ɡe.im]</t>
         </is>
       </c>
       <c r="D618" s="1" t="inlineStr">
@@ -20211,12 +20211,12 @@
       </c>
       <c r="B619" s="1" t="inlineStr">
         <is>
-          <t>[kikkateying] 国家队 (运动)</t>
+          <t>[[kuk̚.k͈a.dɛ.pʰjo.tʰim]] 国家队 (运动)</t>
         </is>
       </c>
       <c r="C619" s="1" t="inlineStr">
         <is>
-          <t>kikkateying</t>
+          <t>[kuk̚.k͈a.dɛ.pʰjo.tʰim]</t>
         </is>
       </c>
       <c r="D619" s="1" t="inlineStr">
@@ -20339,12 +20339,12 @@
       </c>
       <c r="B623" s="1" t="inlineStr">
         <is>
-          <t>[chenkotkyotki] 客场比赛 (运动)</t>
+          <t>[[wʌn.dʑʌŋ.ɡjʌŋ.ɡi]] 客场比赛 (运动)</t>
         </is>
       </c>
       <c r="C623" s="1" t="inlineStr">
         <is>
-          <t>chenkotkyotki</t>
+          <t>[wʌn.dʑʌŋ.ɡjʌŋ.ɡi]</t>
         </is>
       </c>
       <c r="D623" s="1" t="inlineStr">
@@ -20371,12 +20371,12 @@
       </c>
       <c r="B624" s="1" t="inlineStr">
         <is>
-          <t>[ungkyotki] 主场比赛 (运动)</t>
+          <t>[[hom.ɡjʌŋ.ɡi]] 主场比赛 (运动)</t>
         </is>
       </c>
       <c r="C624" s="1" t="inlineStr">
         <is>
-          <t>ungkyotki</t>
+          <t>[hom.ɡjʌŋ.ɡi]</t>
         </is>
       </c>
       <c r="D624" s="1" t="inlineStr">
@@ -20435,12 +20435,12 @@
       </c>
       <c r="B626" s="1" t="inlineStr">
         <is>
-          <t>[ngekyekiruk] 世界纪录 (运动)</t>
+          <t>[[se.ɡje.ɡi.ɾjuk̚]] 世界纪录 (运动)</t>
         </is>
       </c>
       <c r="C626" s="1" t="inlineStr">
         <is>
-          <t>ngekyekiruk</t>
+          <t>[se.ɡje.ɡi.ɾjuk̚]</t>
         </is>
       </c>
       <c r="D626" s="1" t="inlineStr">
@@ -20467,12 +20467,12 @@
       </c>
       <c r="B627" s="1" t="inlineStr">
         <is>
-          <t>[inryonhenge] 训练营 (运动)</t>
+          <t>[[hun.ɲjʌn.kʰɛm.pʰɯ]] 训练营 (运动)</t>
         </is>
       </c>
       <c r="C627" s="1" t="inlineStr">
         <is>
-          <t>inryonhenge</t>
+          <t>[hun.ɲjʌn.kʰɛm.pʰɯ]</t>
         </is>
       </c>
       <c r="D627" s="1" t="inlineStr">
@@ -20499,12 +20499,12 @@
       </c>
       <c r="B628" s="1" t="inlineStr">
         <is>
-          <t>[ngeupechyotchyat] 运动营养学 (运动)</t>
+          <t>[[sɯ.pʰo.tɕʰɯ.jʌŋ.jaŋ]] 运动营养学 (运动)</t>
         </is>
       </c>
       <c r="C628" s="1" t="inlineStr">
         <is>
-          <t>ngeupechyotchyat</t>
+          <t>[sɯ.pʰo.tɕʰɯ.jʌŋ.jaŋ]</t>
         </is>
       </c>
       <c r="D628" s="1" t="inlineStr">
@@ -20531,12 +20531,12 @@
       </c>
       <c r="B629" s="1" t="inlineStr">
         <is>
-          <t>[ngipinngongpe] 水分补充 (运动)</t>
+          <t>[[su.bun.sʌp̚.tɕʰwi]] 水分补充 (运动)</t>
         </is>
       </c>
       <c r="C629" s="1" t="inlineStr">
         <is>
-          <t>ngipinngongpe</t>
+          <t>[su.bun.sʌp̚.tɕʰwi]</t>
         </is>
       </c>
       <c r="D629" s="1" t="inlineStr">
@@ -20595,12 +20595,12 @@
       </c>
       <c r="B631" s="1" t="inlineStr">
         <is>
-          <t>[monginronit] 机器学习 (科技)</t>
+          <t>[[mʌ.ɕin.ɾʌ.niŋ]] 机器学习 (科技)</t>
         </is>
       </c>
       <c r="C631" s="1" t="inlineStr">
         <is>
-          <t>monginronit</t>
+          <t>[mʌ.ɕin.ɾʌ.niŋ]</t>
         </is>
       </c>
       <c r="D631" s="1" t="inlineStr">
@@ -20659,17 +20659,17 @@
       </c>
       <c r="B633" s="1" t="inlineStr">
         <is>
-          <t>[piktechio] 大数据数字展厅 (科技)</t>
+          <t>[[pik̚.tɛ.tʰʌ]] 大数据 (科技)</t>
         </is>
       </c>
       <c r="C633" s="1" t="inlineStr">
         <is>
-          <t>piktechio</t>
+          <t>[pik̚.tɛ.tʰʌ]</t>
         </is>
       </c>
       <c r="D633" s="1" t="inlineStr">
         <is>
-          <t>大数据数字展厅 (科技)</t>
+          <t>大数据 (科技)</t>
         </is>
       </c>
       <c r="E633" s="1" t="inlineStr">
@@ -20723,7 +20723,7 @@
       </c>
       <c r="B635" s="1" t="inlineStr">
         <is>
-          <t>[[s͈ʌ̹bʌ̹]] 区服 (科技)</t>
+          <t>[[s͈ʌ̹bʌ̹]] 服务器 (科技)</t>
         </is>
       </c>
       <c r="C635" s="1" t="inlineStr">
@@ -20733,7 +20733,7 @@
       </c>
       <c r="D635" s="1" t="inlineStr">
         <is>
-          <t>区服 (科技)</t>
+          <t>服务器 (科技)</t>
         </is>
       </c>
       <c r="E635" s="1" t="inlineStr">
@@ -20755,17 +20755,17 @@
       </c>
       <c r="B636" s="1" t="inlineStr">
         <is>
-          <t>[hutit] 编码 (科技)</t>
+          <t>[[kʰo̞diŋ]] 编程 (科技)</t>
         </is>
       </c>
       <c r="C636" s="1" t="inlineStr">
         <is>
-          <t>hutit</t>
+          <t>[kʰo̞diŋ]</t>
         </is>
       </c>
       <c r="D636" s="1" t="inlineStr">
         <is>
-          <t>编码 (科技)</t>
+          <t>编程 (科技)</t>
         </is>
       </c>
       <c r="E636" s="1" t="inlineStr">
@@ -20947,12 +20947,12 @@
       </c>
       <c r="B642" s="1" t="inlineStr">
         <is>
-          <t>[tipoke] 调试 (科技)</t>
+          <t>[[tibʌ̹ɡɯ]] 调试 (科技)</t>
         </is>
       </c>
       <c r="C642" s="1" t="inlineStr">
         <is>
-          <t>tipoke</t>
+          <t>[tibʌ̹ɡɯ]</t>
         </is>
       </c>
       <c r="D642" s="1" t="inlineStr">
@@ -20979,17 +20979,17 @@
       </c>
       <c r="B643" s="1" t="inlineStr">
         <is>
-          <t>[chuenngunge] 华为开源 (科技)</t>
+          <t>[[o̞pʰɯnsʰo̞sʰɯ]] 开源 (科技)</t>
         </is>
       </c>
       <c r="C643" s="1" t="inlineStr">
         <is>
-          <t>chuenngunge</t>
+          <t>[o̞pʰɯnsʰo̞sʰɯ]</t>
         </is>
       </c>
       <c r="D643" s="1" t="inlineStr">
         <is>
-          <t>华为开源 (科技)</t>
+          <t>开源 (科技)</t>
         </is>
       </c>
       <c r="E643" s="1" t="inlineStr">
@@ -21011,12 +21011,12 @@
       </c>
       <c r="B644" s="1" t="inlineStr">
         <is>
-          <t>[inehe] 金融科技；Fintech (명사)</t>
+          <t>[[pʰintʰɛkʰ]] 金融科技；Fintech (명사)</t>
         </is>
       </c>
       <c r="C644" s="1" t="inlineStr">
         <is>
-          <t>inehe</t>
+          <t>[pʰintʰɛkʰ]</t>
         </is>
       </c>
       <c r="D644" s="1" t="inlineStr">
@@ -21043,12 +21043,12 @@
       </c>
       <c r="B645" s="1" t="inlineStr">
         <is>
-          <t>[konkangatkore] 电子商务 (科技)</t>
+          <t>[[t͡ɕʌ̹nd͡ʑa̠sʰa̠ŋɡʌ̹ɾe̞]] 电子商务 (科技)</t>
         </is>
       </c>
       <c r="C645" s="1" t="inlineStr">
         <is>
-          <t>konkangatkore</t>
+          <t>[t͡ɕʌ̹nd͡ʑa̠sʰa̠ŋɡʌ̹ɾe̞]</t>
         </is>
       </c>
       <c r="D645" s="1" t="inlineStr">
@@ -21075,7 +21075,7 @@
       </c>
       <c r="B646" s="1" t="inlineStr">
         <is>
-          <t>[[pʰɯɭɭɛt̚pʰo̞m]] 站台 (科技)</t>
+          <t>[[pʰɯɭɭɛt̚pʰo̞m]] 平台 (科技)</t>
         </is>
       </c>
       <c r="C646" s="1" t="inlineStr">
@@ -21085,7 +21085,7 @@
       </c>
       <c r="D646" s="1" t="inlineStr">
         <is>
-          <t>站台 (科技)</t>
+          <t>平台 (科技)</t>
         </is>
       </c>
       <c r="E646" s="1" t="inlineStr">
@@ -21171,7 +21171,7 @@
       </c>
       <c r="B649" s="1" t="inlineStr">
         <is>
-          <t>[[tisʰɯpʰɯɭɭe̞i]] 波形图显示 (科技)</t>
+          <t>[[tisʰɯpʰɯɭɭe̞i]] 显示器 (科技)</t>
         </is>
       </c>
       <c r="C649" s="1" t="inlineStr">
@@ -21181,7 +21181,7 @@
       </c>
       <c r="D649" s="1" t="inlineStr">
         <is>
-          <t>波形图显示 (科技)</t>
+          <t>显示器 (科技)</t>
         </is>
       </c>
       <c r="E649" s="1" t="inlineStr">
@@ -21235,7 +21235,7 @@
       </c>
       <c r="B651" s="1" t="inlineStr">
         <is>
-          <t>[[kʰucçi]] 曲奇；Cookie (명사)</t>
+          <t>[[kʰucçi]] 曲奇；网络小甜饼 (명사)</t>
         </is>
       </c>
       <c r="C651" s="1" t="inlineStr">
@@ -21245,7 +21245,7 @@
       </c>
       <c r="D651" s="1" t="inlineStr">
         <is>
-          <t>曲奇；Cookie (명사)</t>
+          <t>曲奇；网络小甜饼 (명사)</t>
         </is>
       </c>
       <c r="E651" s="1" t="inlineStr">
@@ -21267,12 +21267,12 @@
       </c>
       <c r="B652" s="1" t="inlineStr">
         <is>
-          <t>[kechinkotpu] 隐私 (科技)</t>
+          <t>[[ke̞ind͡ʑa̠bbo̞]] 隐私 (科技)</t>
         </is>
       </c>
       <c r="C652" s="1" t="inlineStr">
         <is>
-          <t>kechinkotpu</t>
+          <t>[ke̞ind͡ʑa̠bbo̞]</t>
         </is>
       </c>
       <c r="D652" s="1" t="inlineStr">
@@ -21299,17 +21299,17 @@
       </c>
       <c r="B653" s="1" t="inlineStr">
         <is>
-          <t>[ngachipopuchan] 网路安全 (科技)</t>
+          <t>[[sa̠ibʌ̹bo̞a̠n]] 网络安全 (科技)</t>
         </is>
       </c>
       <c r="C653" s="1" t="inlineStr">
         <is>
-          <t>ngachipopuchan</t>
+          <t>[sa̠ibʌ̹bo̞a̠n]</t>
         </is>
       </c>
       <c r="D653" s="1" t="inlineStr">
         <is>
-          <t>网路安全 (科技)</t>
+          <t>网络安全 (科技)</t>
         </is>
       </c>
       <c r="E653" s="1" t="inlineStr">
@@ -21523,12 +21523,12 @@
       </c>
       <c r="B660" s="1" t="inlineStr">
         <is>
-          <t>[kachwmkietpa] 自驾车 (科技)</t>
+          <t>[[t͡ɕa̠ɾjult͡ɕuɦɛŋt͡ɕʰa̠]] 自驾车 (科技)</t>
         </is>
       </c>
       <c r="C660" s="1" t="inlineStr">
         <is>
-          <t>kachwmkietpa</t>
+          <t>[t͡ɕa̠ɾjult͡ɕuɦɛŋt͡ɕʰa̠]</t>
         </is>
       </c>
       <c r="D660" s="1" t="inlineStr">
@@ -21555,12 +21555,12 @@
       </c>
       <c r="B661" s="1" t="inlineStr">
         <is>
-          <t>[ngemaeung] 智慧家庭 (科技)</t>
+          <t>[[sʰɯma̠tʰɯhom]] 智慧家庭 (科技)</t>
         </is>
       </c>
       <c r="C661" s="1" t="inlineStr">
         <is>
-          <t>ngemaeung</t>
+          <t>[sʰɯma̠tʰɯhom]</t>
         </is>
       </c>
       <c r="D661" s="1" t="inlineStr">
@@ -21587,12 +21587,12 @@
       </c>
       <c r="B662" s="1" t="inlineStr">
         <is>
-          <t>[kwtngongchw] 光纤 (科技)</t>
+          <t>[[kwa̠ŋsʰʌ̹mju]] 光纤 (科技)</t>
         </is>
       </c>
       <c r="C662" s="1" t="inlineStr">
         <is>
-          <t>kwtngongchw</t>
+          <t>[kwa̠ŋsʰʌ̹mju]</t>
         </is>
       </c>
       <c r="D662" s="1" t="inlineStr">
@@ -21651,12 +21651,12 @@
       </c>
       <c r="B664" s="1" t="inlineStr">
         <is>
-          <t>[echyatkwtenom] 太阳能电池板 (科技)</t>
+          <t>[[tʰɛja̠ŋkwa̠ŋpʰa̠nne̞ɭ]] 太阳能电池板 (科技)</t>
         </is>
       </c>
       <c r="C664" s="1" t="inlineStr">
         <is>
-          <t>echyatkwtenom</t>
+          <t>[tʰɛja̠ŋkwa̠ŋpʰa̠nne̞ɭ]</t>
         </is>
       </c>
       <c r="D664" s="1" t="inlineStr">
@@ -21683,12 +21683,12 @@
       </c>
       <c r="B665" s="1" t="inlineStr">
         <is>
-          <t>[peorikokat] 电池储能 (科技)</t>
+          <t>[[pe̞tʰʌ̹ɾit͡ɕe̞d͡ʑa̠ŋ]] 电池储能 (科技)</t>
         </is>
       </c>
       <c r="C665" s="1" t="inlineStr">
         <is>
-          <t>peorikokat</t>
+          <t>[pe̞tʰʌ̹ɾit͡ɕe̞d͡ʑa̠ŋ]</t>
         </is>
       </c>
       <c r="D665" s="1" t="inlineStr">
@@ -21715,12 +21715,12 @@
       </c>
       <c r="B666" s="1" t="inlineStr">
         <is>
-          <t>[chechoropemkiki] 穿戴式装置 (科技)</t>
+          <t>[[we.ʌ.ɾʌ.bɯl.ɡi.ɡi]] 穿戴式装置 (科技)</t>
         </is>
       </c>
       <c r="C666" s="1" t="inlineStr">
         <is>
-          <t>chechoropemkiki</t>
+          <t>[we.ʌ.ɾʌ.bɯl.ɡi.ɡi]</t>
         </is>
       </c>
       <c r="D666" s="1" t="inlineStr">
@@ -21747,12 +21747,12 @@
       </c>
       <c r="B667" s="1" t="inlineStr">
         <is>
-          <t>[ngamimchinonet] 物联网 (科技)</t>
+          <t>[[sa.mu.ɾin.tʰʌ.nɛt̚]] 物联网 (科技)</t>
         </is>
       </c>
       <c r="C667" s="1" t="inlineStr">
         <is>
-          <t>ngamimchinonet</t>
+          <t>[sa.mu.ɾin.tʰʌ.nɛt̚]</t>
         </is>
       </c>
       <c r="D667" s="1" t="inlineStr">
@@ -22291,7 +22291,7 @@
       </c>
       <c r="B684" s="1" t="inlineStr">
         <is>
-          <t>[[pʰibuk͈wa̠]] 皮肤 (健康医疗)</t>
+          <t>[[pʰibuk͈wa̠]] 皮肤科 (健康医疗)</t>
         </is>
       </c>
       <c r="C684" s="1" t="inlineStr">
@@ -22301,7 +22301,7 @@
       </c>
       <c r="D684" s="1" t="inlineStr">
         <is>
-          <t>皮肤 (健康医疗)</t>
+          <t>皮肤科 (健康医疗)</t>
         </is>
       </c>
       <c r="E684" s="1" t="inlineStr">
@@ -22387,12 +22387,12 @@
       </c>
       <c r="B687" s="1" t="inlineStr">
         <is>
-          <t>[kewm] 伤兵复原 (健康医疗)</t>
+          <t>[[tɕɛ.ɦwaɾ]] 伤兵复原 (健康医疗)</t>
         </is>
       </c>
       <c r="C687" s="1" t="inlineStr">
         <is>
-          <t>kewm</t>
+          <t>[tɕɛ.ɦwaɾ]</t>
         </is>
       </c>
       <c r="D687" s="1" t="inlineStr">
@@ -22419,12 +22419,12 @@
       </c>
       <c r="B688" s="1" t="inlineStr">
         <is>
-          <t>[konkatpuong] 医疗保险 (健康医疗)</t>
+          <t>[[kʌn.ɡaŋ.bo.hʌm]] 医疗保险 (健康医疗)</t>
         </is>
       </c>
       <c r="C688" s="1" t="inlineStr">
         <is>
-          <t>konkatpuong</t>
+          <t>[kʌn.ɡaŋ.bo.hʌm]</t>
         </is>
       </c>
       <c r="D688" s="1" t="inlineStr">
@@ -22579,12 +22579,12 @@
       </c>
       <c r="B693" s="1" t="inlineStr">
         <is>
-          <t>[pinyom] 贫血 (健康与医疗)</t>
+          <t>[[pin.ɲjʌl]] 贫血 (健康与医疗)</t>
         </is>
       </c>
       <c r="C693" s="1" t="inlineStr">
         <is>
-          <t>pinyom</t>
+          <t>[pin.ɲjʌl]</t>
         </is>
       </c>
       <c r="D693" s="1" t="inlineStr">
@@ -22675,12 +22675,12 @@
       </c>
       <c r="B696" s="1" t="inlineStr">
         <is>
-          <t>[engchingki] 吸入器 (健康与医疗)</t>
+          <t>[[hɯbip̚k͈i]] 吸入器 (健康与医疗)</t>
         </is>
       </c>
       <c r="C696" s="1" t="inlineStr">
         <is>
-          <t>engchingki</t>
+          <t>[hɯbip̚k͈i]</t>
         </is>
       </c>
       <c r="D696" s="1" t="inlineStr">
@@ -22803,7 +22803,7 @@
       </c>
       <c r="B700" s="1" t="inlineStr">
         <is>
-          <t>[[ˈpo̞(ː)ɡʌ̹nsʰo̞]] 公共卫生中心 (健康与医疗)</t>
+          <t>[[ˈpo̞(ː)ɡʌ̹nsʰo̞]] 保健所 (健康与医疗)</t>
         </is>
       </c>
       <c r="C700" s="1" t="inlineStr">
@@ -22813,7 +22813,7 @@
       </c>
       <c r="D700" s="1" t="inlineStr">
         <is>
-          <t>公共卫生中心 (健康与医疗)</t>
+          <t>保健所 (健康与医疗)</t>
         </is>
       </c>
       <c r="E700" s="1" t="inlineStr">
@@ -22835,12 +22835,12 @@
       </c>
       <c r="B701" s="1" t="inlineStr">
         <is>
-          <t>[ritko] 静脉输液 (健康与医疗)</t>
+          <t>[[liŋɡʌ̹]] 静脉输液 (健康与医疗)</t>
         </is>
       </c>
       <c r="C701" s="1" t="inlineStr">
         <is>
-          <t>ritko</t>
+          <t>[liŋɡʌ̹]</t>
         </is>
       </c>
       <c r="D701" s="1" t="inlineStr">
@@ -22867,12 +22867,12 @@
       </c>
       <c r="B702" s="1" t="inlineStr">
         <is>
-          <t>[konkatpuongket] ・健康保险卡 (健康医疗)</t>
+          <t>[[kʌ̹ŋɡa̠nbʌ̹hʌ̹md͡ʑʌ̹ŋ]] ・健康保险卡 (健康医疗)</t>
         </is>
       </c>
       <c r="C702" s="1" t="inlineStr">
         <is>
-          <t>konkatpuongket</t>
+          <t>[kʌ̹ŋɡa̠nbʌ̹hʌ̹md͡ʑʌ̹ŋ]</t>
         </is>
       </c>
       <c r="D702" s="1" t="inlineStr">
@@ -22899,7 +22899,7 @@
       </c>
       <c r="B703" s="1" t="inlineStr">
         <is>
-          <t>[[sʰo̞ŋpʰjʌ̹n]] 松片（半圆形米糕） (节日与庆典)</t>
+          <t>[[sʰo̞ŋpʰjʌ̹n]] 松饼（半月形米糕） (节日与庆典)</t>
         </is>
       </c>
       <c r="C703" s="1" t="inlineStr">
@@ -22909,7 +22909,7 @@
       </c>
       <c r="D703" s="1" t="inlineStr">
         <is>
-          <t>松片（半圆形米糕） (节日与庆典)</t>
+          <t>松饼（半月形米糕） (节日与庆典)</t>
         </is>
       </c>
       <c r="E703" s="1" t="inlineStr">
@@ -22995,17 +22995,17 @@
       </c>
       <c r="B706" s="1" t="inlineStr">
         <is>
-          <t>[ngangchimkom] 3月1日独立运动日 (节日庆典)</t>
+          <t>[[sa̠miɭd͡ʑʌ̹ɭ]] 三一节 (节日庆典)</t>
         </is>
       </c>
       <c r="C706" s="1" t="inlineStr">
         <is>
-          <t>ngangchimkom</t>
+          <t>[sa̠miɭd͡ʑʌ̹ɭ]</t>
         </is>
       </c>
       <c r="D706" s="1" t="inlineStr">
         <is>
-          <t>3月1日独立运动日 (节日庆典)</t>
+          <t>三一节 (节日庆典)</t>
         </is>
       </c>
       <c r="E706" s="1" t="inlineStr">
@@ -23059,17 +23059,17 @@
       </c>
       <c r="B708" s="1" t="inlineStr">
         <is>
-          <t>[yonpitchim] 阵亡将士纪念日 (节日庆典)</t>
+          <t>[[jʌ̹nt͡ɕʰuŋiɭ]] 显忠日 (节日庆典)</t>
         </is>
       </c>
       <c r="C708" s="1" t="inlineStr">
         <is>
-          <t>yonpitchim</t>
+          <t>[jʌ̹nt͡ɕʰuŋiɭ]</t>
         </is>
       </c>
       <c r="D708" s="1" t="inlineStr">
         <is>
-          <t>阵亡将士纪念日 (节日庆典)</t>
+          <t>显忠日 (节日庆典)</t>
         </is>
       </c>
       <c r="E708" s="1" t="inlineStr">
@@ -23155,17 +23155,17 @@
       </c>
       <c r="B711" s="1" t="inlineStr">
         <is>
-          <t>[keneteki] 传统秋千 (节日庆典)</t>
+          <t>[[kɯne̞t͈wigi]] 荡秋千 (节日庆典)</t>
         </is>
       </c>
       <c r="C711" s="1" t="inlineStr">
         <is>
-          <t>keneteki</t>
+          <t>[kɯne̞t͈wigi]</t>
         </is>
       </c>
       <c r="D711" s="1" t="inlineStr">
         <is>
-          <t>传统秋千 (节日庆典)</t>
+          <t>荡秋千 (节日庆典)</t>
         </is>
       </c>
       <c r="E711" s="1" t="inlineStr">
@@ -23219,7 +23219,7 @@
       </c>
       <c r="B713" s="1" t="inlineStr">
         <is>
-          <t>[[ja̠ŋɲʌ̹k̚]] 公历时代 (节日庆典)</t>
+          <t>[[ja̠ŋɲʌ̹k̚]] 阳历 (节日庆典)</t>
         </is>
       </c>
       <c r="C713" s="1" t="inlineStr">
@@ -23229,7 +23229,7 @@
       </c>
       <c r="D713" s="1" t="inlineStr">
         <is>
-          <t>公历时代 (节日庆典)</t>
+          <t>阳历 (节日庆典)</t>
         </is>
       </c>
       <c r="E713" s="1" t="inlineStr">
@@ -23283,12 +23283,12 @@
       </c>
       <c r="B715" s="1" t="inlineStr">
         <is>
-          <t>[chyonnamriki] 风筝 (节日庆典)</t>
+          <t>[[jʌ̹nnaɭɭiɡi]] 风筝 (节日庆典)</t>
         </is>
       </c>
       <c r="C715" s="1" t="inlineStr">
         <is>
-          <t>chyonnamriki</t>
+          <t>[jʌ̹nnaɭɭiɡi]</t>
         </is>
       </c>
       <c r="D715" s="1" t="inlineStr">
@@ -23411,17 +23411,17 @@
       </c>
       <c r="B719" s="1" t="inlineStr">
         <is>
-          <t>[pingikangngakom] 丰收乐园 (节日庆典)</t>
+          <t>[[t͡ɕʰusʰɯɡa̠md͡ʑʌ̹ɭ]] 感恩节 (节日庆典)</t>
         </is>
       </c>
       <c r="C719" s="1" t="inlineStr">
         <is>
-          <t>pingikangngakom</t>
+          <t>[t͡ɕʰusʰɯɡa̠md͡ʑʌ̹ɭ]</t>
         </is>
       </c>
       <c r="D719" s="1" t="inlineStr">
         <is>
-          <t>丰收乐园 (节日庆典)</t>
+          <t>感恩节 (节日庆典)</t>
         </is>
       </c>
       <c r="E719" s="1" t="inlineStr">
@@ -23443,12 +23443,12 @@
       </c>
       <c r="B720" s="1" t="inlineStr">
         <is>
-          <t>[pikchykeng] 恭喜礼物 (节日庆典)</t>
+          <t>[[t͡ɕʰuɡɯiɡɯm]] 恭喜礼物 (节日庆典)</t>
         </is>
       </c>
       <c r="C720" s="1" t="inlineStr">
         <is>
-          <t>pikchykeng</t>
+          <t>[t͡ɕʰuɡɯiɡɯm]</t>
         </is>
       </c>
       <c r="D720" s="1" t="inlineStr">
@@ -23475,12 +23475,12 @@
       </c>
       <c r="B721" s="1" t="inlineStr">
         <is>
-          <t>[pekchimkinyongchim] 百日纪念 (节日与庆典)</t>
+          <t>[[pɛɡiɭkijʌ̹miɭ]] 百日纪念 (节日与庆典)</t>
         </is>
       </c>
       <c r="C721" s="1" t="inlineStr">
         <is>
-          <t>pekchimkinyongchim</t>
+          <t>[pɛɡiɭkijʌ̹miɭ]</t>
         </is>
       </c>
       <c r="D721" s="1" t="inlineStr">
@@ -23539,12 +23539,12 @@
       </c>
       <c r="B723" s="1" t="inlineStr">
         <is>
-          <t>[kengot] 返乡 (节日与庆典)</t>
+          <t>[[kwisʌ̹ŋ]] 返乡 (节日与庆典)</t>
         </is>
       </c>
       <c r="C723" s="1" t="inlineStr">
         <is>
-          <t>kengot</t>
+          <t>[kwisʌ̹ŋ]</t>
         </is>
       </c>
       <c r="D723" s="1" t="inlineStr">
@@ -23667,7 +23667,7 @@
       </c>
       <c r="B727" s="1" t="inlineStr">
         <is>
-          <t>[[tʰa̠ps͈ɯŋk͈wʌ̹n]] 登机证 (交通)</t>
+          <t>[[tʰa̠ps͈ɯŋk͈wʌ̹n]] 登机牌 (交通)</t>
         </is>
       </c>
       <c r="C727" s="1" t="inlineStr">
@@ -23677,7 +23677,7 @@
       </c>
       <c r="D727" s="1" t="inlineStr">
         <is>
-          <t>登机证 (交通)</t>
+          <t>登机牌 (交通)</t>
         </is>
       </c>
       <c r="E727" s="1" t="inlineStr">
@@ -23699,12 +23699,12 @@
       </c>
       <c r="B728" s="1" t="inlineStr">
         <is>
-          <t>[chinkonmyonoket] 驾照 (交通)</t>
+          <t>[[un.dʑʌn.mjʌn.hʌ.dʑɯŋ]] 驾照 (交通)</t>
         </is>
       </c>
       <c r="C728" s="1" t="inlineStr">
         <is>
-          <t>chinkonmyonoket</t>
+          <t>[un.dʑʌn.mjʌn.hʌ.dʑɯŋ]</t>
         </is>
       </c>
       <c r="D728" s="1" t="inlineStr">
@@ -23763,12 +23763,12 @@
       </c>
       <c r="B730" s="1" t="inlineStr">
         <is>
-          <t>[keannguktu] 速度限制 (交通)</t>
+          <t>[[tɕeːɦan.soɡt͈o]] 速度限制 (交通)</t>
         </is>
       </c>
       <c r="C730" s="1" t="inlineStr">
         <is>
-          <t>keannguktu</t>
+          <t>[tɕeːɦan.soɡt͈o]</t>
         </is>
       </c>
       <c r="D730" s="1" t="inlineStr">
@@ -23795,7 +23795,7 @@
       </c>
       <c r="B731" s="1" t="inlineStr">
         <is>
-          <t>[[ɯmd͡ʑuuɲd͡ʑʌ̹n]] 酒醉后驾驶 (交通)</t>
+          <t>[[ɯmd͡ʑuuɲd͡ʑʌ̹n]] 酒后驾驶 (交通)</t>
         </is>
       </c>
       <c r="C731" s="1" t="inlineStr">
@@ -23805,7 +23805,7 @@
       </c>
       <c r="D731" s="1" t="inlineStr">
         <is>
-          <t>酒醉后驾驶 (交通)</t>
+          <t>酒后驾驶 (交通)</t>
         </is>
       </c>
       <c r="E731" s="1" t="inlineStr">
@@ -23827,17 +23827,17 @@
       </c>
       <c r="B732" s="1" t="inlineStr">
         <is>
-          <t>[terichinkon] 指定司机服务 (交通)</t>
+          <t>[[tɛɾi.un.dʑʌn]] 代驾服务 (交通)</t>
         </is>
       </c>
       <c r="C732" s="1" t="inlineStr">
         <is>
-          <t>terichinkon</t>
+          <t>[tɛɾi.un.dʑʌn]</t>
         </is>
       </c>
       <c r="D732" s="1" t="inlineStr">
         <is>
-          <t>指定司机服务 (交通)</t>
+          <t>代驾服务 (交通)</t>
         </is>
       </c>
       <c r="E732" s="1" t="inlineStr">
@@ -23859,12 +23859,12 @@
       </c>
       <c r="B733" s="1" t="inlineStr">
         <is>
-          <t>[haim] 拼车 (交通)</t>
+          <t>[[kʰa.pʰul]] 拼车 (交通)</t>
         </is>
       </c>
       <c r="C733" s="1" t="inlineStr">
         <is>
-          <t>haim</t>
+          <t>[kʰa.pʰul]</t>
         </is>
       </c>
       <c r="D733" s="1" t="inlineStr">
@@ -23891,17 +23891,17 @@
       </c>
       <c r="B734" s="1" t="inlineStr">
         <is>
-          <t>[ngichwiponge] 城际公交车 (交通)</t>
+          <t>[[ɕi.ʌ.pʰʌ.sɯ]] 城际巴士 (交通)</t>
         </is>
       </c>
       <c r="C734" s="1" t="inlineStr">
         <is>
-          <t>ngichwiponge</t>
+          <t>[ɕi.ʌ.pʰʌ.sɯ]</t>
         </is>
       </c>
       <c r="D734" s="1" t="inlineStr">
         <is>
-          <t>城际公交车 (交通)</t>
+          <t>城际巴士 (交通)</t>
         </is>
       </c>
       <c r="E734" s="1" t="inlineStr">
@@ -23955,12 +23955,12 @@
       </c>
       <c r="B736" s="1" t="inlineStr">
         <is>
-          <t>[munurechim] 单轨铁路 (交通)</t>
+          <t>[[mo.no.ɾɛil]] 单轨铁路 (交通)</t>
         </is>
       </c>
       <c r="C736" s="1" t="inlineStr">
         <is>
-          <t>munurechim</t>
+          <t>[mo.no.ɾɛil]</t>
         </is>
       </c>
       <c r="D736" s="1" t="inlineStr">
@@ -23987,12 +23987,12 @@
       </c>
       <c r="B737" s="1" t="inlineStr">
         <is>
-          <t>[kutatpomtu] 机场铁路 (交通)</t>
+          <t>[[koŋ.ɦaŋ.tɕʰʌl.t͈o]] 机场铁路 (交通)</t>
         </is>
       </c>
       <c r="C737" s="1" t="inlineStr">
         <is>
-          <t>kutatpomtu</t>
+          <t>[koŋ.ɦaŋ.tɕʰʌl.t͈o]</t>
         </is>
       </c>
       <c r="D737" s="1" t="inlineStr">
@@ -24019,12 +24019,12 @@
       </c>
       <c r="B738" s="1" t="inlineStr">
         <is>
-          <t>[mimingpukwnngu] 行李寄存 (交通)</t>
+          <t>[[mul.pʰum.po.ɡwan.so]] 行李寄存 (交通)</t>
         </is>
       </c>
       <c r="C738" s="1" t="inlineStr">
         <is>
-          <t>mimingpukwnngu</t>
+          <t>[mul.pʰum.po.ɡwan.so]</t>
         </is>
       </c>
       <c r="D738" s="1" t="inlineStr">
@@ -24051,7 +24051,7 @@
       </c>
       <c r="B739" s="1" t="inlineStr">
         <is>
-          <t>[[kjot͡ɕʰa̠ɾo̞]] 交集 (交通)</t>
+          <t>[[kjot͡ɕʰa̠ɾo̞]] 交叉路口 (交通)</t>
         </is>
       </c>
       <c r="C739" s="1" t="inlineStr">
@@ -24061,7 +24061,7 @@
       </c>
       <c r="D739" s="1" t="inlineStr">
         <is>
-          <t>交集 (交通)</t>
+          <t>交叉路口 (交通)</t>
         </is>
       </c>
       <c r="E739" s="1" t="inlineStr">
@@ -24115,12 +24115,12 @@
       </c>
       <c r="B741" s="1" t="inlineStr">
         <is>
-          <t>[kyonchinpa] 拖吊车 (交通)</t>
+          <t>[[kʲʌ.nin.tɕʰa]] 拖吊车 (交通)</t>
         </is>
       </c>
       <c r="C741" s="1" t="inlineStr">
         <is>
-          <t>kyonchinpa</t>
+          <t>[kʲʌ.nin.tɕʰa]</t>
         </is>
       </c>
       <c r="D741" s="1" t="inlineStr">
@@ -24179,7 +24179,7 @@
       </c>
       <c r="B743" s="1" t="inlineStr">
         <is>
-          <t>[[e̞ɲd͡ʑin]] 部位机动 (交通)</t>
+          <t>[[e̞ɲd͡ʑin]] 发动机 (交通)</t>
         </is>
       </c>
       <c r="C743" s="1" t="inlineStr">
@@ -24189,7 +24189,7 @@
       </c>
       <c r="D743" s="1" t="inlineStr">
         <is>
-          <t>部位机动 (交通)</t>
+          <t>发动机 (交通)</t>
         </is>
       </c>
       <c r="E743" s="1" t="inlineStr">
@@ -24211,12 +24211,12 @@
       </c>
       <c r="B744" s="1" t="inlineStr">
         <is>
-          <t>[chachwri] 挡风板 (交通)</t>
+          <t>[[ap̚.nju.ɾi]] 挡风板 (交通)</t>
         </is>
       </c>
       <c r="C744" s="1" t="inlineStr">
         <is>
-          <t>chachwri</t>
+          <t>[ap̚.nju.ɾi]</t>
         </is>
       </c>
       <c r="D744" s="1" t="inlineStr">
@@ -24243,12 +24243,12 @@
       </c>
       <c r="B745" s="1" t="inlineStr">
         <is>
-          <t>[konkutet] 头灯 (交通)</t>
+          <t>[[tɕʌn.tɕo.tɯŋ]] 头灯 (交通)</t>
         </is>
       </c>
       <c r="C745" s="1" t="inlineStr">
         <is>
-          <t>konkutet</t>
+          <t>[tɕʌn.tɕo.tɯŋ]</t>
         </is>
       </c>
       <c r="D745" s="1" t="inlineStr">
@@ -24275,12 +24275,12 @@
       </c>
       <c r="B746" s="1" t="inlineStr">
         <is>
-          <t>[patyatkingitet] 方向灯 / 转向指示灯 (交通)</t>
+          <t>[[paŋ.ɦjaŋ.tɕi.ɕi.tɯŋ]] 方向灯 / 转向指示灯 (交通)</t>
         </is>
       </c>
       <c r="C746" s="1" t="inlineStr">
         <is>
-          <t>patyatkingitet</t>
+          <t>[paŋ.ɦjaŋ.tɕi.ɕi.tɯŋ]</t>
         </is>
       </c>
       <c r="D746" s="1" t="inlineStr">
@@ -24371,12 +24371,12 @@
       </c>
       <c r="B749" s="1" t="inlineStr">
         <is>
-          <t>[kotkiken] 月票 (交通)</t>
+          <t>[[tɕʌŋ.ɡi.ɡwʌn]] 月票 (交通)</t>
         </is>
       </c>
       <c r="C749" s="1" t="inlineStr">
         <is>
-          <t>kotkiken</t>
+          <t>[tɕʌŋ.ɡi.ɡwʌn]</t>
         </is>
       </c>
       <c r="D749" s="1" t="inlineStr">
@@ -24435,17 +24435,17 @@
       </c>
       <c r="B751" s="1" t="inlineStr">
         <is>
-          <t>[pimchingkik] 移民 (交通)</t>
+          <t>[[tɕʰu.ɾip̚.kuk̚]] 出入境 (交通)</t>
         </is>
       </c>
       <c r="C751" s="1" t="inlineStr">
         <is>
-          <t>pimchingkik</t>
+          <t>[tɕʰu.ɾip̚.kuk̚]</t>
         </is>
       </c>
       <c r="D751" s="1" t="inlineStr">
         <is>
-          <t>移民 (交通)</t>
+          <t>出入境 (交通)</t>
         </is>
       </c>
       <c r="E751" s="1" t="inlineStr">
@@ -24467,12 +24467,12 @@
       </c>
       <c r="B752" s="1" t="inlineStr">
         <is>
-          <t>[kengetchyompa] 区间快车 (交通)</t>
+          <t>[[kɯ.pʰɛŋ.jʌl.tɕʰa]] 区间快车 (交通)</t>
         </is>
       </c>
       <c r="C752" s="1" t="inlineStr">
         <is>
-          <t>kengetchyompa</t>
+          <t>[kɯ.pʰɛŋ.jʌl.tɕʰa]</t>
         </is>
       </c>
       <c r="D752" s="1" t="inlineStr">
@@ -24531,12 +24531,12 @@
       </c>
       <c r="B754" s="1" t="inlineStr">
         <is>
-          <t>[ngingchyaponge] 夜间公车 (交通)</t>
+          <t>[[ɕi.mja.pʰʌ.sɯ]] 夜间公车 (交通)</t>
         </is>
       </c>
       <c r="C754" s="1" t="inlineStr">
         <is>
-          <t>ngingchyaponge</t>
+          <t>[ɕi.mja.pʰʌ.sɯ]</t>
         </is>
       </c>
       <c r="D754" s="1" t="inlineStr">
@@ -24563,12 +24563,12 @@
       </c>
       <c r="B755" s="1" t="inlineStr">
         <is>
-          <t>[onw] 献花 (节庆与活动)</t>
+          <t>[[hʌn.ɦwa]] 献花 (节庆与活动)</t>
         </is>
       </c>
       <c r="C755" s="1" t="inlineStr">
         <is>
-          <t>onw</t>
+          <t>[hʌn.ɦwa]</t>
         </is>
       </c>
       <c r="D755" s="1" t="inlineStr">
@@ -24627,7 +24627,7 @@
       </c>
       <c r="B757" s="1" t="inlineStr">
         <is>
-          <t>[[pʰuŋdɯŋ]] 天灯 (节日庆典)</t>
+          <t>[[pʰuŋdɯŋ]] 灯笼 (节日庆典)</t>
         </is>
       </c>
       <c r="C757" s="1" t="inlineStr">
@@ -24637,7 +24637,7 @@
       </c>
       <c r="D757" s="1" t="inlineStr">
         <is>
-          <t>天灯 (节日庆典)</t>
+          <t>灯笼 (节日庆典)</t>
         </is>
       </c>
       <c r="E757" s="1" t="inlineStr">
@@ -24659,12 +24659,12 @@
       </c>
       <c r="B758" s="1" t="inlineStr">
         <is>
-          <t>[chengennge] 精华液 (美容护肤)</t>
+          <t>[[e̞sʰe̞ns͈ɯ]] 精华液 (美容护肤)</t>
         </is>
       </c>
       <c r="C758" s="1" t="inlineStr">
         <is>
-          <t>chengennge</t>
+          <t>[e̞sʰe̞ns͈ɯ]</t>
         </is>
       </c>
       <c r="D758" s="1" t="inlineStr">
@@ -24691,12 +24691,12 @@
       </c>
       <c r="B759" s="1" t="inlineStr">
         <is>
-          <t>[ngerong] 精华素 (美容护肤)</t>
+          <t>[[sʰe̞ɾʌ̹m]] 精华素 (美容护肤)</t>
         </is>
       </c>
       <c r="C759" s="1" t="inlineStr">
         <is>
-          <t>ngerong</t>
+          <t>[sʰe̞ɾʌ̹m]</t>
         </is>
       </c>
       <c r="D759" s="1" t="inlineStr">
@@ -24723,12 +24723,12 @@
       </c>
       <c r="B760" s="1" t="inlineStr">
         <is>
-          <t>[honichorit] 修容 (美妆护肤)</t>
+          <t>[[kʰʌ̹ntʰuʌ̹ɾiŋ]] 修容 (美妆护肤)</t>
         </is>
       </c>
       <c r="C760" s="1" t="inlineStr">
         <is>
-          <t>honichorit</t>
+          <t>[kʰʌ̹ntʰuʌ̹ɾiŋ]</t>
         </is>
       </c>
       <c r="D760" s="1" t="inlineStr">
@@ -24755,12 +24755,12 @@
       </c>
       <c r="B761" s="1" t="inlineStr">
         <is>
-          <t>[achirachio] 高光 (美妆护肤)</t>
+          <t>[[ha̠iɾa̠itʰʌ̹]] 高光 (美妆护肤)</t>
         </is>
       </c>
       <c r="C761" s="1" t="inlineStr">
         <is>
-          <t>achirachio</t>
+          <t>[ha̠iɾa̠itʰʌ̹]</t>
         </is>
       </c>
       <c r="D761" s="1" t="inlineStr">
@@ -24787,12 +24787,12 @@
       </c>
       <c r="B762" s="1" t="inlineStr">
         <is>
-          <t>[mipek] 美白 (美妆护肤)</t>
+          <t>[[miba̠k̚]] 美白 (美妆护肤)</t>
         </is>
       </c>
       <c r="C762" s="1" t="inlineStr">
         <is>
-          <t>mipek</t>
+          <t>[miba̠k̚]</t>
         </is>
       </c>
       <c r="D762" s="1" t="inlineStr">
@@ -24819,12 +24819,12 @@
       </c>
       <c r="B763" s="1" t="inlineStr">
         <is>
-          <t>[humraken] 胶原蛋白 (美妆护肤)</t>
+          <t>[[kʰoɭːaɡen]] 胶原蛋白 (美妆护肤)</t>
         </is>
       </c>
       <c r="C763" s="1" t="inlineStr">
         <is>
-          <t>humraken</t>
+          <t>[kʰoɭːaɡen]</t>
         </is>
       </c>
       <c r="D763" s="1" t="inlineStr">
@@ -24851,12 +24851,12 @@
       </c>
       <c r="B764" s="1" t="inlineStr">
         <is>
-          <t>[chachihering] 眼霜 (美容与肌肤保养)</t>
+          <t>[[aikʰɯɾim]] 眼霜 (美容与肌肤保养)</t>
         </is>
       </c>
       <c r="C764" s="1" t="inlineStr">
         <is>
-          <t>chachihering</t>
+          <t>[aikʰɯɾim]</t>
         </is>
       </c>
       <c r="D764" s="1" t="inlineStr">
@@ -24883,12 +24883,12 @@
       </c>
       <c r="B765" s="1" t="inlineStr">
         <is>
-          <t>[ringrachino] 唇线笔 (美容与肌肤保养)</t>
+          <t>[[ɾip͈a.inʌ]] 唇线笔 (美容与肌肤保养)</t>
         </is>
       </c>
       <c r="C765" s="1" t="inlineStr">
         <is>
-          <t>ringrachino</t>
+          <t>[ɾip͈a.inʌ]</t>
         </is>
       </c>
       <c r="D765" s="1" t="inlineStr">
@@ -24915,12 +24915,12 @@
       </c>
       <c r="B766" s="1" t="inlineStr">
         <is>
-          <t>[erachimo] 妆前乳 (美容与肌肤保养)</t>
+          <t>[[pʰɯɾaimʌ]] 妆前乳 (美容与肌肤保养)</t>
         </is>
       </c>
       <c r="C766" s="1" t="inlineStr">
         <is>
-          <t>erachimo</t>
+          <t>[pʰɯɾaimʌ]</t>
         </is>
       </c>
       <c r="D766" s="1" t="inlineStr">
@@ -24947,12 +24947,12 @@
       </c>
       <c r="B767" s="1" t="inlineStr">
         <is>
-          <t>[chemomkon] 乳液 (美容与护肤)</t>
+          <t>[[emʌɭdʑʌn]] 乳液 (美容与护肤)</t>
         </is>
       </c>
       <c r="C767" s="1" t="inlineStr">
         <is>
-          <t>chemomkon</t>
+          <t>[emʌɭdʑʌn]</t>
         </is>
       </c>
       <c r="D767" s="1" t="inlineStr">
@@ -24979,12 +24979,12 @@
       </c>
       <c r="B768" s="1" t="inlineStr">
         <is>
-          <t>[utku] 泛红 (美容与护肤)</t>
+          <t>[[hoŋdʑo]] 泛红 (美容与护肤)</t>
         </is>
       </c>
       <c r="C768" s="1" t="inlineStr">
         <is>
-          <t>utku</t>
+          <t>[hoŋdʑo]</t>
         </is>
       </c>
       <c r="D768" s="1" t="inlineStr">
@@ -25011,12 +25011,12 @@
       </c>
       <c r="B769" s="1" t="inlineStr">
         <is>
-          <t>[mukut] 毛孔 (美容与护肤)</t>
+          <t>[[moɡoŋ]] 毛孔 (美容与护肤)</t>
         </is>
       </c>
       <c r="C769" s="1" t="inlineStr">
         <is>
-          <t>mukut</t>
+          <t>[moɡoŋ]</t>
         </is>
       </c>
       <c r="D769" s="1" t="inlineStr">
@@ -25043,12 +25043,12 @@
       </c>
       <c r="B770" s="1" t="inlineStr">
         <is>
-          <t>[kwmnga] 刮痧 (美容与护肤)</t>
+          <t>[[kwaɭsa]] 刮痧 (美容与护肤)</t>
         </is>
       </c>
       <c r="C770" s="1" t="inlineStr">
         <is>
-          <t>kwmnga</t>
+          <t>[kwaɭsa]</t>
         </is>
       </c>
       <c r="D770" s="1" t="inlineStr">
@@ -25171,7 +25171,7 @@
       </c>
       <c r="B774" s="1" t="inlineStr">
         <is>
-          <t>[[to̞je̞]] 陶器 (嗜好与休闲)</t>
+          <t>[[to̞je̞]] 陶艺 (嗜好与休闲)</t>
         </is>
       </c>
       <c r="C774" s="1" t="inlineStr">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="D774" s="1" t="inlineStr">
         <is>
-          <t>陶器 (嗜好与休闲)</t>
+          <t>陶艺 (嗜好与休闲)</t>
         </is>
       </c>
       <c r="E774" s="1" t="inlineStr">
@@ -25203,12 +25203,12 @@
       </c>
       <c r="B775" s="1" t="inlineStr">
         <is>
-          <t>[pechihit] 烘培技术 (嗜好与休闲)</t>
+          <t>[[peikʰiŋ]] 烘培技术 (嗜好与休闲)</t>
         </is>
       </c>
       <c r="C775" s="1" t="inlineStr">
         <is>
-          <t>pechihit</t>
+          <t>[peikʰiŋ]</t>
         </is>
       </c>
       <c r="D775" s="1" t="inlineStr">
@@ -25299,12 +25299,12 @@
       </c>
       <c r="B778" s="1" t="inlineStr">
         <is>
-          <t>[hemrachimit] 球场室内攀岩 (嗜好与休闲)</t>
+          <t>[[kʰɯɾaimiŋ]] 球场室内攀岩 (嗜好与休闲)</t>
         </is>
       </c>
       <c r="C778" s="1" t="inlineStr">
         <is>
-          <t>hemrachimit</t>
+          <t>[kʰɯɾaimiŋ]</t>
         </is>
       </c>
       <c r="D778" s="1" t="inlineStr">
@@ -25363,12 +25363,12 @@
       </c>
       <c r="B780" s="1" t="inlineStr">
         <is>
-          <t>[pechiruke] 视频日志 (嗜好与休闲)</t>
+          <t>[[pɯiɾoɡɯ]] 视频日志 (嗜好与休闲)</t>
         </is>
       </c>
       <c r="C780" s="1" t="inlineStr">
         <is>
-          <t>pechiruke</t>
+          <t>[pɯiɾoɡɯ]</t>
         </is>
       </c>
       <c r="D780" s="1" t="inlineStr">
@@ -25427,17 +25427,17 @@
       </c>
       <c r="B782" s="1" t="inlineStr">
         <is>
-          <t>[reorit] 手写字 (嗜好与休闲)</t>
+          <t>[[ɾetʰʌɾiŋ]] 手绘字体设计 (嗜好与休闲)</t>
         </is>
       </c>
       <c r="C782" s="1" t="inlineStr">
         <is>
-          <t>reorit</t>
+          <t>[ɾetʰʌɾiŋ]</t>
         </is>
       </c>
       <c r="D782" s="1" t="inlineStr">
         <is>
-          <t>手写字 (嗜好与休闲)</t>
+          <t>手绘字体设计 (嗜好与休闲)</t>
         </is>
       </c>
       <c r="E782" s="1" t="inlineStr">
@@ -25459,17 +25459,17 @@
       </c>
       <c r="B783" s="1" t="inlineStr">
         <is>
-          <t>[ngeahereee] 星海争霸 (嗜好与休闲)</t>
+          <t>[[sɯtʰakʰɯɾepʰɯtɯ]] 星际争霸 (嗜好与休闲)</t>
         </is>
       </c>
       <c r="C783" s="1" t="inlineStr">
         <is>
-          <t>ngeahereee</t>
+          <t>[sɯtʰakʰɯɾepʰɯtɯ]</t>
         </is>
       </c>
       <c r="D783" s="1" t="inlineStr">
         <is>
-          <t>星海争霸 (嗜好与休闲)</t>
+          <t>星际争霸 (嗜好与休闲)</t>
         </is>
       </c>
       <c r="E783" s="1" t="inlineStr">
@@ -25491,12 +25491,12 @@
       </c>
       <c r="B784" s="1" t="inlineStr">
         <is>
-          <t>[nachierachie] 夜生活 (嗜好与休闲)</t>
+          <t>[[na.itʰɯɾaipʰɯ]] 夜生活 (嗜好与休闲)</t>
         </is>
       </c>
       <c r="C784" s="1" t="inlineStr">
         <is>
-          <t>nachierachie</t>
+          <t>[na.itʰɯɾaipʰɯ]</t>
         </is>
       </c>
       <c r="D784" s="1" t="inlineStr">
@@ -25523,12 +25523,12 @@
       </c>
       <c r="B785" s="1" t="inlineStr">
         <is>
-          <t>[etempute] 立式桨板 (嗜好与休闲)</t>
+          <t>[[pʰɛdɯɭbo.dɯ]] 立式桨板 (嗜好与休闲)</t>
         </is>
       </c>
       <c r="C785" s="1" t="inlineStr">
         <is>
-          <t>etempute</t>
+          <t>[pʰɛdɯɭbo.dɯ]</t>
         </is>
       </c>
       <c r="D785" s="1" t="inlineStr">
@@ -25555,12 +25555,12 @@
       </c>
       <c r="B786" s="1" t="inlineStr">
         <is>
-          <t>[ngipew] 水彩画 (嗜好与休闲)</t>
+          <t>[[sʰwe̞t͡ɕʰwa̠]] 水彩画 (嗜好与休闲)</t>
         </is>
       </c>
       <c r="C786" s="1" t="inlineStr">
         <is>
-          <t>ngipew</t>
+          <t>[sʰwe̞t͡ɕʰwa̠]</t>
         </is>
       </c>
       <c r="D786" s="1" t="inlineStr">
@@ -25619,12 +25619,12 @@
       </c>
       <c r="B788" s="1" t="inlineStr">
         <is>
-          <t>[maherame] 编织 (嗜好与休闲)</t>
+          <t>[[maːkʰɯɾame]] 编织 (嗜好与休闲)</t>
         </is>
       </c>
       <c r="C788" s="1" t="inlineStr">
         <is>
-          <t>maherame</t>
+          <t>[maːkʰɯɾame]</t>
         </is>
       </c>
       <c r="D788" s="1" t="inlineStr">
@@ -25651,12 +25651,12 @@
       </c>
       <c r="B789" s="1" t="inlineStr">
         <is>
-          <t>[erariching] 玻璃瓶花园 (嗜好与休闲)</t>
+          <t>[[tʰe̞ɾaɾium]] 玻璃瓶花园 (嗜好与休闲)</t>
         </is>
       </c>
       <c r="C789" s="1" t="inlineStr">
         <is>
-          <t>erariching</t>
+          <t>[tʰe̞ɾaɾium]</t>
         </is>
       </c>
       <c r="D789" s="1" t="inlineStr">
@@ -25715,12 +25715,12 @@
       </c>
       <c r="B791" s="1" t="inlineStr">
         <is>
-          <t>[changw] 压花 (嗜好与休闲)</t>
+          <t>[[a̠pʰwa̠]] 压花 (嗜好与休闲)</t>
         </is>
       </c>
       <c r="C791" s="1" t="inlineStr">
         <is>
-          <t>changw</t>
+          <t>[a̠pʰwa̠]</t>
         </is>
       </c>
       <c r="D791" s="1" t="inlineStr">
@@ -25747,12 +25747,12 @@
       </c>
       <c r="B792" s="1" t="inlineStr">
         <is>
-          <t>[mukkutchye] 木工 (嗜好与休闲)</t>
+          <t>[[mok̚kʰo̞ŋɡje]] 木工 (嗜好与休闲)</t>
         </is>
       </c>
       <c r="C792" s="1" t="inlineStr">
         <is>
-          <t>mukkutchye</t>
+          <t>[mok̚kʰo̞ŋɡje]</t>
         </is>
       </c>
       <c r="D792" s="1" t="inlineStr">
@@ -25907,7 +25907,7 @@
       </c>
       <c r="B797" s="1" t="inlineStr">
         <is>
-          <t>[[pʰa̠ɭba̠ŋmiin]] 三脚猫 (成语俗语)</t>
+          <t>[[pʰa̠ɭba̠ŋmiin]] 多才多艺的人 (成语俗语)</t>
         </is>
       </c>
       <c r="C797" s="1" t="inlineStr">
@@ -25917,7 +25917,7 @@
       </c>
       <c r="D797" s="1" t="inlineStr">
         <is>
-          <t>三脚猫 (成语俗语)</t>
+          <t>多才多艺的人 (成语俗语)</t>
         </is>
       </c>
       <c r="E797" s="1" t="inlineStr">
@@ -25939,17 +25939,17 @@
       </c>
       <c r="B798" s="1" t="inlineStr">
         <is>
-          <t>[mamngimngiata] 把脚放进嘴里 (成语俗语)</t>
+          <t>[[ma̠ɭɕiɭs͈uɦa̠da̠]] 失言 (成语俗语)</t>
         </is>
       </c>
       <c r="C798" s="1" t="inlineStr">
         <is>
-          <t>mamngimngiata</t>
+          <t>[ma̠ɭɕiɭs͈uɦa̠da̠]</t>
         </is>
       </c>
       <c r="D798" s="1" t="inlineStr">
         <is>
-          <t>把脚放进嘴里 (成语俗语)</t>
+          <t>失言 (成语俗语)</t>
         </is>
       </c>
       <c r="E798" s="1" t="inlineStr">
@@ -26003,17 +26003,17 @@
       </c>
       <c r="B800" s="1" t="inlineStr">
         <is>
-          <t>[netteata] 给予冰冷的肩膀 (成语俗语)</t>
+          <t>[[nɛːŋdɛha̠da̠]] 冷待 (成语俗语)</t>
         </is>
       </c>
       <c r="C800" s="1" t="inlineStr">
         <is>
-          <t>netteata</t>
+          <t>[nɛːŋdɛha̠da̠]</t>
         </is>
       </c>
       <c r="D800" s="1" t="inlineStr">
         <is>
-          <t>给予冰冷的肩膀 (成语俗语)</t>
+          <t>冷待 (成语俗语)</t>
         </is>
       </c>
       <c r="E800" s="1" t="inlineStr">
@@ -26035,7 +26035,7 @@
       </c>
       <c r="B801" s="1" t="inlineStr">
         <is>
-          <t>[[pjʌ̹k̚t͡ɕ͈i]] 墙漆 (家居与家具)</t>
+          <t>[[pjʌ̹k̚t͡ɕ͈i]] 壁纸 (家居与家具)</t>
         </is>
       </c>
       <c r="C801" s="1" t="inlineStr">
@@ -26045,7 +26045,7 @@
       </c>
       <c r="D801" s="1" t="inlineStr">
         <is>
-          <t>墙漆 (家居与家具)</t>
+          <t>壁纸 (家居与家具)</t>
         </is>
       </c>
       <c r="E801" s="1" t="inlineStr">
@@ -26067,12 +26067,12 @@
       </c>
       <c r="B802" s="1" t="inlineStr">
         <is>
-          <t>[nginang] 储物 (家居与家具)</t>
+          <t>[[sʰuna̠p̚]] 储物 (家居与家具)</t>
         </is>
       </c>
       <c r="C802" s="1" t="inlineStr">
         <is>
-          <t>nginang</t>
+          <t>[sʰuna̠p̚]</t>
         </is>
       </c>
       <c r="D802" s="1" t="inlineStr">
@@ -26131,12 +26131,12 @@
       </c>
       <c r="B804" s="1" t="inlineStr">
         <is>
-          <t>[aingyon] 隔间屏风 (居家与家具)</t>
+          <t>[[pʰa̠tʰiɕʌ̹n]] 隔间屏风 (居家与家具)</t>
         </is>
       </c>
       <c r="C804" s="1" t="inlineStr">
         <is>
-          <t>aingyon</t>
+          <t>[pʰa̠tʰiɕʌ̹n]</t>
         </is>
       </c>
       <c r="D804" s="1" t="inlineStr">
@@ -26163,12 +26163,12 @@
       </c>
       <c r="B805" s="1" t="inlineStr">
         <is>
-          <t>[tachyttungim] 储藏室 (居家与家具)</t>
+          <t>[[taːjoŋdosʰiɭ]] 储藏室 (居家与家具)</t>
         </is>
       </c>
       <c r="C805" s="1" t="inlineStr">
         <is>
-          <t>tachyttungim</t>
+          <t>[taːjoŋdosʰiɭ]</t>
         </is>
       </c>
       <c r="D805" s="1" t="inlineStr">
@@ -26227,7 +26227,7 @@
       </c>
       <c r="B807" s="1" t="inlineStr">
         <is>
-          <t>[[ko̞ŋɡit͡ɕʰʌ̹ŋd͡ʑʌ̹ŋɡi]] 空气清净机 (居家与家具)</t>
+          <t>[[ko̞ŋɡit͡ɕʰʌ̹ŋd͡ʑʌ̹ŋɡi]] 空气净化器 (居家与家具)</t>
         </is>
       </c>
       <c r="C807" s="1" t="inlineStr">
@@ -26237,7 +26237,7 @@
       </c>
       <c r="D807" s="1" t="inlineStr">
         <is>
-          <t>空气清净机 (居家与家具)</t>
+          <t>空气净化器 (居家与家具)</t>
         </is>
       </c>
       <c r="E807" s="1" t="inlineStr">
@@ -26323,12 +26323,12 @@
       </c>
       <c r="B810" s="1" t="inlineStr">
         <is>
-          <t>[erange] 露台 (居家与家具)</t>
+          <t>[[tʰe̞ɾasʰɯ]] 露台 (居家与家具)</t>
         </is>
       </c>
       <c r="C810" s="1" t="inlineStr">
         <is>
-          <t>erange</t>
+          <t>[tʰe̞ɾasʰɯ]</t>
         </is>
       </c>
       <c r="D810" s="1" t="inlineStr">
@@ -26355,12 +26355,12 @@
       </c>
       <c r="B811" s="1" t="inlineStr">
         <is>
-          <t>[kingpinetkatku] 泡菜冰箱 (居家与家具)</t>
+          <t>[[kimt͡ɕʰina̠ŋd͡ʑa̠ŋɡo]] 泡菜冰箱 (居家与家具)</t>
         </is>
       </c>
       <c r="C811" s="1" t="inlineStr">
         <is>
-          <t>kingpinetkatku</t>
+          <t>[kimt͡ɕʰina̠ŋd͡ʑa̠ŋɡo]</t>
         </is>
       </c>
       <c r="D811" s="1" t="inlineStr">
@@ -26451,12 +26451,12 @@
       </c>
       <c r="B814" s="1" t="inlineStr">
         <is>
-          <t>[ungking] 居家健身房 (居家与家具)</t>
+          <t>[[homd͡ʑim]] 居家健身房 (居家与家具)</t>
         </is>
       </c>
       <c r="C814" s="1" t="inlineStr">
         <is>
-          <t>ungking</t>
+          <t>[homd͡ʑim]</t>
         </is>
       </c>
       <c r="D814" s="1" t="inlineStr">
@@ -26483,12 +26483,12 @@
       </c>
       <c r="B815" s="1" t="inlineStr">
         <is>
-          <t>[erenpihue] 风衣 (时尚与风格)</t>
+          <t>[[tʰɯɾɛnt͡ɕʰikʰo̞tʰɯ]] 风衣 (时尚与风格)</t>
         </is>
       </c>
       <c r="C815" s="1" t="inlineStr">
         <is>
-          <t>erenpihue</t>
+          <t>[tʰɯɾɛnt͡ɕʰikʰo̞tʰɯ]</t>
         </is>
       </c>
       <c r="D815" s="1" t="inlineStr">
@@ -26547,12 +26547,12 @@
       </c>
       <c r="B817" s="1" t="inlineStr">
         <is>
-          <t>[chengemreko] 运动休闲风 (时尚与风格)</t>
+          <t>[[ɛ.sʰɯl.le.dʑʌ]] 运动休闲风 (时尚与风格)</t>
         </is>
       </c>
       <c r="C817" s="1" t="inlineStr">
         <is>
-          <t>chengemreko</t>
+          <t>[ɛ.sʰɯl.le.dʑʌ]</t>
         </is>
       </c>
       <c r="D817" s="1" t="inlineStr">
@@ -26579,12 +26579,12 @@
       </c>
       <c r="B818" s="1" t="inlineStr">
         <is>
-          <t>[hutinechingyon] 服装搭配 (时尚与风格)</t>
+          <t>[[kʰo.di.ne.i.ɕʰin]] 服装搭配 (时尚与风格)</t>
         </is>
       </c>
       <c r="C818" s="1" t="inlineStr">
         <is>
-          <t>hutinechingyon</t>
+          <t>[kʰo.di.ne.i.ɕʰin]</t>
         </is>
       </c>
       <c r="D818" s="1" t="inlineStr">
@@ -26611,17 +26611,17 @@
       </c>
       <c r="B819" s="1" t="inlineStr">
         <is>
-          <t>[rikpik] 搭配 (时尚穿搭)</t>
+          <t>[[lukp͈uk]] 穿搭集 (时尚穿搭)</t>
         </is>
       </c>
       <c r="C819" s="1" t="inlineStr">
         <is>
-          <t>rikpik</t>
+          <t>[lukp͈uk]</t>
         </is>
       </c>
       <c r="D819" s="1" t="inlineStr">
         <is>
-          <t>搭配 (时尚穿搭)</t>
+          <t>穿搭集 (时尚穿搭)</t>
         </is>
       </c>
       <c r="E819" s="1" t="inlineStr">
@@ -26643,17 +26643,17 @@
       </c>
       <c r="B820" s="1" t="inlineStr">
         <is>
-          <t>[rechichorit] 压条 (时尚穿搭)</t>
+          <t>[[ɾe.i.ʌ.ɾiŋ]] 叠穿 (时尚穿搭)</t>
         </is>
       </c>
       <c r="C820" s="1" t="inlineStr">
         <is>
-          <t>rechichorit</t>
+          <t>[ɾe.i.ʌ.ɾiŋ]</t>
         </is>
       </c>
       <c r="D820" s="1" t="inlineStr">
         <is>
-          <t>压条 (时尚穿搭)</t>
+          <t>叠穿 (时尚穿搭)</t>
         </is>
       </c>
       <c r="E820" s="1" t="inlineStr">
@@ -26675,12 +26675,12 @@
       </c>
       <c r="B821" s="1" t="inlineStr">
         <is>
-          <t>[munuun] 单色 (时尚穿搭)</t>
+          <t>[[mo.no.tʰon]] 单色 (时尚穿搭)</t>
         </is>
       </c>
       <c r="C821" s="1" t="inlineStr">
         <is>
-          <t>munuun</t>
+          <t>[mo.no.tʰon]</t>
         </is>
       </c>
       <c r="D821" s="1" t="inlineStr">
@@ -26739,12 +26739,12 @@
       </c>
       <c r="B823" s="1" t="inlineStr">
         <is>
-          <t>[chwningeknge] 中性 (时尚穿搭)</t>
+          <t>[[ju.ni.sek̚.sɨ]] 中性 (时尚穿搭)</t>
         </is>
       </c>
       <c r="C823" s="1" t="inlineStr">
         <is>
-          <t>chwningeknge</t>
+          <t>[ju.ni.sek̚.sɨ]</t>
         </is>
       </c>
       <c r="D823" s="1" t="inlineStr">
@@ -26771,12 +26771,12 @@
       </c>
       <c r="B824" s="1" t="inlineStr">
         <is>
-          <t>[hoemrik] 匹配时装 (时尚穿搭)</t>
+          <t>[[kʰʌ.pʰɯl.luk̚]] 匹配时装 (时尚穿搭)</t>
         </is>
       </c>
       <c r="C824" s="1" t="inlineStr">
         <is>
-          <t>hoemrik</t>
+          <t>[kʰʌ.pʰɯl.luk̚]</t>
         </is>
       </c>
       <c r="D824" s="1" t="inlineStr">
@@ -26803,12 +26803,12 @@
       </c>
       <c r="B825" s="1" t="inlineStr">
         <is>
-          <t>[myoting] 奢侈品 (时尚与风格)</t>
+          <t>[[mjʌŋ.pʰum]] 奢侈品 (时尚与风格)</t>
         </is>
       </c>
       <c r="C825" s="1" t="inlineStr">
         <is>
-          <t>myoting</t>
+          <t>[mjʌŋ.pʰum]</t>
         </is>
       </c>
       <c r="D825" s="1" t="inlineStr">
@@ -26835,17 +26835,17 @@
       </c>
       <c r="B826" s="1" t="inlineStr">
         <is>
-          <t>[ngemritpek] 后跟系带凉鞋；Slingback (명사)</t>
+          <t>[[sɯl.liŋ.pɛk̚]] 后绊带凉鞋 (명사)</t>
         </is>
       </c>
       <c r="C826" s="1" t="inlineStr">
         <is>
-          <t>ngemritpek</t>
+          <t>[sɯl.liŋ.pɛk̚]</t>
         </is>
       </c>
       <c r="D826" s="1" t="inlineStr">
         <is>
-          <t>后跟系带凉鞋；Slingback (명사)</t>
+          <t>后绊带凉鞋 (명사)</t>
         </is>
       </c>
       <c r="E826" s="1" t="inlineStr">
@@ -26867,12 +26867,12 @@
       </c>
       <c r="B827" s="1" t="inlineStr">
         <is>
-          <t>[homropemruk] 颜色区块 (时尚穿搭)</t>
+          <t>[[kʰʌl.lʌ.bɯl.lok̚]] 颜色区块 (时尚穿搭)</t>
         </is>
       </c>
       <c r="C827" s="1" t="inlineStr">
         <is>
-          <t>homropemruk</t>
+          <t>[kʰʌl.lʌ.bɯl.lok̚]</t>
         </is>
       </c>
       <c r="D827" s="1" t="inlineStr">
@@ -27027,12 +27027,12 @@
       </c>
       <c r="B832" s="1" t="inlineStr">
         <is>
-          <t>[wipiw] 堆肥 (环境)</t>
+          <t>[[tʰwe.bi.βwa]] 堆肥 (环境)</t>
         </is>
       </c>
       <c r="C832" s="1" t="inlineStr">
         <is>
-          <t>wipiw</t>
+          <t>[tʰwe.bi.βwa]</t>
         </is>
       </c>
       <c r="D832" s="1" t="inlineStr">
@@ -27187,12 +27187,12 @@
       </c>
       <c r="B837" s="1" t="inlineStr">
         <is>
-          <t>[ngekuttechwt] 世宗大帝 (韩国历史)</t>
+          <t>[[se.d͡ʑoŋ.dɛ.waŋ]] 世宗大帝 (韩国历史)</t>
         </is>
       </c>
       <c r="C837" s="1" t="inlineStr">
         <is>
-          <t>ngekuttechwt</t>
+          <t>[se.d͡ʑoŋ.dɛ.waŋ]</t>
         </is>
       </c>
       <c r="D837" s="1" t="inlineStr">
@@ -27315,12 +27315,12 @@
       </c>
       <c r="B841" s="1" t="inlineStr">
         <is>
-          <t>[pimikatkite] 非军事区（DMZ） (韩国历史)</t>
+          <t>[[pi.mu.d͡ʑaŋ.d͡ʑi.dɛ]] 非军事区（DMZ） (韩国历史)</t>
         </is>
       </c>
       <c r="C841" s="1" t="inlineStr">
         <is>
-          <t>pimikatkite</t>
+          <t>[pi.mu.d͡ʑaŋ.d͡ʑi.dɛ]</t>
         </is>
       </c>
       <c r="D841" s="1" t="inlineStr">
@@ -27411,12 +27411,12 @@
       </c>
       <c r="B844" s="1" t="inlineStr">
         <is>
-          <t>[tukringkinyongkwn] 独立纪念馆 (韩国历史)</t>
+          <t>[[toŋ.nip̚.ki.njʌm.kwan]] 独立纪念馆 (韩国历史)</t>
         </is>
       </c>
       <c r="C844" s="1" t="inlineStr">
         <is>
-          <t>tukringkinyongkwn</t>
+          <t>[toŋ.nip̚.ki.njʌm.kwan]</t>
         </is>
       </c>
       <c r="D844" s="1" t="inlineStr">
@@ -27443,12 +27443,12 @@
       </c>
       <c r="B845" s="1" t="inlineStr">
         <is>
-          <t>[tokngikit] 德寿宫 (韩国历史)</t>
+          <t>[[tʌk̚.su.ɡuŋ]] 德寿宫 (韩国历史)</t>
         </is>
       </c>
       <c r="C845" s="1" t="inlineStr">
         <is>
-          <t>tokngikit</t>
+          <t>[tʌk̚.su.ɡuŋ]</t>
         </is>
       </c>
       <c r="D845" s="1" t="inlineStr">
@@ -27475,12 +27475,12 @@
       </c>
       <c r="B846" s="1" t="inlineStr">
         <is>
-          <t>[kikringkitchatpakmimkwn] 国立博物馆 (韩国历史)</t>
+          <t>[[kuŋ.nip̚.t͡ɕu.ŋʌŋ.pak̚.mul.ɡwan]] 国立博物馆 (韩国历史)</t>
         </is>
       </c>
       <c r="C846" s="1" t="inlineStr">
         <is>
-          <t>kikringkitchatpakmimkwn</t>
+          <t>[kuŋ.nip̚.t͡ɕu.ŋʌŋ.pak̚.mul.ɡwan]</t>
         </is>
       </c>
       <c r="D846" s="1" t="inlineStr">
@@ -27507,12 +27507,12 @@
       </c>
       <c r="B847" s="1" t="inlineStr">
         <is>
-          <t>[echinnga] 海印寺 (韩国历史)</t>
+          <t>[[hɛ.in.sa]] 海印寺 (韩国历史)</t>
         </is>
       </c>
       <c r="C847" s="1" t="inlineStr">
         <is>
-          <t>echinnga</t>
+          <t>[hɛ.in.sa]</t>
         </is>
       </c>
       <c r="D847" s="1" t="inlineStr">
@@ -27539,12 +27539,12 @@
       </c>
       <c r="B848" s="1" t="inlineStr">
         <is>
-          <t>[pimkiknga] 佛国寺 (韩国历史)</t>
+          <t>[[pul.ɡuk̚.sa]] 佛国寺 (韩国历史)</t>
         </is>
       </c>
       <c r="C848" s="1" t="inlineStr">
         <is>
-          <t>pimkiknga</t>
+          <t>[pul.ɡuk̚.sa]</t>
         </is>
       </c>
       <c r="D848" s="1" t="inlineStr">
@@ -27603,12 +27603,12 @@
       </c>
       <c r="B850" s="1" t="inlineStr">
         <is>
-          <t>[pattokkit] 昌德宫 (韩国历史)</t>
+          <t>[[t͡ɕʰaŋ.dʌk̚.ɡuŋ]] 昌德宫 (韩国历史)</t>
         </is>
       </c>
       <c r="C850" s="1" t="inlineStr">
         <is>
-          <t>pattokkit</t>
+          <t>[t͡ɕʰaŋ.dʌk̚.ɡuŋ]</t>
         </is>
       </c>
       <c r="D850" s="1" t="inlineStr">
@@ -27699,12 +27699,12 @@
       </c>
       <c r="B853" s="1" t="inlineStr">
         <is>
-          <t>[chwkwnngin] 柳宽顺 (韩国历史)</t>
+          <t>[[ju.ɡwan.sun]] 柳宽顺 (韩国历史)</t>
         </is>
       </c>
       <c r="C853" s="1" t="inlineStr">
         <is>
-          <t>chwkwnngin</t>
+          <t>[ju.ɡwan.sun]</t>
         </is>
       </c>
       <c r="D853" s="1" t="inlineStr">
@@ -27731,12 +27731,12 @@
       </c>
       <c r="B854" s="1" t="inlineStr">
         <is>
-          <t>[konketkinyongkwn] 战争纪念馆 (韩国历史)</t>
+          <t>[[t͡ɕʌn.d͡ʑɛŋ.ki.njʌm.kwan]] 战争纪念馆 (韩国历史)</t>
         </is>
       </c>
       <c r="C854" s="1" t="inlineStr">
         <is>
-          <t>konketkinyongkwn</t>
+          <t>[t͡ɕʌn.d͡ʑɛŋ.ki.njʌm.kwan]</t>
         </is>
       </c>
       <c r="D854" s="1" t="inlineStr">
@@ -27763,17 +27763,17 @@
       </c>
       <c r="B855" s="1" t="inlineStr">
         <is>
-          <t>[[kunin]] 士兵 (军事)</t>
+          <t>[[kuːnin]] 军人 (军事)</t>
         </is>
       </c>
       <c r="C855" s="1" t="inlineStr">
         <is>
-          <t>[kunin]</t>
+          <t>[kuːnin]</t>
         </is>
       </c>
       <c r="D855" s="1" t="inlineStr">
         <is>
-          <t>士兵 (军事)</t>
+          <t>军人 (军事)</t>
         </is>
       </c>
       <c r="E855" s="1" t="inlineStr">
@@ -27827,7 +27827,7 @@
       </c>
       <c r="B857" s="1" t="inlineStr">
         <is>
-          <t>[[ko̞ŋɡun]] 空军化一 (军事)</t>
+          <t>[[ko̞ŋɡun]] 空军 (军事)</t>
         </is>
       </c>
       <c r="C857" s="1" t="inlineStr">
@@ -27837,7 +27837,7 @@
       </c>
       <c r="D857" s="1" t="inlineStr">
         <is>
-          <t>空军化一 (军事)</t>
+          <t>空军 (军事)</t>
         </is>
       </c>
       <c r="E857" s="1" t="inlineStr">
@@ -27891,7 +27891,7 @@
       </c>
       <c r="B859" s="1" t="inlineStr">
         <is>
-          <t>[[ˈmu(ː)ɡi]] 作用武器 (军事)</t>
+          <t>[[ˈmu(ː)ɡi]] 武器 (军事)</t>
         </is>
       </c>
       <c r="C859" s="1" t="inlineStr">
@@ -27901,7 +27901,7 @@
       </c>
       <c r="D859" s="1" t="inlineStr">
         <is>
-          <t>作用武器 (军事)</t>
+          <t>武器 (军事)</t>
         </is>
       </c>
       <c r="E859" s="1" t="inlineStr">
@@ -28019,17 +28019,17 @@
       </c>
       <c r="B863" s="1" t="inlineStr">
         <is>
-          <t>[kinpite] 军事基地 (军事)</t>
+          <t>[[kun.bu.dɛ]] 部队 (军事)</t>
         </is>
       </c>
       <c r="C863" s="1" t="inlineStr">
         <is>
-          <t>kinpite</t>
+          <t>[kun.bu.dɛ]</t>
         </is>
       </c>
       <c r="D863" s="1" t="inlineStr">
         <is>
-          <t>军事基地 (军事)</t>
+          <t>部队 (军事)</t>
         </is>
       </c>
       <c r="E863" s="1" t="inlineStr">
@@ -28083,7 +28083,7 @@
       </c>
       <c r="B865" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕuŋsʰa̠]] 士官长 (军事)</t>
+          <t>[[t͡ɕuŋsʰa̠]] 中士 (军事)</t>
         </is>
       </c>
       <c r="C865" s="1" t="inlineStr">
@@ -28093,7 +28093,7 @@
       </c>
       <c r="D865" s="1" t="inlineStr">
         <is>
-          <t>士官长 (军事)</t>
+          <t>中士 (军事)</t>
         </is>
       </c>
       <c r="E865" s="1" t="inlineStr">
@@ -28275,7 +28275,7 @@
       </c>
       <c r="B871" s="1" t="inlineStr">
         <is>
-          <t>[[kjʌ̹ŋbi]] 守卫 (军事)</t>
+          <t>[[kjʌ̹ŋbi]] 警卫 (军事)</t>
         </is>
       </c>
       <c r="C871" s="1" t="inlineStr">
@@ -28285,7 +28285,7 @@
       </c>
       <c r="D871" s="1" t="inlineStr">
         <is>
-          <t>守卫 (军事)</t>
+          <t>警卫 (军事)</t>
         </is>
       </c>
       <c r="E871" s="1" t="inlineStr">
@@ -28371,7 +28371,7 @@
       </c>
       <c r="B874" s="1" t="inlineStr">
         <is>
-          <t>[[pʰo̞bjʌ̹ŋ]] 火炮 (军事)</t>
+          <t>[[pʰo̞bjʌ̹ŋ]] 炮兵 (军事)</t>
         </is>
       </c>
       <c r="C874" s="1" t="inlineStr">
@@ -28381,7 +28381,7 @@
       </c>
       <c r="D874" s="1" t="inlineStr">
         <is>
-          <t>火炮 (军事)</t>
+          <t>炮兵 (军事)</t>
         </is>
       </c>
       <c r="E874" s="1" t="inlineStr">
@@ -28467,7 +28467,7 @@
       </c>
       <c r="B877" s="1" t="inlineStr">
         <is>
-          <t>[[ˈsʰa̠(ː)ɡwa̠nɦa̠k̚k͈jo]] 军事学院 (军事)</t>
+          <t>[[ˈsʰa̠(ː)ɡwa̠nɦa̠k̚k͈jo]] 军官学校 (军事)</t>
         </is>
       </c>
       <c r="C877" s="1" t="inlineStr">
@@ -28477,7 +28477,7 @@
       </c>
       <c r="D877" s="1" t="inlineStr">
         <is>
-          <t>军事学院 (军事)</t>
+          <t>军官学校 (军事)</t>
         </is>
       </c>
       <c r="E877" s="1" t="inlineStr">
@@ -28563,7 +28563,7 @@
       </c>
       <c r="B880" s="1" t="inlineStr">
         <is>
-          <t>[[ˈku(ː)k̚p͈a̠ŋ]] 国土防卫 (军事)</t>
+          <t>[[ˈku(ː)k̚p͈a̠ŋ]] 国防 (军事)</t>
         </is>
       </c>
       <c r="C880" s="1" t="inlineStr">
@@ -28573,7 +28573,7 @@
       </c>
       <c r="D880" s="1" t="inlineStr">
         <is>
-          <t>国土防卫 (军事)</t>
+          <t>国防 (军事)</t>
         </is>
       </c>
       <c r="E880" s="1" t="inlineStr">
@@ -28723,12 +28723,12 @@
       </c>
       <c r="B885" s="1" t="inlineStr">
         <is>
-          <t>[kokyokngi] 狙击手 (军事)</t>
+          <t>[[t͡ɕʌɡjʌks͈u]] 狙击手 (军事)</t>
         </is>
       </c>
       <c r="C885" s="1" t="inlineStr">
         <is>
-          <t>kokyokngi</t>
+          <t>[t͡ɕʌɡjʌks͈u]</t>
         </is>
       </c>
       <c r="D885" s="1" t="inlineStr">
@@ -28787,12 +28787,12 @@
       </c>
       <c r="B887" s="1" t="inlineStr">
         <is>
-          <t>[nakanganpyot] 伞兵 (军事)</t>
+          <t>[[na̠kʰa̠sʰa̠mbjʌ̹ŋ]] 伞兵 (军事)</t>
         </is>
       </c>
       <c r="C887" s="1" t="inlineStr">
         <is>
-          <t>nakanganpyot</t>
+          <t>[na̠kʰa̠sʰa̠mbjʌ̹ŋ]</t>
         </is>
       </c>
       <c r="D887" s="1" t="inlineStr">
@@ -28883,12 +28883,12 @@
       </c>
       <c r="B890" s="1" t="inlineStr">
         <is>
-          <t>[pangkonchytnga] 老兵 (军事)</t>
+          <t>[[t͡ɕʰa̠mʤʌ̹ŋjoŋsa]] 老兵 (军事)</t>
         </is>
       </c>
       <c r="C890" s="1" t="inlineStr">
         <is>
-          <t>pangkonchytnga</t>
+          <t>[t͡ɕʰa̠mʤʌ̹ŋjoŋsa]</t>
         </is>
       </c>
       <c r="D890" s="1" t="inlineStr">
@@ -29363,7 +29363,7 @@
       </c>
       <c r="B905" s="1" t="inlineStr">
         <is>
-          <t>[[kunsʰu]] 物流 (军事)</t>
+          <t>[[kunsʰu]] 军需；后勤 (军事)</t>
         </is>
       </c>
       <c r="C905" s="1" t="inlineStr">
@@ -29373,7 +29373,7 @@
       </c>
       <c r="D905" s="1" t="inlineStr">
         <is>
-          <t>物流 (军事)</t>
+          <t>军需；后勤 (军事)</t>
         </is>
       </c>
       <c r="E905" s="1" t="inlineStr">
@@ -29395,12 +29395,12 @@
       </c>
       <c r="B906" s="1" t="inlineStr">
         <is>
-          <t>[kinchykwn] 军医 (军事)</t>
+          <t>[[kunŭigwan]] 军医 (军事)</t>
         </is>
       </c>
       <c r="C906" s="1" t="inlineStr">
         <is>
-          <t>kinchykwn</t>
+          <t>[kunŭigwan]</t>
         </is>
       </c>
       <c r="D906" s="1" t="inlineStr">
@@ -29427,12 +29427,12 @@
       </c>
       <c r="B907" s="1" t="inlineStr">
         <is>
-          <t>[chymipyot] 医护兵；卫生员 (军事)</t>
+          <t>[[ŭimubyŏng]] 医护兵；卫生员 (军事)</t>
         </is>
       </c>
       <c r="C907" s="1" t="inlineStr">
         <is>
-          <t>chymipyot</t>
+          <t>[ŭimubyŏng]</t>
         </is>
       </c>
       <c r="D907" s="1" t="inlineStr">
@@ -29459,17 +29459,17 @@
       </c>
       <c r="B908" s="1" t="inlineStr">
         <is>
-          <t>[kinkutkatky] 军队牧师 (军事)</t>
+          <t>[[kun.d͡ʑoŋ.d͡ʑaŋ.ɡjo]] 随军牧师 (军事)</t>
         </is>
       </c>
       <c r="C908" s="1" t="inlineStr">
         <is>
-          <t>kinkutkatky</t>
+          <t>[kun.d͡ʑoŋ.d͡ʑaŋ.ɡjo]</t>
         </is>
       </c>
       <c r="D908" s="1" t="inlineStr">
         <is>
-          <t>军队牧师 (军事)</t>
+          <t>随军牧师 (军事)</t>
         </is>
       </c>
       <c r="E908" s="1" t="inlineStr">
@@ -29491,12 +29491,12 @@
       </c>
       <c r="B909" s="1" t="inlineStr">
         <is>
-          <t>[kinchakte] 军乐队 (军事)</t>
+          <t>[[ku.nak̚.tɛ]] 军乐队 (军事)</t>
         </is>
       </c>
       <c r="C909" s="1" t="inlineStr">
         <is>
-          <t>kinchakte</t>
+          <t>[ku.nak̚.tɛ]</t>
         </is>
       </c>
       <c r="D909" s="1" t="inlineStr">
@@ -29523,17 +29523,17 @@
       </c>
       <c r="B910" s="1" t="inlineStr">
         <is>
-          <t>[chykatte] 荣耀之光 (军事)</t>
+          <t>[[ŭichangttae]] 仪仗队 (军事)</t>
         </is>
       </c>
       <c r="C910" s="1" t="inlineStr">
         <is>
-          <t>chykatte</t>
+          <t>[ŭichangttae]</t>
         </is>
       </c>
       <c r="D910" s="1" t="inlineStr">
         <is>
-          <t>荣耀之光 (军事)</t>
+          <t>仪仗队 (军事)</t>
         </is>
       </c>
       <c r="E910" s="1" t="inlineStr">
@@ -29587,7 +29587,7 @@
       </c>
       <c r="B912" s="1" t="inlineStr">
         <is>
-          <t>[[pʌ̹ŋkʰʌ̹]] 碉堡 (军事)</t>
+          <t>[[pʌ̹ŋkʰʌ̹]] 地堡 (军事)</t>
         </is>
       </c>
       <c r="C912" s="1" t="inlineStr">
@@ -29597,7 +29597,7 @@
       </c>
       <c r="D912" s="1" t="inlineStr">
         <is>
-          <t>碉堡 (军事)</t>
+          <t>地堡 (军事)</t>
         </is>
       </c>
       <c r="E912" s="1" t="inlineStr">
@@ -29619,7 +29619,7 @@
       </c>
       <c r="B913" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʰa̠mβo̞]] 管道沟。 (军事)</t>
+          <t>[[t͡ɕʰa̠mβo̞]] 战壕 (军事)</t>
         </is>
       </c>
       <c r="C913" s="1" t="inlineStr">
@@ -29629,7 +29629,7 @@
       </c>
       <c r="D913" s="1" t="inlineStr">
         <is>
-          <t>管道沟。 (军事)</t>
+          <t>战壕 (军事)</t>
         </is>
       </c>
       <c r="E913" s="1" t="inlineStr">
@@ -29651,12 +29651,12 @@
       </c>
       <c r="B914" s="1" t="inlineStr">
         <is>
-          <t>[onpyotte] 军事警察 ,宪兵 (军事)</t>
+          <t>[[hŏnpyŏngttae]] 军事警察 ,宪兵 (军事)</t>
         </is>
       </c>
       <c r="C914" s="1" t="inlineStr">
         <is>
-          <t>onpyotte</t>
+          <t>[hŏnpyŏngttae]</t>
         </is>
       </c>
       <c r="D914" s="1" t="inlineStr">
@@ -29715,12 +29715,12 @@
       </c>
       <c r="B916" s="1" t="inlineStr">
         <is>
-          <t>[kinpong] 军法 (军事)</t>
+          <t>[[kunpŏp]] 军法 (军事)</t>
         </is>
       </c>
       <c r="C916" s="1" t="inlineStr">
         <is>
-          <t>kinpong</t>
+          <t>[kunpŏp]</t>
         </is>
       </c>
       <c r="D916" s="1" t="inlineStr">
@@ -29747,12 +29747,12 @@
       </c>
       <c r="B917" s="1" t="inlineStr">
         <is>
-          <t>[kinki] 军纪 (军事)</t>
+          <t>[[kuŋɡi]] 军纪 (军事)</t>
         </is>
       </c>
       <c r="C917" s="1" t="inlineStr">
         <is>
-          <t>kinki</t>
+          <t>[kuŋɡi]</t>
         </is>
       </c>
       <c r="D917" s="1" t="inlineStr">
@@ -30355,7 +30355,7 @@
       </c>
       <c r="B936" s="1" t="inlineStr">
         <is>
-          <t>[[pʰa̠nɡjʌ̹ɭ]] 刑期 (法律与政府)</t>
+          <t>[[pʰa̠nɡjʌ̹ɭ]] 判决 (法律与政府)</t>
         </is>
       </c>
       <c r="C936" s="1" t="inlineStr">
@@ -30365,7 +30365,7 @@
       </c>
       <c r="D936" s="1" t="inlineStr">
         <is>
-          <t>刑期 (法律与政府)</t>
+          <t>判决 (法律与政府)</t>
         </is>
       </c>
       <c r="E936" s="1" t="inlineStr">
@@ -31155,12 +31155,12 @@
       </c>
       <c r="B961" s="1" t="inlineStr">
         <is>
-          <t>[anw] 版画 (艺术与设计)</t>
+          <t>[[pʰa̠nwa̠]] 版画 (艺术与设计)</t>
         </is>
       </c>
       <c r="C961" s="1" t="inlineStr">
         <is>
-          <t>anw</t>
+          <t>[pʰa̠nwa̠]</t>
         </is>
       </c>
       <c r="D961" s="1" t="inlineStr">
@@ -31187,12 +31187,12 @@
       </c>
       <c r="B962" s="1" t="inlineStr">
         <is>
-          <t>[chepit] 蚀刻 (艺术与设计)</t>
+          <t>[[e̞t͡ɕʰiŋ]] 蚀刻 (艺术与设计)</t>
         </is>
       </c>
       <c r="C962" s="1" t="inlineStr">
         <is>
-          <t>chepit</t>
+          <t>[e̞t͡ɕʰiŋ]</t>
         </is>
       </c>
       <c r="D962" s="1" t="inlineStr">
@@ -31219,17 +31219,17 @@
       </c>
       <c r="B963" s="1" t="inlineStr">
         <is>
-          <t>[ngokanw] 光固化成型技术 (艺术与设计)</t>
+          <t>[[sʰʌ̹k̚pʰa̠nwa̠]] 石版画 (艺术与设计)</t>
         </is>
       </c>
       <c r="C963" s="1" t="inlineStr">
         <is>
-          <t>ngokanw</t>
+          <t>[sʰʌ̹k̚pʰa̠nwa̠]</t>
         </is>
       </c>
       <c r="D963" s="1" t="inlineStr">
         <is>
-          <t>光固化成型技术 (艺术与设计)</t>
+          <t>石版画 (艺术与设计)</t>
         </is>
       </c>
       <c r="E963" s="1" t="inlineStr">
@@ -31251,12 +31251,12 @@
       </c>
       <c r="B964" s="1" t="inlineStr">
         <is>
-          <t>[mukanw] 木版画 (艺术与设计)</t>
+          <t>[[mo̞k̚pʰa̠nwa̠]] 木版画 (艺术与设计)</t>
         </is>
       </c>
       <c r="C964" s="1" t="inlineStr">
         <is>
-          <t>mukanw</t>
+          <t>[mo̞k̚pʰa̠nwa̠]</t>
         </is>
       </c>
       <c r="D964" s="1" t="inlineStr">
@@ -31411,12 +31411,12 @@
       </c>
       <c r="B969" s="1" t="inlineStr">
         <is>
-          <t>[chenkenpong] 透视 (艺术与设计)</t>
+          <t>[[wʌ̹nɡɯnmjʌ̹pʰ]] 透视 (艺术与设计)</t>
         </is>
       </c>
       <c r="C969" s="1" t="inlineStr">
         <is>
-          <t>chenkenpong</t>
+          <t>[wʌ̹nɡɯnmjʌ̹pʰ]</t>
         </is>
       </c>
       <c r="D969" s="1" t="inlineStr">
@@ -31475,12 +31475,12 @@
       </c>
       <c r="B971" s="1" t="inlineStr">
         <is>
-          <t>[kimkang] 纹理 (艺术与设计)</t>
+          <t>[[t͡ɕiɭɡa̠m]] 纹理 (艺术与设计)</t>
         </is>
       </c>
       <c r="C971" s="1" t="inlineStr">
         <is>
-          <t>kimkang</t>
+          <t>[t͡ɕiɭɡa̠m]</t>
         </is>
       </c>
       <c r="D971" s="1" t="inlineStr">
@@ -31507,12 +31507,12 @@
       </c>
       <c r="B972" s="1" t="inlineStr">
         <is>
-          <t>[ngangimkichy] 写实主义 (艺术与设计)</t>
+          <t>[[sʰa̠ɕʰiɭt͡ɕuɰi]] 写实主义 (艺术与设计)</t>
         </is>
       </c>
       <c r="C972" s="1" t="inlineStr">
         <is>
-          <t>ngangimkichy</t>
+          <t>[sʰa̠ɕʰiɭt͡ɕuɰi]</t>
         </is>
       </c>
       <c r="D972" s="1" t="inlineStr">
@@ -31539,12 +31539,12 @@
       </c>
       <c r="B973" s="1" t="inlineStr">
         <is>
-          <t>[chinngatkichy] 印象派 (艺术与设计)</t>
+          <t>[[ins͈a̠ŋt͡ɕuɰi]] 印象派 (艺术与设计)</t>
         </is>
       </c>
       <c r="C973" s="1" t="inlineStr">
         <is>
-          <t>chinngatkichy</t>
+          <t>[ins͈a̠ŋt͡ɕuɰi]</t>
         </is>
       </c>
       <c r="D973" s="1" t="inlineStr">
@@ -31571,12 +31571,12 @@
       </c>
       <c r="B974" s="1" t="inlineStr">
         <is>
-          <t>[minimomrikeng] 极简主义 (艺术与设计)</t>
+          <t>[[minimo̞ɭɭid͡ʑɯm]] 极简主义 (艺术与设计)</t>
         </is>
       </c>
       <c r="C974" s="1" t="inlineStr">
         <is>
-          <t>minimomrikeng</t>
+          <t>[minimo̞ɭɭid͡ʑɯm]</t>
         </is>
       </c>
       <c r="D974" s="1" t="inlineStr">
@@ -31603,12 +31603,12 @@
       </c>
       <c r="B975" s="1" t="inlineStr">
         <is>
-          <t>[puyonngimkichy] 超现实主义 (艺术与设计)</t>
+          <t>[[t͡ɕʰo̞çjʌ̹nɕʰiɭt͡ɕuɰi]] 超现实主义 (艺术与设计)</t>
         </is>
       </c>
       <c r="C975" s="1" t="inlineStr">
         <is>
-          <t>puyonngimkichy</t>
+          <t>[t͡ɕʰo̞çjʌ̹nɕʰiɭt͡ɕuɰi]</t>
         </is>
       </c>
       <c r="D975" s="1" t="inlineStr">
@@ -31635,12 +31635,12 @@
       </c>
       <c r="B976" s="1" t="inlineStr">
         <is>
-          <t>[chapatkarete] 前卫艺术 (艺术与设计)</t>
+          <t>[[a̠ba̠ŋɡa̠ɾɯdɯ]] 前卫艺术 (艺术与设计)</t>
         </is>
       </c>
       <c r="C976" s="1" t="inlineStr">
         <is>
-          <t>chapatkarete</t>
+          <t>[a̠ba̠ŋɡa̠ɾɯdɯ]</t>
         </is>
       </c>
       <c r="D976" s="1" t="inlineStr">
@@ -31699,12 +31699,12 @@
       </c>
       <c r="B978" s="1" t="inlineStr">
         <is>
-          <t>[paruhe] 巴洛克 (艺术与设计)</t>
+          <t>[[pa̠ɾo̞kʰɯ]] 巴洛克 (艺术与设计)</t>
         </is>
       </c>
       <c r="C978" s="1" t="inlineStr">
         <is>
-          <t>paruhe</t>
+          <t>[pa̠ɾo̞kʰɯ]</t>
         </is>
       </c>
       <c r="D978" s="1" t="inlineStr">
@@ -31731,12 +31731,12 @@
       </c>
       <c r="B979" s="1" t="inlineStr">
         <is>
-          <t>[kikku] 织入 (艺术与设计)</t>
+          <t>[[t͡ɕikt͡ɕo]] 织入 (艺术与设计)</t>
         </is>
       </c>
       <c r="C979" s="1" t="inlineStr">
         <is>
-          <t>kikku</t>
+          <t>[t͡ɕikt͡ɕo]</t>
         </is>
       </c>
       <c r="D979" s="1" t="inlineStr">
@@ -31763,12 +31763,12 @@
       </c>
       <c r="B980" s="1" t="inlineStr">
         <is>
-          <t>[hwrechio] 保管人 (艺术与设计)</t>
+          <t>[[kʰjuɾe̞itʰʌ̹]] 保管人 (艺术与设计)</t>
         </is>
       </c>
       <c r="C980" s="1" t="inlineStr">
         <is>
-          <t>hwrechio</t>
+          <t>[kʰjuɾe̞itʰʌ̹]</t>
         </is>
       </c>
       <c r="D980" s="1" t="inlineStr">
@@ -31859,7 +31859,7 @@
       </c>
       <c r="B983" s="1" t="inlineStr">
         <is>
-          <t>[[ɰiɾwe̞]] 佣金 (艺术设计)</t>
+          <t>[[ɰiɾwe̞]] 委托 (艺术设计)</t>
         </is>
       </c>
       <c r="C983" s="1" t="inlineStr">
@@ -31869,7 +31869,7 @@
       </c>
       <c r="D983" s="1" t="inlineStr">
         <is>
-          <t>佣金 (艺术设计)</t>
+          <t>委托 (艺术设计)</t>
         </is>
       </c>
       <c r="E983" s="1" t="inlineStr">
@@ -31891,17 +31891,17 @@
       </c>
       <c r="B984" s="1" t="inlineStr">
         <is>
-          <t>[ngikingka] 托收人 (艺术设计)</t>
+          <t>[[sʰud͡ʑip͈ka̠]] 收藏家 (艺术设计)</t>
         </is>
       </c>
       <c r="C984" s="1" t="inlineStr">
         <is>
-          <t>ngikingka</t>
+          <t>[sʰud͡ʑip͈ka̠]</t>
         </is>
       </c>
       <c r="D984" s="1" t="inlineStr">
         <is>
-          <t>托收人 (艺术设计)</t>
+          <t>收藏家 (艺术设计)</t>
         </is>
       </c>
       <c r="E984" s="1" t="inlineStr">
@@ -31923,7 +31923,7 @@
       </c>
       <c r="B985" s="1" t="inlineStr">
         <is>
-          <t>[[ɸʷuwʌ̹n]] 庇护 (艺术设计)</t>
+          <t>[[ɸʷuwʌ̹n]] 赞助 (艺术设计)</t>
         </is>
       </c>
       <c r="C985" s="1" t="inlineStr">
@@ -31933,7 +31933,7 @@
       </c>
       <c r="D985" s="1" t="inlineStr">
         <is>
-          <t>庇护 (艺术设计)</t>
+          <t>赞助 (艺术设计)</t>
         </is>
       </c>
       <c r="E985" s="1" t="inlineStr">
@@ -31955,12 +31955,12 @@
       </c>
       <c r="B986" s="1" t="inlineStr">
         <is>
-          <t>[miky] 萨满教 (宗教)</t>
+          <t>[[muɡjʌ̹]] 萨满教 (宗教)</t>
         </is>
       </c>
       <c r="C986" s="1" t="inlineStr">
         <is>
-          <t>miky</t>
+          <t>[muɡjʌ̹]</t>
         </is>
       </c>
       <c r="D986" s="1" t="inlineStr">
@@ -32243,7 +32243,7 @@
       </c>
       <c r="B995" s="1" t="inlineStr">
         <is>
-          <t>[[mo̞ks͈a̠nim]] 上人 (宗教)</t>
+          <t>[[mo̞ks͈a̠nim]] 牧师 (宗教)</t>
         </is>
       </c>
       <c r="C995" s="1" t="inlineStr">
@@ -32253,7 +32253,7 @@
       </c>
       <c r="D995" s="1" t="inlineStr">
         <is>
-          <t>上人 (宗教)</t>
+          <t>牧师 (宗教)</t>
         </is>
       </c>
       <c r="E995" s="1" t="inlineStr">
@@ -32339,12 +32339,12 @@
       </c>
       <c r="B998" s="1" t="inlineStr">
         <is>
-          <t>[kykit] 会众 (宗教)</t>
+          <t>[[kjoːd͡ʑuŋ]] 会众 (宗教)</t>
         </is>
       </c>
       <c r="C998" s="1" t="inlineStr">
         <is>
-          <t>kykit</t>
+          <t>[kjoːd͡ʑuŋ]</t>
         </is>
       </c>
       <c r="D998" s="1" t="inlineStr">
@@ -32595,7 +32595,7 @@
       </c>
       <c r="B1006" s="1" t="inlineStr">
         <is>
-          <t>[[jʌ̹mbuɭ]] 诵经 (宗教)</t>
+          <t>[[jʌ̹mbuɭ]] 念佛 (宗教)</t>
         </is>
       </c>
       <c r="C1006" s="1" t="inlineStr">
@@ -32605,7 +32605,7 @@
       </c>
       <c r="D1006" s="1" t="inlineStr">
         <is>
-          <t>诵经 (宗教)</t>
+          <t>念佛 (宗教)</t>
         </is>
       </c>
       <c r="E1006" s="1" t="inlineStr">
@@ -32755,12 +32755,12 @@
       </c>
       <c r="B1011" s="1" t="inlineStr">
         <is>
-          <t>[kyonkin] 坚信礼 (宗教)</t>
+          <t>[[kjʌːnd͡ʑin]] 坚信礼 (宗教)</t>
         </is>
       </c>
       <c r="C1011" s="1" t="inlineStr">
         <is>
-          <t>kyonkin</t>
+          <t>[kjʌːnd͡ʑin]</t>
         </is>
       </c>
       <c r="D1011" s="1" t="inlineStr">
@@ -32787,7 +32787,7 @@
       </c>
       <c r="B1012" s="1" t="inlineStr">
         <is>
-          <t>[[ˈmu(ː)da̠ŋ]] 巫师 (宗教)</t>
+          <t>[[ˈmu(ː)da̠ŋ]] 巫婆 (宗教)</t>
         </is>
       </c>
       <c r="C1012" s="1" t="inlineStr">
@@ -32797,7 +32797,7 @@
       </c>
       <c r="D1012" s="1" t="inlineStr">
         <is>
-          <t>巫师 (宗教)</t>
+          <t>巫婆 (宗教)</t>
         </is>
       </c>
       <c r="E1012" s="1" t="inlineStr">
@@ -32819,7 +32819,7 @@
       </c>
       <c r="B1013" s="1" t="inlineStr">
         <is>
-          <t>[[unsʰe̞]] 星座 (宗教)</t>
+          <t>[[unsʰe̞]] 运势 (宗教)</t>
         </is>
       </c>
       <c r="C1013" s="1" t="inlineStr">
@@ -32829,7 +32829,7 @@
       </c>
       <c r="D1013" s="1" t="inlineStr">
         <is>
-          <t>星座 (宗教)</t>
+          <t>运势 (宗教)</t>
         </is>
       </c>
       <c r="E1013" s="1" t="inlineStr">
@@ -33011,12 +33011,12 @@
       </c>
       <c r="B1019" s="1" t="inlineStr">
         <is>
-          <t>[ramatan] 斋戒月 (宗教)</t>
+          <t>[[ɾamadan]] 斋戒月 (宗教)</t>
         </is>
       </c>
       <c r="C1019" s="1" t="inlineStr">
         <is>
-          <t>ramatan</t>
+          <t>[ɾamadan]</t>
         </is>
       </c>
       <c r="D1019" s="1" t="inlineStr">
@@ -33043,12 +33043,12 @@
       </c>
       <c r="B1020" s="1" t="inlineStr">
         <is>
-          <t>[chite] 开斋节 (宗教)</t>
+          <t>[[idɯ]] 开斋节 (宗教)</t>
         </is>
       </c>
       <c r="C1020" s="1" t="inlineStr">
         <is>
-          <t>chite</t>
+          <t>[idɯ]</t>
         </is>
       </c>
       <c r="D1020" s="1" t="inlineStr">
@@ -33139,12 +33139,12 @@
       </c>
       <c r="B1023" s="1" t="inlineStr">
         <is>
-          <t>[ngingchimku] 什一奉献 (宗教)</t>
+          <t>[[ɕibild͡ʑo]] 什一奉献 (宗教)</t>
         </is>
       </c>
       <c r="C1023" s="1" t="inlineStr">
         <is>
-          <t>ngingchimku</t>
+          <t>[ɕibild͡ʑo]</t>
         </is>
       </c>
       <c r="D1023" s="1" t="inlineStr">
@@ -33203,12 +33203,12 @@
       </c>
       <c r="B1025" s="1" t="inlineStr">
         <is>
-          <t>[kichimakky] 主日学 (宗教)</t>
+          <t>[[t͡ɕuilhakkjo]] 主日学 (宗教)</t>
         </is>
       </c>
       <c r="C1025" s="1" t="inlineStr">
         <is>
-          <t>kichimakky</t>
+          <t>[t͡ɕuilhakkjo]</t>
         </is>
       </c>
       <c r="D1025" s="1" t="inlineStr">
@@ -33235,12 +33235,12 @@
       </c>
       <c r="B1026" s="1" t="inlineStr">
         <is>
-          <t>[ngimikw] 水墨画 (艺术与设计)</t>
+          <t>[[sʰumuk̚kʰwa]] 水墨画 (艺术与设计)</t>
         </is>
       </c>
       <c r="C1026" s="1" t="inlineStr">
         <is>
-          <t>ngimikw</t>
+          <t>[sʰumuk̚kʰwa]</t>
         </is>
       </c>
       <c r="D1026" s="1" t="inlineStr">
@@ -33267,12 +33267,12 @@
       </c>
       <c r="B1027" s="1" t="inlineStr">
         <is>
-          <t>[pinpotngaki] 粉青瓷 (艺术与设计)</t>
+          <t>[[pundʑʰʌŋsaɡi]] 粉青瓷 (艺术与设计)</t>
         </is>
       </c>
       <c r="C1027" s="1" t="inlineStr">
         <is>
-          <t>pinpotngaki</t>
+          <t>[pundʑʰʌŋsaɡi]</t>
         </is>
       </c>
       <c r="D1027" s="1" t="inlineStr">
@@ -33299,12 +33299,12 @@
       </c>
       <c r="B1028" s="1" t="inlineStr">
         <is>
-          <t>[pekka] 白瓷 (艺术与设计)</t>
+          <t>[[pɛk̚t͈ɐ]] 白瓷 (艺术与设计)</t>
         </is>
       </c>
       <c r="C1028" s="1" t="inlineStr">
         <is>
-          <t>pekka</t>
+          <t>[pɛk̚t͈ɐ]</t>
         </is>
       </c>
       <c r="D1028" s="1" t="inlineStr">
@@ -33363,12 +33363,12 @@
       </c>
       <c r="B1030" s="1" t="inlineStr">
         <is>
-          <t>[piku] 浮雕 (艺术与设计)</t>
+          <t>[[pudʑo]] 浮雕 (艺术与设计)</t>
         </is>
       </c>
       <c r="C1030" s="1" t="inlineStr">
         <is>
-          <t>piku</t>
+          <t>[pudʑo]</t>
         </is>
       </c>
       <c r="D1030" s="1" t="inlineStr">
@@ -33395,12 +33395,12 @@
       </c>
       <c r="B1031" s="1" t="inlineStr">
         <is>
-          <t>[ngokku] 石雕 (艺术与设计)</t>
+          <t>[[sʰʌk̚t͈o]] 石雕 (艺术与设计)</t>
         </is>
       </c>
       <c r="C1031" s="1" t="inlineStr">
         <is>
-          <t>ngokku</t>
+          <t>[sʰʌk̚t͈o]</t>
         </is>
       </c>
       <c r="D1031" s="1" t="inlineStr">
@@ -33427,7 +33427,7 @@
       </c>
       <c r="B1032" s="1" t="inlineStr">
         <is>
-          <t>[[mo̞k̚t͡ɕ͈o̞]] 木雕 (艺术与设计)</t>
+          <t>[[mo̞k̚t͡ɕ͈o̞]] 木造；木结构 (艺术与设计)</t>
         </is>
       </c>
       <c r="C1032" s="1" t="inlineStr">
@@ -33437,7 +33437,7 @@
       </c>
       <c r="D1032" s="1" t="inlineStr">
         <is>
-          <t>木雕 (艺术与设计)</t>
+          <t>木造；木结构 (艺术与设计)</t>
         </is>
       </c>
       <c r="E1032" s="1" t="inlineStr">
@@ -33459,12 +33459,12 @@
       </c>
       <c r="B1033" s="1" t="inlineStr">
         <is>
-          <t>[chikachwm] 利率 (金融与银行)</t>
+          <t>[[idʑajul]] 利率 (金融与银行)</t>
         </is>
       </c>
       <c r="C1033" s="1" t="inlineStr">
         <is>
-          <t>chikachwm</t>
+          <t>[idʑajul]</t>
         </is>
       </c>
       <c r="D1033" s="1" t="inlineStr">
@@ -33555,12 +33555,12 @@
       </c>
       <c r="B1036" s="1" t="inlineStr">
         <is>
-          <t>[kikpim] 扣帐 (金融与银行)</t>
+          <t>[[tɕik̚pʰul]] 扣帐 (金融与银行)</t>
         </is>
       </c>
       <c r="C1036" s="1" t="inlineStr">
         <is>
-          <t>kikpim</t>
+          <t>[tɕik̚pʰul]</t>
         </is>
       </c>
       <c r="D1036" s="1" t="inlineStr">
@@ -33875,12 +33875,12 @@
       </c>
       <c r="B1046" s="1" t="inlineStr">
         <is>
-          <t>[nguteknge] 所得税 (金融与银行)</t>
+          <t>[[sodɯk̚s͈e]] 所得税 (金融与银行)</t>
         </is>
       </c>
       <c r="C1046" s="1" t="inlineStr">
         <is>
-          <t>nguteknge</t>
+          <t>[sodɯk̚s͈e]</t>
         </is>
       </c>
       <c r="D1046" s="1" t="inlineStr">
@@ -34003,12 +34003,12 @@
       </c>
       <c r="B1050" s="1" t="inlineStr">
         <is>
-          <t>[echiam] 贝宝（PayPal） (金融银行)</t>
+          <t>[[pʰeipʰal]] 贝宝（PayPal） (金融银行)</t>
         </is>
       </c>
       <c r="C1050" s="1" t="inlineStr">
         <is>
-          <t>echiam</t>
+          <t>[pʰeipʰal]</t>
         </is>
       </c>
       <c r="D1050" s="1" t="inlineStr">
@@ -34099,12 +34099,12 @@
       </c>
       <c r="B1053" s="1" t="inlineStr">
         <is>
-          <t>[korikan] 神圣 (宗教)</t>
+          <t>[[kʌɾuk̚han]] 神圣 (宗教)</t>
         </is>
       </c>
       <c r="C1053" s="1" t="inlineStr">
         <is>
-          <t>korikan</t>
+          <t>[kʌɾuk̚han]</t>
         </is>
       </c>
       <c r="D1053" s="1" t="inlineStr">
@@ -34323,17 +34323,17 @@
       </c>
       <c r="B1060" s="1" t="inlineStr">
         <is>
-          <t>[inchwk] 管教 (育儿与家庭生活)</t>
+          <t>[[hunɲuk]] 教养 (育儿与家庭生活)</t>
         </is>
       </c>
       <c r="C1060" s="1" t="inlineStr">
         <is>
-          <t>inchwk</t>
+          <t>[hunɲuk]</t>
         </is>
       </c>
       <c r="D1060" s="1" t="inlineStr">
         <is>
-          <t>管教 (育儿与家庭生活)</t>
+          <t>教养 (育儿与家庭生活)</t>
         </is>
       </c>
       <c r="E1060" s="1" t="inlineStr">
@@ -34355,12 +34355,12 @@
       </c>
       <c r="B1061" s="1" t="inlineStr">
         <is>
-          <t>[chuecho] 互惠生 (育儿与家庭生活)</t>
+          <t>[[opʰeʌ]] 互惠生 (育儿与家庭生活)</t>
         </is>
       </c>
       <c r="C1061" s="1" t="inlineStr">
         <is>
-          <t>chuecho</t>
+          <t>[opʰeʌ]</t>
         </is>
       </c>
       <c r="D1061" s="1" t="inlineStr">
@@ -34387,12 +34387,12 @@
       </c>
       <c r="B1062" s="1" t="inlineStr">
         <is>
-          <t>[anpimu] 单亲家长 (育儿与家庭生活)</t>
+          <t>[[hanbumo]] 单亲家长 (育儿与家庭生活)</t>
         </is>
       </c>
       <c r="C1062" s="1" t="inlineStr">
         <is>
-          <t>anpimu</t>
+          <t>[hanbumo]</t>
         </is>
       </c>
       <c r="D1062" s="1" t="inlineStr">
@@ -34483,12 +34483,12 @@
       </c>
       <c r="B1065" s="1" t="inlineStr">
         <is>
-          <t>[ngotchinngik] 成年礼 (亲子与家庭生活)</t>
+          <t>[[sʰʌŋinɕik̚]] 成年礼 (亲子与家庭生活)</t>
         </is>
       </c>
       <c r="C1065" s="1" t="inlineStr">
         <is>
-          <t>ngotchinngik</t>
+          <t>[sʰʌŋinɕik̚]</t>
         </is>
       </c>
       <c r="D1065" s="1" t="inlineStr">
@@ -34515,12 +34515,12 @@
       </c>
       <c r="B1066" s="1" t="inlineStr">
         <is>
-          <t>[kengannge] 财产税 (金融与银行)</t>
+          <t>[[tɕɛsʰansʰe]] 财产税 (金融与银行)</t>
         </is>
       </c>
       <c r="C1066" s="1" t="inlineStr">
         <is>
-          <t>kengannge</t>
+          <t>[tɕɛsʰansʰe]</t>
         </is>
       </c>
       <c r="D1066" s="1" t="inlineStr">
@@ -34547,12 +34547,12 @@
       </c>
       <c r="B1067" s="1" t="inlineStr">
         <is>
-          <t>[nginchytkongngi] 信用评分 (金融与银行)</t>
+          <t>[[ɕiɲoŋtɕʌmsʰu]] 信用评分 (金融与银行)</t>
         </is>
       </c>
       <c r="C1067" s="1" t="inlineStr">
         <is>
-          <t>nginchytkongngi</t>
+          <t>[ɕiɲoŋtɕʌmsʰu]</t>
         </is>
       </c>
       <c r="D1067" s="1" t="inlineStr">
@@ -34611,12 +34611,12 @@
       </c>
       <c r="B1069" s="1" t="inlineStr">
         <is>
-          <t>[yotmyontu] 平面图 (建筑)</t>
+          <t>[[pʰjʌŋmjʌndo]] 平面图 (建筑)</t>
         </is>
       </c>
       <c r="C1069" s="1" t="inlineStr">
         <is>
-          <t>yotmyontu</t>
+          <t>[pʰjʌŋmjʌndo]</t>
         </is>
       </c>
       <c r="D1069" s="1" t="inlineStr">
@@ -35443,12 +35443,12 @@
       </c>
       <c r="B1095" s="1" t="inlineStr">
         <is>
-          <t>[hongwokwak] 计算机科学 (科学与研究)</t>
+          <t>[[kʰʌmpʰjutʰɔkwaŋhak̚]] 计算机科学 (科学与研究)</t>
         </is>
       </c>
       <c r="C1095" s="1" t="inlineStr">
         <is>
-          <t>hongwokwak</t>
+          <t>[kʰʌmpʰjutʰɔkwaŋhak̚]</t>
         </is>
       </c>
       <c r="D1095" s="1" t="inlineStr">
@@ -35507,12 +35507,12 @@
       </c>
       <c r="B1097" s="1" t="inlineStr">
         <is>
-          <t>[akngimki] 期刊 (科学与研究)</t>
+          <t>[[haks͈utɕi]] 期刊 (科学与研究)</t>
         </is>
       </c>
       <c r="C1097" s="1" t="inlineStr">
         <is>
-          <t>akngimki</t>
+          <t>[haks͈utɕi]</t>
         </is>
       </c>
       <c r="D1097" s="1" t="inlineStr">
@@ -35603,12 +35603,12 @@
       </c>
       <c r="B1100" s="1" t="inlineStr">
         <is>
-          <t>[pukukeng] 补助金 (科学与研究)</t>
+          <t>[[podʑoɡɯm]] 补助金 (科学与研究)</t>
         </is>
       </c>
       <c r="C1100" s="1" t="inlineStr">
         <is>
-          <t>pukukeng</t>
+          <t>[podʑoɡɯm]</t>
         </is>
       </c>
       <c r="D1100" s="1" t="inlineStr">
@@ -35667,12 +35667,12 @@
       </c>
       <c r="B1102" s="1" t="inlineStr">
         <is>
-          <t>[pakngaakche] 博士学位 (科学与研究)</t>
+          <t>[[pa̠k̚sa̠hɥi]] 博士学位 (科学与研究)</t>
         </is>
       </c>
       <c r="C1102" s="1" t="inlineStr">
         <is>
-          <t>pakngaakche</t>
+          <t>[pa̠k̚sa̠hɥi]</t>
         </is>
       </c>
       <c r="D1102" s="1" t="inlineStr">
@@ -35923,12 +35923,12 @@
       </c>
       <c r="B1110" s="1" t="inlineStr">
         <is>
-          <t>[chyonkiing] 研究团队 (科学与研究)</t>
+          <t>[[jʌ̹nɡutʰim]] 研究团队 (科学与研究)</t>
         </is>
       </c>
       <c r="C1110" s="1" t="inlineStr">
         <is>
-          <t>chyonkiing</t>
+          <t>[jʌ̹nɡutʰim]</t>
         </is>
       </c>
       <c r="D1110" s="1" t="inlineStr">
@@ -35987,12 +35987,12 @@
       </c>
       <c r="B1112" s="1" t="inlineStr">
         <is>
-          <t>[hunngoeum] 音乐厅 (建筑)</t>
+          <t>[[kʰo̞nsʰɔtʰɯhɔl]] 音乐厅 (建筑)</t>
         </is>
       </c>
       <c r="C1112" s="1" t="inlineStr">
         <is>
-          <t>hunngoeum</t>
+          <t>[kʰo̞nsʰɔtʰɯhɔl]</t>
         </is>
       </c>
       <c r="D1112" s="1" t="inlineStr">
@@ -36019,12 +36019,12 @@
       </c>
       <c r="B1113" s="1" t="inlineStr">
         <is>
-          <t>[kotkichyekeng] 定期存款 (金融与银行)</t>
+          <t>[[tɕʌ̹ŋɡije̞ɡɯm]] 定期存款 (金融与银行)</t>
         </is>
       </c>
       <c r="C1113" s="1" t="inlineStr">
         <is>
-          <t>kotkichyekeng</t>
+          <t>[tɕʌ̹ŋɡije̞ɡɯm]</t>
         </is>
       </c>
       <c r="D1113" s="1" t="inlineStr">
@@ -36147,12 +36147,12 @@
       </c>
       <c r="B1117" s="1" t="inlineStr">
         <is>
-          <t>[ekkut] 独家新闻 (媒体与新闻)</t>
+          <t>[[tʰɯk̚t͡ɕ͈oŋ]] 独家新闻 (媒体与新闻)</t>
         </is>
       </c>
       <c r="C1117" s="1" t="inlineStr">
         <is>
-          <t>ekkut</t>
+          <t>[tʰɯk̚t͡ɕ͈oŋ]</t>
         </is>
       </c>
       <c r="D1117" s="1" t="inlineStr">
@@ -36179,12 +36179,12 @@
       </c>
       <c r="B1118" s="1" t="inlineStr">
         <is>
-          <t>[apemruchite] 小报 (媒体与新闻)</t>
+          <t>[[tʰa̠bɯlloido]] 小报 (媒体与新闻)</t>
         </is>
       </c>
       <c r="C1118" s="1" t="inlineStr">
         <is>
-          <t>apemruchite</t>
+          <t>[tʰa̠bɯlloido]</t>
         </is>
       </c>
       <c r="D1118" s="1" t="inlineStr">
@@ -36211,12 +36211,12 @@
       </c>
       <c r="B1119" s="1" t="inlineStr">
         <is>
-          <t>[ekepehe] 事实查核 (媒体与新闻)</t>
+          <t>[[pʰɛktʰɯt͡ɕʰe̞kʰ]] 事实查核 (媒体与新闻)</t>
         </is>
       </c>
       <c r="C1119" s="1" t="inlineStr">
         <is>
-          <t>ekepehe</t>
+          <t>[pʰɛktʰɯt͡ɕʰe̞kʰ]</t>
         </is>
       </c>
       <c r="D1119" s="1" t="inlineStr">
@@ -36339,12 +36339,12 @@
       </c>
       <c r="B1123" s="1" t="inlineStr">
         <is>
-          <t>[nwngering] 新闻编辑室 (媒体与新闻学)</t>
+          <t>[[njusɯɾum]] 新闻编辑室 (媒体与新闻学)</t>
         </is>
       </c>
       <c r="C1123" s="1" t="inlineStr">
         <is>
-          <t>nwngering</t>
+          <t>[njusɯɾum]</t>
         </is>
       </c>
       <c r="D1123" s="1" t="inlineStr">
@@ -36403,7 +36403,7 @@
       </c>
       <c r="B1125" s="1" t="inlineStr">
         <is>
-          <t>[[ˈhɛ(ː)sʰʌ̹ɭ]] 评论 (媒体与新闻学)</t>
+          <t>[[ˈhɛ(ː)sʰʌ̹ɭ]] 解说 (媒体与新闻学)</t>
         </is>
       </c>
       <c r="C1125" s="1" t="inlineStr">
@@ -36413,7 +36413,7 @@
       </c>
       <c r="D1125" s="1" t="inlineStr">
         <is>
-          <t>评论 (媒体与新闻学)</t>
+          <t>解说 (媒体与新闻学)</t>
         </is>
       </c>
       <c r="E1125" s="1" t="inlineStr">
@@ -36435,12 +36435,12 @@
       </c>
       <c r="B1126" s="1" t="inlineStr">
         <is>
-          <t>[chonrunnga] 媒体机构 (媒体与新闻学)</t>
+          <t>[[ʌ̹lloːnsa]] 媒体机构 (媒体与新闻学)</t>
         </is>
       </c>
       <c r="C1126" s="1" t="inlineStr">
         <is>
-          <t>chonrunnga</t>
+          <t>[ʌ̹lloːnsa]</t>
         </is>
       </c>
       <c r="D1126" s="1" t="inlineStr">
@@ -36467,12 +36467,12 @@
       </c>
       <c r="B1127" s="1" t="inlineStr">
         <is>
-          <t>[kekkwnngot] 客观性 (媒体与新闻学)</t>
+          <t>[[kɛk̚k͈wa̠nsʰʌ̹ŋ]] 客观性 (媒体与新闻学)</t>
         </is>
       </c>
       <c r="C1127" s="1" t="inlineStr">
         <is>
-          <t>kekkwnngot</t>
+          <t>[kɛk̚k͈wa̠nsʰʌ̹ŋ]</t>
         </is>
       </c>
       <c r="D1127" s="1" t="inlineStr">
@@ -36563,12 +36563,12 @@
       </c>
       <c r="B1130" s="1" t="inlineStr">
         <is>
-          <t>[kikaket] 记者证 (媒体与新闻学)</t>
+          <t>[[kid͡ʑa̠d͡ʑɯŋ]] 记者证 (媒体与新闻学)</t>
         </is>
       </c>
       <c r="C1130" s="1" t="inlineStr">
         <is>
-          <t>kikaket</t>
+          <t>[kid͡ʑa̠d͡ʑɯŋ]</t>
         </is>
       </c>
       <c r="D1130" s="1" t="inlineStr">
@@ -36595,12 +36595,12 @@
       </c>
       <c r="B1131" s="1" t="inlineStr">
         <is>
-          <t>[tukkapet] 读者群 (媒体与新闻学)</t>
+          <t>[[to̞k̚t͡ɕ͈a̠t͡ɕʰɯŋ]] 读者群 (媒体与新闻学)</t>
         </is>
       </c>
       <c r="C1131" s="1" t="inlineStr">
         <is>
-          <t>tukkapet</t>
+          <t>[to̞k̚t͡ɕ͈a̠t͡ɕʰɯŋ]</t>
         </is>
       </c>
       <c r="D1131" s="1" t="inlineStr">
@@ -36627,12 +36627,12 @@
       </c>
       <c r="B1132" s="1" t="inlineStr">
         <is>
-          <t>[chinukereik] 信息图 (媒体与新闻学)</t>
+          <t>[[inpo̞kɯɾepʰik]] 信息图 (媒体与新闻学)</t>
         </is>
       </c>
       <c r="C1132" s="1" t="inlineStr">
         <is>
-          <t>chinukereik</t>
+          <t>[inpo̞kɯɾepʰik]</t>
         </is>
       </c>
       <c r="D1132" s="1" t="inlineStr">
@@ -36659,12 +36659,12 @@
       </c>
       <c r="B1133" s="1" t="inlineStr">
         <is>
-          <t>[hemrikrwm] 点击率 (媒体与新闻学)</t>
+          <t>[[kɯllik̚ɲul]] 点击率 (媒体与新闻学)</t>
         </is>
       </c>
       <c r="C1133" s="1" t="inlineStr">
         <is>
-          <t>hemrikrwm</t>
+          <t>[kɯllik̚ɲul]</t>
         </is>
       </c>
       <c r="D1133" s="1" t="inlineStr">
@@ -36691,12 +36691,12 @@
       </c>
       <c r="B1134" s="1" t="inlineStr">
         <is>
-          <t>[tantuk] 专属 (媒体与新闻学)</t>
+          <t>[[ta̠ndo̞k̚]] 专属 (媒体与新闻学)</t>
         </is>
       </c>
       <c r="C1134" s="1" t="inlineStr">
         <is>
-          <t>tantuk</t>
+          <t>[ta̠ndo̞k̚]</t>
         </is>
       </c>
       <c r="D1134" s="1" t="inlineStr">
@@ -36755,12 +36755,12 @@
       </c>
       <c r="B1136" s="1" t="inlineStr">
         <is>
-          <t>[echikipw] 页面视图 (媒体与新闻学)</t>
+          <t>[[pʰed͡ʑibju]] 页面视图 (媒体与新闻学)</t>
         </is>
       </c>
       <c r="C1136" s="1" t="inlineStr">
         <is>
-          <t>echikipw</t>
+          <t>[pʰed͡ʑibju]</t>
         </is>
       </c>
       <c r="D1136" s="1" t="inlineStr">
@@ -36851,12 +36851,12 @@
       </c>
       <c r="B1139" s="1" t="inlineStr">
         <is>
-          <t>[chyorunkunga] 观点投票 (媒体与新闻学)</t>
+          <t>[[jʌ̹ɾo̞nt͡ɕʰo̞sa]] 观点投票 (媒体与新闻学)</t>
         </is>
       </c>
       <c r="C1139" s="1" t="inlineStr">
         <is>
-          <t>chyorunkunga</t>
+          <t>[jʌ̹ɾo̞nt͡ɕʰo̞sa]</t>
         </is>
       </c>
       <c r="D1139" s="1" t="inlineStr">
@@ -36883,12 +36883,12 @@
       </c>
       <c r="B1140" s="1" t="inlineStr">
         <is>
-          <t>[pekengok] 采访席 (媒体与新闻业)</t>
+          <t>[[t͡ɕʰwe̞d͡ʑɛsʰʌ̹k̚]] 采访席 (媒体与新闻业)</t>
         </is>
       </c>
       <c r="C1140" s="1" t="inlineStr">
         <is>
-          <t>pekengok</t>
+          <t>[t͡ɕʰwe̞d͡ʑɛsʰʌ̹k̚]</t>
         </is>
       </c>
       <c r="D1140" s="1" t="inlineStr">
@@ -37107,12 +37107,12 @@
       </c>
       <c r="B1147" s="1" t="inlineStr">
         <is>
-          <t>[pekkingpi] 白泡菜 (韩国美食与餐饮)</t>
+          <t>[[pɛ̝k̚k͈imtɕʰi]] 白泡菜 (韩国美食与餐饮)</t>
         </is>
       </c>
       <c r="C1147" s="1" t="inlineStr">
         <is>
-          <t>pekkingpi</t>
+          <t>[pɛ̝k̚k͈imtɕʰi]</t>
         </is>
       </c>
       <c r="D1147" s="1" t="inlineStr">
@@ -37235,12 +37235,12 @@
       </c>
       <c r="B1151" s="1" t="inlineStr">
         <is>
-          <t>[chuchingupakchi] 黄瓜泡菜 (韩国美食与餐饮)</t>
+          <t>[[o̞iso̞ba̠ɡi]] 黄瓜泡菜 (韩国美食与餐饮)</t>
         </is>
       </c>
       <c r="C1151" s="1" t="inlineStr">
         <is>
-          <t>chuchingupakchi</t>
+          <t>[o̞iso̞ba̠ɡi]</t>
         </is>
       </c>
       <c r="D1151" s="1" t="inlineStr">
@@ -37299,12 +37299,12 @@
       </c>
       <c r="B1153" s="1" t="inlineStr">
         <is>
-          <t>[tumngupipingpang] 石锅拌饭 (명사)</t>
+          <t>[[to̞l̚s͈o̞t̚pibimbap̚]] 石锅拌饭 (명사)</t>
         </is>
       </c>
       <c r="C1153" s="1" t="inlineStr">
         <is>
-          <t>tumngupipingpang</t>
+          <t>[to̞l̚s͈o̞t̚pibimbap̚]</t>
         </is>
       </c>
       <c r="D1153" s="1" t="inlineStr">
@@ -37363,12 +37363,12 @@
       </c>
       <c r="B1155" s="1" t="inlineStr">
         <is>
-          <t>[kampikuring] 炖带鱼 (명사)</t>
+          <t>[[ka̠ltɕʰitɕo̞ɾim]] 炖带鱼 (명사)</t>
         </is>
       </c>
       <c r="C1155" s="1" t="inlineStr">
         <is>
-          <t>kampikuring</t>
+          <t>[ka̠ltɕʰitɕo̞ɾim]</t>
         </is>
       </c>
       <c r="D1155" s="1" t="inlineStr">
@@ -37395,12 +37395,12 @@
       </c>
       <c r="B1156" s="1" t="inlineStr">
         <is>
-          <t>[makkikngi] 荞麦面 (명사)</t>
+          <t>[[ma̠k̚k͈uk̚s͈u]] 荞麦面 (명사)</t>
         </is>
       </c>
       <c r="C1156" s="1" t="inlineStr">
         <is>
-          <t>makkikngi</t>
+          <t>[ma̠k̚k͈uk̚s͈u]</t>
         </is>
       </c>
       <c r="D1156" s="1" t="inlineStr">
@@ -37427,12 +37427,12 @@
       </c>
       <c r="B1157" s="1" t="inlineStr">
         <is>
-          <t>[myompipukcheng] 炒小鱼干 (명사)</t>
+          <t>[[mjʌ̹ltɕʰip͈o̞ɡɯm]] 炒小鱼干 (명사)</t>
         </is>
       </c>
       <c r="C1157" s="1" t="inlineStr">
         <is>
-          <t>myompipukcheng</t>
+          <t>[mjʌ̹ltɕʰip͈o̞ɡɯm]</t>
         </is>
       </c>
       <c r="D1157" s="1" t="inlineStr">
@@ -37459,12 +37459,12 @@
       </c>
       <c r="B1158" s="1" t="inlineStr">
         <is>
-          <t>[ngintekik] 米肠汤 (명사)</t>
+          <t>[[sun̪dɛ̝ɡuk̚]] 米肠汤 (명사)</t>
         </is>
       </c>
       <c r="C1158" s="1" t="inlineStr">
         <is>
-          <t>ngintekik</t>
+          <t>[sun̪dɛ̝ɡuk̚]</t>
         </is>
       </c>
       <c r="D1158" s="1" t="inlineStr">
@@ -37619,12 +37619,12 @@
       </c>
       <c r="B1163" s="1" t="inlineStr">
         <is>
-          <t>[talkik] 鸡肉粥 (명사)</t>
+          <t>[[ta̠k̚t͈uk̚]] 鸡肉粥 (명사)</t>
         </is>
       </c>
       <c r="C1163" s="1" t="inlineStr">
         <is>
-          <t>talkik</t>
+          <t>[ta̠k̚t͈uk̚]</t>
         </is>
       </c>
       <c r="D1163" s="1" t="inlineStr">
@@ -37651,12 +37651,12 @@
       </c>
       <c r="B1164" s="1" t="inlineStr">
         <is>
-          <t>[kankatkichi] 酱油烤肉/烤鱼；酱油烧烤 (명사)</t>
+          <t>[[ka̠ndʑa̠ŋɡui]] 酱油烤肉/烤鱼；酱油烧烤 (명사)</t>
         </is>
       </c>
       <c r="C1164" s="1" t="inlineStr">
         <is>
-          <t>kankatkichi</t>
+          <t>[ka̠ndʑa̠ŋɡui]</t>
         </is>
       </c>
       <c r="D1164" s="1" t="inlineStr">
@@ -37683,12 +37683,12 @@
       </c>
       <c r="B1165" s="1" t="inlineStr">
         <is>
-          <t>[upakkon] 煎西葫芦饼；南瓜饼 (명사)</t>
+          <t>[[ho̞bak̚tɕʌ̹n]] 煎西葫芦饼；南瓜饼 (명사)</t>
         </is>
       </c>
       <c r="C1165" s="1" t="inlineStr">
         <is>
-          <t>upakkon</t>
+          <t>[ho̞bak̚tɕʌ̹n]</t>
         </is>
       </c>
       <c r="D1165" s="1" t="inlineStr">
@@ -37715,12 +37715,12 @@
       </c>
       <c r="B1166" s="1" t="inlineStr">
         <is>
-          <t>[twekikikpang] 猪肉汤饭 (명사)</t>
+          <t>[[twe̞dʑiɡuk̚p͈ap̚]] 猪肉汤饭 (명사)</t>
         </is>
       </c>
       <c r="C1166" s="1" t="inlineStr">
         <is>
-          <t>twekikikpang</t>
+          <t>[twe̞dʑiɡuk̚p͈ap̚]</t>
         </is>
       </c>
       <c r="D1166" s="1" t="inlineStr">
@@ -37779,12 +37779,12 @@
       </c>
       <c r="B1168" s="1" t="inlineStr">
         <is>
-          <t>[pipikon] 韭菜煎饼 (명사)</t>
+          <t>[[pu̠tɕʰutɕʌ̹n]] 韭菜煎饼 (명사)</t>
         </is>
       </c>
       <c r="C1168" s="1" t="inlineStr">
         <is>
-          <t>pipikon</t>
+          <t>[pu̠tɕʰutɕʌ̹n]</t>
         </is>
       </c>
       <c r="D1168" s="1" t="inlineStr">
@@ -37811,7 +37811,7 @@
       </c>
       <c r="B1169" s="1" t="inlineStr">
         <is>
-          <t>[[ɸwe̞]] 锄头 (韩国饮食文化)</t>
+          <t>[[ɸwe̞]] 生鱼片 (韩国饮食文化)</t>
         </is>
       </c>
       <c r="C1169" s="1" t="inlineStr">
@@ -37821,7 +37821,7 @@
       </c>
       <c r="D1169" s="1" t="inlineStr">
         <is>
-          <t>锄头 (韩国饮食文化)</t>
+          <t>生鱼片 (韩国饮食文化)</t>
         </is>
       </c>
       <c r="E1169" s="1" t="inlineStr">
@@ -37843,12 +37843,12 @@
       </c>
       <c r="B1170" s="1" t="inlineStr">
         <is>
-          <t>[ngintepukcheng] 炒米肠 (명사)</t>
+          <t>[[sun̪de̞p͈o̞ɡɯm]] 炒米肠 (명사)</t>
         </is>
       </c>
       <c r="C1170" s="1" t="inlineStr">
         <is>
-          <t>ngintepukcheng</t>
+          <t>[sun̪de̞p͈o̞ɡɯm]</t>
         </is>
       </c>
       <c r="D1170" s="1" t="inlineStr">
@@ -37875,12 +37875,12 @@
       </c>
       <c r="B1171" s="1" t="inlineStr">
         <is>
-          <t>[memimkikngi] 荞麦面 (韩国饮食文化)</t>
+          <t>[[me̞miɡuk̚s͈u]] 荞麦面 (韩国饮食文化)</t>
         </is>
       </c>
       <c r="C1171" s="1" t="inlineStr">
         <is>
-          <t>memimkikngi</t>
+          <t>[me̞miɡuk̚s͈u]</t>
         </is>
       </c>
       <c r="D1171" s="1" t="inlineStr">
@@ -37939,12 +37939,12 @@
       </c>
       <c r="B1173" s="1" t="inlineStr">
         <is>
-          <t>[chwku] 肉干；牛肉干 (명사)</t>
+          <t>[[juk̚pʰo̞]] 肉干；牛肉干 (명사)</t>
         </is>
       </c>
       <c r="C1173" s="1" t="inlineStr">
         <is>
-          <t>chwku</t>
+          <t>[juk̚pʰo̞]</t>
         </is>
       </c>
       <c r="D1173" s="1" t="inlineStr">
@@ -38035,12 +38035,12 @@
       </c>
       <c r="B1176" s="1" t="inlineStr">
         <is>
-          <t>[ngichwk] 白切肉；熟肉 (명사)</t>
+          <t>[[su̠juk̚]] 白切肉；熟肉 (명사)</t>
         </is>
       </c>
       <c r="C1176" s="1" t="inlineStr">
         <is>
-          <t>ngichwk</t>
+          <t>[su̠juk̚]</t>
         </is>
       </c>
       <c r="D1176" s="1" t="inlineStr">
@@ -38067,17 +38067,17 @@
       </c>
       <c r="B1177" s="1" t="inlineStr">
         <is>
-          <t>[chekkot] 鳀鱼酱 (韩国饮食文化)</t>
+          <t>[[ɛk̚t͡ɕʌt̚]] 鱼露 (韩国饮食文化)</t>
         </is>
       </c>
       <c r="C1177" s="1" t="inlineStr">
         <is>
-          <t>chekkot</t>
+          <t>[ɛk̚t͡ɕʌt̚]</t>
         </is>
       </c>
       <c r="D1177" s="1" t="inlineStr">
         <is>
-          <t>鳀鱼酱 (韩国饮食文化)</t>
+          <t>鱼露 (韩国饮食文化)</t>
         </is>
       </c>
       <c r="E1177" s="1" t="inlineStr">
@@ -38163,12 +38163,12 @@
       </c>
       <c r="B1180" s="1" t="inlineStr">
         <is>
-          <t>[chukitchopukcheng] 辣炒鱿鱼 (韩国饮食文化)</t>
+          <t>[[o.d͡ʑi.ŋʌ.po.k͈ɯm]] 辣炒鱿鱼 (韩国饮食文化)</t>
         </is>
       </c>
       <c r="C1180" s="1" t="inlineStr">
         <is>
-          <t>chukitchopukcheng</t>
+          <t>[o.d͡ʑi.ŋʌ.po.k͈ɯm]</t>
         </is>
       </c>
       <c r="D1180" s="1" t="inlineStr">
@@ -38227,12 +38227,12 @@
       </c>
       <c r="B1182" s="1" t="inlineStr">
         <is>
-          <t>[ngukampi] 韩式烤排骨 (韩国饮食文化)</t>
+          <t>[[so.kaɾ.bi]] 韩式烤排骨 (韩国饮食文化)</t>
         </is>
       </c>
       <c r="C1182" s="1" t="inlineStr">
         <is>
-          <t>ngukampi</t>
+          <t>[so.kaɾ.bi]</t>
         </is>
       </c>
       <c r="D1182" s="1" t="inlineStr">
@@ -38259,12 +38259,12 @@
       </c>
       <c r="B1183" s="1" t="inlineStr">
         <is>
-          <t>[talpukcheng] 辣炖鸡 (韩国饮食文化)</t>
+          <t>[[ta.k̚po.k͈ɯm]] 辣炖鸡 (韩国饮食文化)</t>
         </is>
       </c>
       <c r="C1183" s="1" t="inlineStr">
         <is>
-          <t>talpukcheng</t>
+          <t>[ta.k̚po.k͈ɯm]</t>
         </is>
       </c>
       <c r="D1183" s="1" t="inlineStr">
@@ -38291,12 +38291,12 @@
       </c>
       <c r="B1184" s="1" t="inlineStr">
         <is>
-          <t>[tuurimikmiping] 橡子冻 (韩国饮食文化)</t>
+          <t>[[to.to.ɾi.mu.k͈mu.t͡ɕʰim]] 橡子冻 (韩国饮食文化)</t>
         </is>
       </c>
       <c r="C1184" s="1" t="inlineStr">
         <is>
-          <t>tuurimikmiping</t>
+          <t>[to.to.ɾi.mu.k͈mu.t͡ɕʰim]</t>
         </is>
       </c>
       <c r="D1184" s="1" t="inlineStr">
@@ -38355,12 +38355,12 @@
       </c>
       <c r="B1186" s="1" t="inlineStr">
         <is>
-          <t>[mingetpe] 凉拌萝卜丝 (韩国饮食文化)</t>
+          <t>[[mu.sɛŋ.t͡ɕʰɛ]] 凉拌萝卜丝 (韩国饮食文化)</t>
         </is>
       </c>
       <c r="C1186" s="1" t="inlineStr">
         <is>
-          <t>mingetpe</t>
+          <t>[mu.sɛŋ.t͡ɕʰɛ]</t>
         </is>
       </c>
       <c r="D1186" s="1" t="inlineStr">
@@ -38387,12 +38387,12 @@
       </c>
       <c r="B1187" s="1" t="inlineStr">
         <is>
-          <t>[ketpankikngi] 盘子冷面 (韩国饮食文化)</t>
+          <t>[[t͡ɕɛŋ.pan.kuk̚.su]] 盘子冷面 (韩国饮食文化)</t>
         </is>
       </c>
       <c r="C1187" s="1" t="inlineStr">
         <is>
-          <t>ketpankikngi</t>
+          <t>[t͡ɕɛŋ.pan.kuk̚.su]</t>
         </is>
       </c>
       <c r="D1187" s="1" t="inlineStr">
@@ -38419,12 +38419,12 @@
       </c>
       <c r="B1188" s="1" t="inlineStr">
         <is>
-          <t>[machengpetking] 正念 (心理健康与身心保健)</t>
+          <t>[[ma.ɯm.t͡ɕʰɛŋ.k͈im]] 正念 (心理健康与身心保健)</t>
         </is>
       </c>
       <c r="C1188" s="1" t="inlineStr">
         <is>
-          <t>machengpetking</t>
+          <t>[ma.ɯm.t͡ɕʰɛŋ.k͈im]</t>
         </is>
       </c>
       <c r="D1188" s="1" t="inlineStr">
@@ -38451,12 +38451,12 @@
       </c>
       <c r="B1189" s="1" t="inlineStr">
         <is>
-          <t>[erachima] 创伤 (心理健康与保健)</t>
+          <t>[[tʰɯ.ɾa.u.ma]] 创伤 (心理健康与保健)</t>
         </is>
       </c>
       <c r="C1189" s="1" t="inlineStr">
         <is>
-          <t>erachima</t>
+          <t>[tʰɯ.ɾa.u.ma]</t>
         </is>
       </c>
       <c r="D1189" s="1" t="inlineStr">
@@ -38483,12 +38483,12 @@
       </c>
       <c r="B1190" s="1" t="inlineStr">
         <is>
-          <t>[kutwtpamkak] 恐慌攻击 (心理健康与保健)</t>
+          <t>[[koŋ.ɦwaŋ.paɾ.t͡ɕak̚]] 恐慌攻击 (心理健康与保健)</t>
         </is>
       </c>
       <c r="C1190" s="1" t="inlineStr">
         <is>
-          <t>kutwtpamkak</t>
+          <t>[koŋ.ɦwaŋ.paɾ.t͡ɕak̚]</t>
         </is>
       </c>
       <c r="D1190" s="1" t="inlineStr">
@@ -38643,12 +38643,12 @@
       </c>
       <c r="B1195" s="1" t="inlineStr">
         <is>
-          <t>[ngingripiry] 心理治疗 (心理健康与保健)</t>
+          <t>[[ɕim.ɲi.t͡ɕʰi.ɾjo]] 心理治疗 (心理健康与保健)</t>
         </is>
       </c>
       <c r="C1195" s="1" t="inlineStr">
         <is>
-          <t>ngingripiry</t>
+          <t>[ɕim.ɲi.t͡ɕʰi.ɾjo]</t>
         </is>
       </c>
       <c r="D1195" s="1" t="inlineStr">
@@ -38675,12 +38675,12 @@
       </c>
       <c r="B1196" s="1" t="inlineStr">
         <is>
-          <t>[ngichyt] 接纳 (心理健康与保健)</t>
+          <t>[[su.joŋ]] 接纳 (心理健康与保健)</t>
         </is>
       </c>
       <c r="C1196" s="1" t="inlineStr">
         <is>
-          <t>ngichyt</t>
+          <t>[su.joŋ]</t>
         </is>
       </c>
       <c r="D1196" s="1" t="inlineStr">
@@ -38707,12 +38707,12 @@
       </c>
       <c r="B1197" s="1" t="inlineStr">
         <is>
-          <t>[chwnpyokkichy] 完美主义 (心理健康与保健)</t>
+          <t>[[waɲ.bjʌk̚.t͡ɕu.ɰi]] 完美主义 (心理健康与保健)</t>
         </is>
       </c>
       <c r="C1197" s="1" t="inlineStr">
         <is>
-          <t>chwnpyokkichy</t>
+          <t>[waɲ.bjʌk̚.t͡ɕu.ɰi]</t>
         </is>
       </c>
       <c r="D1197" s="1" t="inlineStr">
@@ -38739,12 +38739,12 @@
       </c>
       <c r="B1198" s="1" t="inlineStr">
         <is>
-          <t>[nginpengat] 身体意象 (心理健康与保健)</t>
+          <t>[[ɕin.t͡ɕʰe.saŋ]] 身体意象 (心理健康与保健)</t>
         </is>
       </c>
       <c r="C1198" s="1" t="inlineStr">
         <is>
-          <t>nginpengat</t>
+          <t>[ɕin.t͡ɕʰe.saŋ]</t>
         </is>
       </c>
       <c r="D1198" s="1" t="inlineStr">
@@ -38835,12 +38835,12 @@
       </c>
       <c r="B1201" s="1" t="inlineStr">
         <is>
-          <t>[enngachie] 站姐网站 (韩国流行文化)</t>
+          <t>[[pʰɛn.sa.i.tʰɯ]] 站姐网站 (韩国流行文化)</t>
         </is>
       </c>
       <c r="C1201" s="1" t="inlineStr">
         <is>
-          <t>enngachie</t>
+          <t>[pʰɛn.sa.i.tʰɯ]</t>
         </is>
       </c>
       <c r="D1201" s="1" t="inlineStr">
@@ -38899,12 +38899,12 @@
       </c>
       <c r="B1203" s="1" t="inlineStr">
         <is>
-          <t>[iko] 预告片 (韩国流行文化)</t>
+          <t>[[tʰi.d͡ʑʌ]] 预告片 (韩国流行文化)</t>
         </is>
       </c>
       <c r="C1203" s="1" t="inlineStr">
         <is>
-          <t>iko</t>
+          <t>[tʰi.d͡ʑʌ]</t>
         </is>
       </c>
       <c r="D1203" s="1" t="inlineStr">
@@ -38995,12 +38995,12 @@
       </c>
       <c r="B1206" s="1" t="inlineStr">
         <is>
-          <t>[ngeen] 狂粉 (韩国流行文化)</t>
+          <t>[[sɯ.tʰɛn]] 狂粉 (韩国流行文化)</t>
         </is>
       </c>
       <c r="C1206" s="1" t="inlineStr">
         <is>
-          <t>ngeen</t>
+          <t>[sɯ.tʰɛn]</t>
         </is>
       </c>
       <c r="D1206" s="1" t="inlineStr">
@@ -39059,12 +39059,12 @@
       </c>
       <c r="B1208" s="1" t="inlineStr">
         <is>
-          <t>[ngetringee] 歌单 (韩国流行文化)</t>
+          <t>[[seːn.ɲi.sɯ.tʰɯ]] 歌单 (韩国流行文化)</t>
         </is>
       </c>
       <c r="C1208" s="1" t="inlineStr">
         <is>
-          <t>ngetringee</t>
+          <t>[seːn.ɲi.sɯ.tʰɯ]</t>
         </is>
       </c>
       <c r="D1208" s="1" t="inlineStr">
@@ -39155,12 +39155,12 @@
       </c>
       <c r="B1211" s="1" t="inlineStr">
         <is>
-          <t>[kitngotw] 结扎 (宠物照护与动物)</t>
+          <t>[[t͡ɕuŋ.sʌŋ.ɦwa]] 结扎 (宠物照护与动物)</t>
         </is>
       </c>
       <c r="C1211" s="1" t="inlineStr">
         <is>
-          <t>kitngotw</t>
+          <t>[t͡ɕuŋ.sʌŋ.ɦwa]</t>
         </is>
       </c>
       <c r="D1211" s="1" t="inlineStr">
@@ -39187,12 +39187,12 @@
       </c>
       <c r="B1212" s="1" t="inlineStr">
         <is>
-          <t>[machiheruping] 微芯 (宠物照护与动物)</t>
+          <t>[[ma.i.kʰɯ.ɾo.t͡ɕʰip̚]] 微芯 (宠物照护与动物)</t>
         </is>
       </c>
       <c r="C1212" s="1" t="inlineStr">
         <is>
-          <t>machiheruping</t>
+          <t>[ma.i.kʰɯ.ɾo.t͡ɕʰip̚]</t>
         </is>
       </c>
       <c r="D1212" s="1" t="inlineStr">
@@ -39219,12 +39219,12 @@
       </c>
       <c r="B1213" s="1" t="inlineStr">
         <is>
-          <t>[enngachinwi] 粉丝签名会 (韩国流行文化)</t>
+          <t>[[pʰɛn.sa.in.ɦwe]] 粉丝签名会 (韩国流行文化)</t>
         </is>
       </c>
       <c r="C1213" s="1" t="inlineStr">
         <is>
-          <t>enngachinwi</t>
+          <t>[pʰɛn.sa.in.ɦwe]</t>
         </is>
       </c>
       <c r="D1213" s="1" t="inlineStr">
@@ -39251,12 +39251,12 @@
       </c>
       <c r="B1214" s="1" t="inlineStr">
         <is>
-          <t>[chwnit] 小分队 (韩国流行文化)</t>
+          <t>[[ju.nit̚]] 小分队 (韩国流行文化)</t>
         </is>
       </c>
       <c r="C1214" s="1" t="inlineStr">
         <is>
-          <t>chwnit</t>
+          <t>[ju.nit̚]</t>
         </is>
       </c>
       <c r="D1214" s="1" t="inlineStr">
@@ -39315,12 +39315,12 @@
       </c>
       <c r="B1216" s="1" t="inlineStr">
         <is>
-          <t>[kipitke] 驱虫治疗 (宠物照护与动物)</t>
+          <t>[[ku.tɕʰuŋ.dʑe]] 驱虫治疗 (宠物照护与动物)</t>
         </is>
       </c>
       <c r="C1216" s="1" t="inlineStr">
         <is>
-          <t>kipitke</t>
+          <t>[ku.tɕʰuŋ.dʑe]</t>
         </is>
       </c>
       <c r="D1216" s="1" t="inlineStr">
@@ -39347,12 +39347,12 @@
       </c>
       <c r="B1217" s="1" t="inlineStr">
         <is>
-          <t>[channekyon] 服务犬 (宠物照护与动物)</t>
+          <t>[[an.nɛ.ɡjʌn]] 服务犬 (宠物照护与动物)</t>
         </is>
       </c>
       <c r="C1217" s="1" t="inlineStr">
         <is>
-          <t>channekyon</t>
+          <t>[an.nɛ.ɡjʌn]</t>
         </is>
       </c>
       <c r="D1217" s="1" t="inlineStr">
@@ -39411,12 +39411,12 @@
       </c>
       <c r="B1219" s="1" t="inlineStr">
         <is>
-          <t>[kimte] 公会 (游戏与电竞)</t>
+          <t>[[kil.dɯ]] 公会 (游戏与电竞)</t>
         </is>
       </c>
       <c r="C1219" s="1" t="inlineStr">
         <is>
-          <t>kimte</t>
+          <t>[kil.dɯ]</t>
         </is>
       </c>
       <c r="D1219" s="1" t="inlineStr">
@@ -39603,12 +39603,12 @@
       </c>
       <c r="B1225" s="1" t="inlineStr">
         <is>
-          <t>[noe] 削弱 (游戏与电竞)</t>
+          <t>[[nʌ.pʰɯ]] 削弱 (游戏与电竞)</t>
         </is>
       </c>
       <c r="C1225" s="1" t="inlineStr">
         <is>
-          <t>noe</t>
+          <t>[nʌ.pʰɯ]</t>
         </is>
       </c>
       <c r="D1225" s="1" t="inlineStr">
@@ -39635,17 +39635,17 @@
       </c>
       <c r="B1226" s="1" t="inlineStr">
         <is>
-          <t>[wkkatek] 游戏扩充内容 (游戏与电竞)</t>
+          <t>[[ɦwa.k̚.tɕaŋ.pʰɛk̚]] 资料片 (游戏与电竞)</t>
         </is>
       </c>
       <c r="C1226" s="1" t="inlineStr">
         <is>
-          <t>wkkatek</t>
+          <t>[ɦwa.k̚.tɕaŋ.pʰɛk̚]</t>
         </is>
       </c>
       <c r="D1226" s="1" t="inlineStr">
         <is>
-          <t>游戏扩充内容 (游戏与电竞)</t>
+          <t>资料片 (游戏与电竞)</t>
         </is>
       </c>
       <c r="E1226" s="1" t="inlineStr">
@@ -39667,17 +39667,17 @@
       </c>
       <c r="B1227" s="1" t="inlineStr">
         <is>
-          <t>[rumpengnge] LCK (英雄联盟冠军赛) (游戏与电竞)</t>
+          <t>[[rol.tɕʰɛm.sɯ]] 英雄联盟韩国冠军联赛 (游戏与电竞)</t>
         </is>
       </c>
       <c r="C1227" s="1" t="inlineStr">
         <is>
-          <t>rumpengnge</t>
+          <t>[rol.tɕʰɛm.sɯ]</t>
         </is>
       </c>
       <c r="D1227" s="1" t="inlineStr">
         <is>
-          <t>LCK (英雄联盟冠军赛) (游戏与电竞)</t>
+          <t>英雄联盟韩国冠军联赛 (游戏与电竞)</t>
         </is>
       </c>
       <c r="E1227" s="1" t="inlineStr">
@@ -39699,12 +39699,12 @@
       </c>
       <c r="B1228" s="1" t="inlineStr">
         <is>
-          <t>[himaching] 冷却时间 (游戏与电竞)</t>
+          <t>[[kʰul.tʰa.im]] 冷却时间 (游戏与电竞)</t>
         </is>
       </c>
       <c r="C1228" s="1" t="inlineStr">
         <is>
-          <t>himaching</t>
+          <t>[kʰul.tʰa.im]</t>
         </is>
       </c>
       <c r="D1228" s="1" t="inlineStr">
